--- a/03_Output/Models/Exposure_models_PO_cox_cesarea_stratified.xlsx
+++ b/03_Output/Models/Exposure_models_PO_cox_cesarea_stratified.xlsx
@@ -463,31 +463,31 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9960637169347852</v>
+        <v>0.9960637169347893</v>
       </c>
       <c r="C2">
-        <v>0.986661966971513</v>
+        <v>0.9866619669715172</v>
       </c>
       <c r="D2">
-        <v>1.005555054725835</v>
+        <v>1.005555054725839</v>
       </c>
       <c r="E2">
-        <v>-0.003944050617623196</v>
+        <v>-0.003944050617619071</v>
       </c>
       <c r="F2">
-        <v>-0.01342778354803243</v>
+        <v>-0.01342778354802816</v>
       </c>
       <c r="G2">
-        <v>0.005539682312785985</v>
+        <v>0.005539682312790181</v>
       </c>
       <c r="H2">
-        <v>0.004838728162974247</v>
+        <v>0.004838728162974217</v>
       </c>
       <c r="I2">
-        <v>-0.8151006803405358</v>
+        <v>-0.8151006803396785</v>
       </c>
       <c r="J2">
-        <v>0.4150146822492841</v>
+        <v>0.4150146822497747</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -543,31 +543,31 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9981195263716121</v>
+        <v>0.9981195263716119</v>
       </c>
       <c r="C3">
-        <v>0.995283286429701</v>
+        <v>0.9952832864297009</v>
       </c>
       <c r="D3">
         <v>1.000963848692799</v>
       </c>
       <c r="E3">
-        <v>-0.001882243938617413</v>
+        <v>-0.001882243938617524</v>
       </c>
       <c r="F3">
-        <v>-0.004727872366140343</v>
+        <v>-0.004727872366140454</v>
       </c>
       <c r="G3">
-        <v>0.0009633844889054891</v>
+        <v>0.0009633844889052673</v>
       </c>
       <c r="H3">
-        <v>0.001451877917129531</v>
+        <v>0.001451877917129537</v>
       </c>
       <c r="I3">
-        <v>-1.296420254354964</v>
+        <v>-1.296420254355055</v>
       </c>
       <c r="J3">
-        <v>0.1948307377386926</v>
+        <v>0.1948307377386611</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.045205041396942</v>
+        <v>1.045205041396765</v>
       </c>
       <c r="C4">
-        <v>0.5470552168521238</v>
+        <v>0.5470552168520343</v>
       </c>
       <c r="D4">
-        <v>1.996971320094163</v>
+        <v>1.996971320093812</v>
       </c>
       <c r="E4">
-        <v>0.04421307803284719</v>
+        <v>0.04421307803267745</v>
       </c>
       <c r="F4">
-        <v>-0.6032055367696953</v>
+        <v>-0.6032055367698589</v>
       </c>
       <c r="G4">
-        <v>0.6916316928353897</v>
+        <v>0.6916316928352141</v>
       </c>
       <c r="H4">
-        <v>0.3303216895357762</v>
+        <v>0.3303216895357732</v>
       </c>
       <c r="I4">
-        <v>0.1338485465334806</v>
+        <v>0.133848546532968</v>
       </c>
       <c r="J4">
-        <v>0.8935223379652991</v>
+        <v>0.8935223379657043</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -703,31 +703,31 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9167872495940824</v>
+        <v>0.916787249594093</v>
       </c>
       <c r="C5">
-        <v>0.7690731122607659</v>
+        <v>0.769073112260774</v>
       </c>
       <c r="D5">
-        <v>1.092872507982438</v>
+        <v>1.092872507982452</v>
       </c>
       <c r="E5">
-        <v>-0.08687984062918987</v>
+        <v>-0.08687984062917836</v>
       </c>
       <c r="F5">
-        <v>-0.2625692395344492</v>
+        <v>-0.2625692395344386</v>
       </c>
       <c r="G5">
-        <v>0.08880955827606953</v>
+        <v>0.08880955827608172</v>
       </c>
       <c r="H5">
-        <v>0.0896390955604669</v>
+        <v>0.08963909556046736</v>
       </c>
       <c r="I5">
-        <v>-0.9692181752389971</v>
+        <v>-0.9692181752388648</v>
       </c>
       <c r="J5">
-        <v>0.3324363445945532</v>
+        <v>0.3324363445946193</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -783,31 +783,31 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.894598676847702</v>
+        <v>0.8945986768477566</v>
       </c>
       <c r="C6">
-        <v>0.4996832861263028</v>
+        <v>0.4996832861263355</v>
       </c>
       <c r="D6">
-        <v>1.601628100915445</v>
+        <v>1.601628100915536</v>
       </c>
       <c r="E6">
-        <v>-0.111380067027964</v>
+        <v>-0.1113800670279029</v>
       </c>
       <c r="F6">
-        <v>-0.6937808090074524</v>
+        <v>-0.693780809007387</v>
       </c>
       <c r="G6">
-        <v>0.4710206749515244</v>
+        <v>0.4710206749515812</v>
       </c>
       <c r="H6">
-        <v>0.2971486958808383</v>
+        <v>0.2971486958808361</v>
       </c>
       <c r="I6">
-        <v>-0.3748293987890471</v>
+        <v>-0.3748293987888444</v>
       </c>
       <c r="J6">
-        <v>0.7077873485711842</v>
+        <v>0.707787348571335</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -863,31 +863,31 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.9058898825790466</v>
+        <v>0.9058898825790543</v>
       </c>
       <c r="C7">
-        <v>0.7709076928205754</v>
+        <v>0.7709076928205831</v>
       </c>
       <c r="D7">
-        <v>1.064506797638193</v>
+        <v>1.064506797638201</v>
       </c>
       <c r="E7">
-        <v>-0.09883752273326803</v>
+        <v>-0.09883752273325944</v>
       </c>
       <c r="F7">
-        <v>-0.2601866365544193</v>
+        <v>-0.2601866365544092</v>
       </c>
       <c r="G7">
-        <v>0.06251159108788305</v>
+        <v>0.06251159108789035</v>
       </c>
       <c r="H7">
-        <v>0.08232248913441904</v>
+        <v>0.08232248913441834</v>
       </c>
       <c r="I7">
-        <v>-1.200613875655323</v>
+        <v>-1.200613875655228</v>
       </c>
       <c r="J7">
-        <v>0.2299010160665704</v>
+        <v>0.2299010160666072</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.9956014384262458</v>
+        <v>0.9956014384262457</v>
       </c>
       <c r="C8">
         <v>0.9914691627655455</v>
@@ -952,7 +952,7 @@
         <v>0.9997509367124974</v>
       </c>
       <c r="E8">
-        <v>-0.004408263706451504</v>
+        <v>-0.004408263706451615</v>
       </c>
       <c r="F8">
         <v>-0.008567433103988904</v>
@@ -964,10 +964,10 @@
         <v>0.002122064196252768</v>
       </c>
       <c r="I8">
-        <v>-2.077347006860494</v>
+        <v>-2.077347006860534</v>
       </c>
       <c r="J8">
-        <v>0.03776954345902864</v>
+        <v>0.03776954345902499</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1041,13 +1041,13 @@
         <v>-7.816985417275221E-05</v>
       </c>
       <c r="H9">
-        <v>0.0008586313307493355</v>
+        <v>0.0008586313307493321</v>
       </c>
       <c r="I9">
-        <v>-2.051004051881296</v>
+        <v>-2.051004051881319</v>
       </c>
       <c r="J9">
-        <v>0.04026655215845265</v>
+        <v>0.04026655215845044</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.7682917523785002</v>
+        <v>0.7682917523785276</v>
       </c>
       <c r="C10">
-        <v>0.4453999653086981</v>
+        <v>0.4453999653087163</v>
       </c>
       <c r="D10">
-        <v>1.3252632751413</v>
+        <v>1.325263275141341</v>
       </c>
       <c r="E10">
-        <v>-0.2635857320633425</v>
+        <v>-0.2635857320633068</v>
       </c>
       <c r="F10">
-        <v>-0.808782602046843</v>
+        <v>-0.8087826020468022</v>
       </c>
       <c r="G10">
-        <v>0.2816111379201579</v>
+        <v>0.2816111379201885</v>
       </c>
       <c r="H10">
-        <v>0.278166779738783</v>
+        <v>0.2781667797387804</v>
       </c>
       <c r="I10">
-        <v>-0.9475816354162314</v>
+        <v>-0.9475816354161116</v>
       </c>
       <c r="J10">
-        <v>0.3433424789155348</v>
+        <v>0.3433424789155959</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1183,31 +1183,31 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.8918196432191006</v>
+        <v>0.8918196432191082</v>
       </c>
       <c r="C11">
-        <v>0.7543704226349459</v>
+        <v>0.7543704226349538</v>
       </c>
       <c r="D11">
-        <v>1.054312645574553</v>
+        <v>1.05431264557456</v>
       </c>
       <c r="E11">
-        <v>-0.1144913605465896</v>
+        <v>-0.1144913605465811</v>
       </c>
       <c r="F11">
-        <v>-0.2818717549068996</v>
+        <v>-0.2818717549068891</v>
       </c>
       <c r="G11">
-        <v>0.05288903381372014</v>
+        <v>0.05288903381372688</v>
       </c>
       <c r="H11">
-        <v>0.0853997296279856</v>
+        <v>0.08539972962798463</v>
       </c>
       <c r="I11">
-        <v>-1.340652494397016</v>
+        <v>-1.340652494396931</v>
       </c>
       <c r="J11">
-        <v>0.180033305129683</v>
+        <v>0.1800333051297106</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1263,31 +1263,31 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.8249023476938189</v>
+        <v>0.8249023476938283</v>
       </c>
       <c r="C12">
-        <v>0.6003701177206118</v>
+        <v>0.6003701177206153</v>
       </c>
       <c r="D12">
-        <v>1.133407315164601</v>
+        <v>1.13340731516462</v>
       </c>
       <c r="E12">
-        <v>-0.1924902660850497</v>
+        <v>-0.1924902660850382</v>
       </c>
       <c r="F12">
-        <v>-0.5102089510799965</v>
+        <v>-0.5102089510799905</v>
       </c>
       <c r="G12">
-        <v>0.1252284189098972</v>
+        <v>0.1252284189099141</v>
       </c>
       <c r="H12">
-        <v>0.1621043486008271</v>
+        <v>0.1621043486008299</v>
       </c>
       <c r="I12">
-        <v>-1.187446652397008</v>
+        <v>-1.187446652396917</v>
       </c>
       <c r="J12">
-        <v>0.2350514874540254</v>
+        <v>0.2350514874540613</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1343,31 +1343,31 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9114381428469348</v>
+        <v>0.9114381428469375</v>
       </c>
       <c r="C13">
-        <v>0.8153326005206215</v>
+        <v>0.8153326005206241</v>
       </c>
       <c r="D13">
-        <v>1.018871915223092</v>
+        <v>1.018871915223095</v>
       </c>
       <c r="E13">
-        <v>-0.09273155019755769</v>
+        <v>-0.09273155019755476</v>
       </c>
       <c r="F13">
-        <v>-0.2041591501926317</v>
+        <v>-0.2041591501926286</v>
       </c>
       <c r="G13">
-        <v>0.01869604979751652</v>
+        <v>0.01869604979751913</v>
       </c>
       <c r="H13">
-        <v>0.05685186099030434</v>
+        <v>0.05685186099030419</v>
       </c>
       <c r="I13">
-        <v>-1.631108438356527</v>
+        <v>-1.631108438356479</v>
       </c>
       <c r="J13">
-        <v>0.1028674404614714</v>
+        <v>0.1028674404614814</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1423,31 +1423,31 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.009001345882695</v>
+        <v>1.009001345882691</v>
       </c>
       <c r="C14">
-        <v>0.9965389010507015</v>
+        <v>0.9965389010506983</v>
       </c>
       <c r="D14">
-        <v>1.0216196426649</v>
+        <v>1.021619642664896</v>
       </c>
       <c r="E14">
-        <v>0.008961075248377104</v>
+        <v>0.008961075248373583</v>
       </c>
       <c r="F14">
-        <v>-0.003467102408647546</v>
+        <v>-0.003467102408650777</v>
       </c>
       <c r="G14">
-        <v>0.02138925290540198</v>
+        <v>0.02138925290539764</v>
       </c>
       <c r="H14">
-        <v>0.006341023485664337</v>
+        <v>0.006341023485664098</v>
       </c>
       <c r="I14">
-        <v>1.413190673183313</v>
+        <v>1.413190673182782</v>
       </c>
       <c r="J14">
-        <v>0.1575996681498356</v>
+        <v>0.1575996681499915</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1518,16 +1518,16 @@
         <v>-0.005068405993019046</v>
       </c>
       <c r="G15">
-        <v>0.001898855433435355</v>
+        <v>0.001898855433435133</v>
       </c>
       <c r="H15">
-        <v>0.001777395268844548</v>
+        <v>0.001777395268844515</v>
       </c>
       <c r="I15">
-        <v>-0.8916279386869637</v>
+        <v>-0.8916279386870176</v>
       </c>
       <c r="J15">
-        <v>0.3725923899043913</v>
+        <v>0.3725923899043623</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1583,31 +1583,31 @@
         </is>
       </c>
       <c r="B16">
-        <v>2.060434459578541</v>
+        <v>2.060434459578528</v>
       </c>
       <c r="C16">
-        <v>0.9202414235695511</v>
+        <v>0.9202414235695645</v>
       </c>
       <c r="D16">
-        <v>4.613343904636619</v>
+        <v>4.613343904636493</v>
       </c>
       <c r="E16">
-        <v>0.7229168632726696</v>
+        <v>0.7229168632726631</v>
       </c>
       <c r="F16">
-        <v>-0.08311922644092444</v>
+        <v>-0.08311922644090984</v>
       </c>
       <c r="G16">
-        <v>1.528952952986264</v>
+        <v>1.528952952986236</v>
       </c>
       <c r="H16">
-        <v>0.4112504597388035</v>
+        <v>0.4112504597387928</v>
       </c>
       <c r="I16">
-        <v>1.757850589958767</v>
+        <v>1.757850589958797</v>
       </c>
       <c r="J16">
-        <v>0.07877293481622548</v>
+        <v>0.07877293481622059</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1663,31 +1663,31 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.920704914600261</v>
+        <v>0.9207049146002245</v>
       </c>
       <c r="C17">
-        <v>0.7448843214134627</v>
+        <v>0.7448843214134354</v>
       </c>
       <c r="D17">
-        <v>1.138025751650293</v>
+        <v>1.138025751650244</v>
       </c>
       <c r="E17">
-        <v>-0.08261569080722002</v>
+        <v>-0.0826156908072597</v>
       </c>
       <c r="F17">
-        <v>-0.2945263459292397</v>
+        <v>-0.2945263459292763</v>
       </c>
       <c r="G17">
-        <v>0.1292949643147996</v>
+        <v>0.1292949643147569</v>
       </c>
       <c r="H17">
-        <v>0.1081196679089738</v>
+        <v>0.1081196679089722</v>
       </c>
       <c r="I17">
-        <v>-0.7641134347247009</v>
+        <v>-0.7641134347250796</v>
       </c>
       <c r="J17">
-        <v>0.4447996468650676</v>
+        <v>0.4447996468648419</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1743,31 +1743,31 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.776215888951896</v>
+        <v>1.776215888952032</v>
       </c>
       <c r="C18">
-        <v>0.8468085785827864</v>
+        <v>0.8468085785828677</v>
       </c>
       <c r="D18">
-        <v>3.72568602156259</v>
+        <v>3.725686021562804</v>
       </c>
       <c r="E18">
-        <v>0.5744851962768063</v>
+        <v>0.5744851962768831</v>
       </c>
       <c r="F18">
-        <v>-0.166280609183716</v>
+        <v>-0.1662806091836199</v>
       </c>
       <c r="G18">
-        <v>1.315251001737328</v>
+        <v>1.315251001737386</v>
       </c>
       <c r="H18">
-        <v>0.3779486823755889</v>
+        <v>0.377948682375579</v>
       </c>
       <c r="I18">
-        <v>1.52000846428645</v>
+        <v>1.520008464286693</v>
       </c>
       <c r="J18">
-        <v>0.1285088483285919</v>
+        <v>0.1285088483285301</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1823,31 +1823,31 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.91230467635794</v>
+        <v>0.9123046763579312</v>
       </c>
       <c r="C19">
-        <v>0.7498712957125269</v>
+        <v>0.7498712957125198</v>
       </c>
       <c r="D19">
-        <v>1.109923565901686</v>
+        <v>1.109923565901675</v>
       </c>
       <c r="E19">
-        <v>-0.09178126974453635</v>
+        <v>-0.09178126974454597</v>
       </c>
       <c r="F19">
-        <v>-0.2878536928943575</v>
+        <v>-0.287853692894367</v>
       </c>
       <c r="G19">
-        <v>0.1042911534052848</v>
+        <v>0.104291153405275</v>
       </c>
       <c r="H19">
-        <v>0.1000387888228638</v>
+        <v>0.1000387888228637</v>
       </c>
       <c r="I19">
-        <v>-0.917456826741987</v>
+        <v>-0.9174568267420837</v>
       </c>
       <c r="J19">
-        <v>0.3589033064098999</v>
+        <v>0.3589033064098492</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1903,31 +1903,31 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.9996212219806674</v>
+        <v>0.9996212219806678</v>
       </c>
       <c r="C20">
-        <v>0.9949705963275784</v>
+        <v>0.9949705963275789</v>
       </c>
       <c r="D20">
         <v>1.00429358528012</v>
       </c>
       <c r="E20">
-        <v>-0.0003788497738465071</v>
+        <v>-0.0003788497738460628</v>
       </c>
       <c r="F20">
-        <v>-0.005042093689765777</v>
+        <v>-0.005042093689765331</v>
       </c>
       <c r="G20">
-        <v>0.00428439414207285</v>
+        <v>0.00428439414207307</v>
       </c>
       <c r="H20">
-        <v>0.002379249798824056</v>
+        <v>0.002379249798824029</v>
       </c>
       <c r="I20">
-        <v>-0.1592307684690125</v>
+        <v>-0.1592307684688496</v>
       </c>
       <c r="J20">
-        <v>0.8734870633738401</v>
+        <v>0.8734870633739683</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>0.9984142324152323</v>
       </c>
       <c r="C21">
-        <v>0.9964190883569868</v>
+        <v>0.9964190883569867</v>
       </c>
       <c r="D21">
         <v>1.000413371378694</v>
@@ -1995,19 +1995,19 @@
         <v>-0.001587026244988518</v>
       </c>
       <c r="F21">
-        <v>-0.003587338454260027</v>
+        <v>-0.003587338454260138</v>
       </c>
       <c r="G21">
         <v>0.0004132859642829818</v>
       </c>
       <c r="H21">
-        <v>0.00102058620722102</v>
+        <v>0.001020586207221035</v>
       </c>
       <c r="I21">
-        <v>-1.555014396392656</v>
+        <v>-1.555014396392692</v>
       </c>
       <c r="J21">
-        <v>0.1199426406907859</v>
+        <v>0.119942640690778</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2063,31 +2063,31 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.213819304526057</v>
+        <v>1.213819304526115</v>
       </c>
       <c r="C22">
-        <v>0.6395040507669623</v>
+        <v>0.6395040507669926</v>
       </c>
       <c r="D22">
-        <v>2.303906132061419</v>
+        <v>2.30390613206153</v>
       </c>
       <c r="E22">
-        <v>0.1937718384998182</v>
+        <v>0.1937718384998661</v>
       </c>
       <c r="F22">
-        <v>-0.4470623237112725</v>
+        <v>-0.4470623237112251</v>
       </c>
       <c r="G22">
-        <v>0.8346060007109087</v>
+        <v>0.8346060007109571</v>
       </c>
       <c r="H22">
-        <v>0.3269622132171351</v>
+        <v>0.3269622132171354</v>
       </c>
       <c r="I22">
-        <v>0.59264291305471</v>
+        <v>0.5926429130548559</v>
       </c>
       <c r="J22">
-        <v>0.5534201536292217</v>
+        <v>0.5534201536291239</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2143,31 +2143,31 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.8934645520491271</v>
+        <v>0.8934645520491359</v>
       </c>
       <c r="C23">
-        <v>0.7311891672300027</v>
+        <v>0.7311891672300077</v>
       </c>
       <c r="D23">
-        <v>1.091754284041849</v>
+        <v>1.091754284041863</v>
       </c>
       <c r="E23">
-        <v>-0.1126486183099708</v>
+        <v>-0.112648618309961</v>
       </c>
       <c r="F23">
-        <v>-0.313083074009377</v>
+        <v>-0.3130830740093701</v>
       </c>
       <c r="G23">
-        <v>0.0877858373894355</v>
+        <v>0.08778583738944812</v>
       </c>
       <c r="H23">
-        <v>0.1022643565292055</v>
+        <v>0.102264356529207</v>
       </c>
       <c r="I23">
-        <v>-1.101543315121722</v>
+        <v>-1.10154331512161</v>
       </c>
       <c r="J23">
-        <v>0.2706602634917921</v>
+        <v>0.2706602634918409</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2223,31 +2223,31 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.099520907569097</v>
+        <v>1.099520907569056</v>
       </c>
       <c r="C24">
-        <v>0.7675176846235088</v>
+        <v>0.7675176846234822</v>
       </c>
       <c r="D24">
-        <v>1.575137941967549</v>
+        <v>1.575137941967484</v>
       </c>
       <c r="E24">
-        <v>0.09487454635630393</v>
+        <v>0.09487454635626617</v>
       </c>
       <c r="F24">
-        <v>-0.2645937579315097</v>
+        <v>-0.2645937579315443</v>
       </c>
       <c r="G24">
-        <v>0.4543428506441176</v>
+        <v>0.4543428506440768</v>
       </c>
       <c r="H24">
-        <v>0.1834055661855289</v>
+        <v>0.1834055661855273</v>
       </c>
       <c r="I24">
-        <v>0.5172937132144126</v>
+        <v>0.5172937132142114</v>
       </c>
       <c r="J24">
-        <v>0.6049511420007736</v>
+        <v>0.604951142000914</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2303,31 +2303,31 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.9170400063414285</v>
+        <v>0.9170400063414473</v>
       </c>
       <c r="C25">
-        <v>0.8032324113696342</v>
+        <v>0.8032324113696502</v>
       </c>
       <c r="D25">
-        <v>1.046972658631538</v>
+        <v>1.04697265863156</v>
       </c>
       <c r="E25">
-        <v>-0.08660418026027725</v>
+        <v>-0.08660418026025667</v>
       </c>
       <c r="F25">
-        <v>-0.2191111780579853</v>
+        <v>-0.2191111780579654</v>
       </c>
       <c r="G25">
-        <v>0.04590281753743053</v>
+        <v>0.04590281753745195</v>
       </c>
       <c r="H25">
-        <v>0.06760685341307608</v>
+        <v>0.06760685341307644</v>
       </c>
       <c r="I25">
-        <v>-1.280997057075383</v>
+        <v>-1.280997057075072</v>
       </c>
       <c r="J25">
-        <v>0.200194699784481</v>
+        <v>0.2001946997845904</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2383,31 +2383,31 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.9495766011110668</v>
+        <v>0.949576601111118</v>
       </c>
       <c r="C26">
-        <v>0.8384929212844265</v>
+        <v>0.8384929212844719</v>
       </c>
       <c r="D26">
-        <v>1.075376665072382</v>
+        <v>1.07537666507244</v>
       </c>
       <c r="E26">
-        <v>-0.05173907677473841</v>
+        <v>-0.05173907677468451</v>
       </c>
       <c r="F26">
-        <v>-0.1761491398720677</v>
+        <v>-0.1761491398720135</v>
       </c>
       <c r="G26">
-        <v>0.07267098632259107</v>
+        <v>0.07267098632264433</v>
       </c>
       <c r="H26">
-        <v>0.06347568836910275</v>
+        <v>0.06347568836910256</v>
       </c>
       <c r="I26">
-        <v>-0.8151006803405181</v>
+        <v>-0.8151006803396729</v>
       </c>
       <c r="J26">
-        <v>0.4150146822492942</v>
+        <v>0.4150146822497779</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2463,31 +2463,31 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.9246069331597488</v>
+        <v>0.9246069331597427</v>
       </c>
       <c r="C27">
-        <v>0.821278052850916</v>
+        <v>0.8212780528509102</v>
       </c>
       <c r="D27">
-        <v>1.040936109128273</v>
+        <v>1.040936109128266</v>
       </c>
       <c r="E27">
-        <v>-0.07838656890567297</v>
+        <v>-0.07838656890567958</v>
       </c>
       <c r="F27">
-        <v>-0.1968935510441361</v>
+        <v>-0.1968935510441432</v>
       </c>
       <c r="G27">
-        <v>0.04012041323279013</v>
+        <v>0.04012041323278416</v>
       </c>
       <c r="H27">
-        <v>0.0604638570265735</v>
+        <v>0.06046385702657379</v>
       </c>
       <c r="I27">
-        <v>-1.29642025435497</v>
+        <v>-1.296420254355072</v>
       </c>
       <c r="J27">
-        <v>0.1948307377386906</v>
+        <v>0.1948307377386552</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2543,31 +2543,31 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.009851050158681</v>
+        <v>1.009851050158642</v>
       </c>
       <c r="C28">
-        <v>0.8748160381135678</v>
+        <v>0.8748160381135346</v>
       </c>
       <c r="D28">
-        <v>1.165729820986891</v>
+        <v>1.165729820986845</v>
       </c>
       <c r="E28">
-        <v>0.009802844887232867</v>
+        <v>0.009802844887193948</v>
       </c>
       <c r="F28">
-        <v>-0.1337416568844254</v>
+        <v>-0.1337416568844634</v>
       </c>
       <c r="G28">
-        <v>0.1533473466588911</v>
+        <v>0.1533473466588511</v>
       </c>
       <c r="H28">
-        <v>0.07323833647144488</v>
+        <v>0.07323833647144436</v>
       </c>
       <c r="I28">
-        <v>0.1338485465334801</v>
+        <v>0.1338485465329491</v>
       </c>
       <c r="J28">
-        <v>0.8935223379652995</v>
+        <v>0.8935223379657193</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2623,31 +2623,31 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.9392955487939146</v>
+        <v>0.939295548793922</v>
       </c>
       <c r="C29">
-        <v>0.8275661048334905</v>
+        <v>0.8275661048334961</v>
       </c>
       <c r="D29">
-        <v>1.066109550440782</v>
+        <v>1.066109550440791</v>
       </c>
       <c r="E29">
-        <v>-0.06262510084745272</v>
+        <v>-0.06262510084744492</v>
       </c>
       <c r="F29">
-        <v>-0.1892662899264007</v>
+        <v>-0.1892662899263939</v>
       </c>
       <c r="G29">
-        <v>0.06401608823149528</v>
+        <v>0.06401608823150402</v>
       </c>
       <c r="H29">
-        <v>0.06461403886901881</v>
+        <v>0.06461403886901931</v>
       </c>
       <c r="I29">
-        <v>-0.9692181752390076</v>
+        <v>-0.96921817523888</v>
       </c>
       <c r="J29">
-        <v>0.332436344594548</v>
+        <v>0.3324363445946117</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2703,31 +2703,31 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.9744388441941962</v>
+        <v>0.9744388441942093</v>
       </c>
       <c r="C30">
-        <v>0.8510457294902374</v>
+        <v>0.8510457294902497</v>
       </c>
       <c r="D30">
-        <v>1.115722725784988</v>
+        <v>1.115722725785002</v>
       </c>
       <c r="E30">
-        <v>-0.02589351808976378</v>
+        <v>-0.02589351808975033</v>
       </c>
       <c r="F30">
-        <v>-0.1612894156712573</v>
+        <v>-0.1612894156712428</v>
       </c>
       <c r="G30">
-        <v>0.1095023794917297</v>
+        <v>0.1095023794917422</v>
       </c>
       <c r="H30">
-        <v>0.06908080895847016</v>
+        <v>0.0690808089584697</v>
       </c>
       <c r="I30">
-        <v>-0.3748293987890386</v>
+        <v>-0.3748293987888462</v>
       </c>
       <c r="J30">
-        <v>0.7077873485711905</v>
+        <v>0.7077873485713335</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2783,31 +2783,31 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.9319119188361791</v>
+        <v>0.9319119188361844</v>
       </c>
       <c r="C31">
-        <v>0.8305777809289547</v>
+        <v>0.8305777809289603</v>
       </c>
       <c r="D31">
-        <v>1.045609266717448</v>
+        <v>1.045609266717453</v>
       </c>
       <c r="E31">
-        <v>-0.0705169764491818</v>
+        <v>-0.07051697644917608</v>
       </c>
       <c r="F31">
-        <v>-0.1856336987706002</v>
+        <v>-0.1856336987705935</v>
       </c>
       <c r="G31">
-        <v>0.04459974587223666</v>
+        <v>0.04459974587224133</v>
       </c>
       <c r="H31">
-        <v>0.05873410084544636</v>
+        <v>0.05873410084544589</v>
       </c>
       <c r="I31">
-        <v>-1.20061387565532</v>
+        <v>-1.200613875655233</v>
       </c>
       <c r="J31">
-        <v>0.2299010160665712</v>
+        <v>0.2299010160666053</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2863,31 +2863,31 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.8868444456544349</v>
+        <v>0.8868444456544327</v>
       </c>
       <c r="C32">
-        <v>0.7918480362998163</v>
+        <v>0.7918480362998143</v>
       </c>
       <c r="D32">
-        <v>0.9932373823433126</v>
+        <v>0.9932373823433102</v>
       </c>
       <c r="E32">
-        <v>-0.1200856833546817</v>
+        <v>-0.1200856833546842</v>
       </c>
       <c r="F32">
-        <v>-0.2333857789365769</v>
+        <v>-0.2333857789365795</v>
       </c>
       <c r="G32">
-        <v>-0.006785587772786569</v>
+        <v>-0.006785587772789029</v>
       </c>
       <c r="H32">
-        <v>0.05780723343673245</v>
+        <v>0.05780723343673248</v>
       </c>
       <c r="I32">
-        <v>-2.07734700686049</v>
+        <v>-2.07734700686053</v>
       </c>
       <c r="J32">
-        <v>0.03776954345902901</v>
+        <v>0.03776954345902535</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2943,31 +2943,31 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.8892550211573946</v>
+        <v>0.8892550211573947</v>
       </c>
       <c r="C33">
-        <v>0.7949050830525713</v>
+        <v>0.7949050830525718</v>
       </c>
       <c r="D33">
-        <v>0.9948036684039423</v>
+        <v>0.994803668403942</v>
       </c>
       <c r="E33">
-        <v>-0.1173712216613389</v>
+        <v>-0.1173712216613388</v>
       </c>
       <c r="F33">
-        <v>-0.2295325638423462</v>
+        <v>-0.2295325638423456</v>
       </c>
       <c r="G33">
-        <v>-0.005209879480331611</v>
+        <v>-0.005209879480331946</v>
       </c>
       <c r="H33">
-        <v>0.05722622612748076</v>
+        <v>0.05722622612748052</v>
       </c>
       <c r="I33">
-        <v>-2.051004051881306</v>
+        <v>-2.051004051881313</v>
       </c>
       <c r="J33">
-        <v>0.04026655215845163</v>
+        <v>0.04026655215845092</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3023,31 +3023,31 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.9408822351378238</v>
+        <v>0.9408822351378301</v>
       </c>
       <c r="C34">
-        <v>0.8294610664234636</v>
+        <v>0.8294610664234701</v>
       </c>
       <c r="D34">
-        <v>1.067270564265396</v>
+        <v>1.067270564265402</v>
       </c>
       <c r="E34">
-        <v>-0.06093729585993146</v>
+        <v>-0.06093729585992474</v>
       </c>
       <c r="F34">
-        <v>-0.1869791066515318</v>
+        <v>-0.186979106651524</v>
       </c>
       <c r="G34">
-        <v>0.06510451493166883</v>
+        <v>0.06510451493167464</v>
       </c>
       <c r="H34">
-        <v>0.06430822800102558</v>
+        <v>0.06430822800102505</v>
       </c>
       <c r="I34">
-        <v>-0.9475816354162281</v>
+        <v>-0.9475816354161302</v>
       </c>
       <c r="J34">
-        <v>0.3433424789155365</v>
+        <v>0.3433424789155864</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3103,31 +3103,31 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.9166116470582912</v>
+        <v>0.916611647058292</v>
       </c>
       <c r="C35">
-        <v>0.8070535601931801</v>
+        <v>0.8070535601931819</v>
       </c>
       <c r="D35">
         <v>1.041042321059589</v>
       </c>
       <c r="E35">
-        <v>-0.08707140018194055</v>
+        <v>-0.08707140018193971</v>
       </c>
       <c r="F35">
-        <v>-0.2143652434062689</v>
+        <v>-0.2143652434062668</v>
       </c>
       <c r="G35">
-        <v>0.04022244304238757</v>
+        <v>0.04022244304238736</v>
       </c>
       <c r="H35">
-        <v>0.06494703179670949</v>
+        <v>0.0649470317967089</v>
       </c>
       <c r="I35">
-        <v>-1.340652494397012</v>
+        <v>-1.34065249439701</v>
       </c>
       <c r="J35">
-        <v>0.1800333051296845</v>
+        <v>0.1800333051296852</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3183,31 +3183,31 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.9332884679375856</v>
+        <v>0.9332884679375897</v>
       </c>
       <c r="C36">
-        <v>0.8327699370112021</v>
+        <v>0.8327699370112046</v>
       </c>
       <c r="D36">
-        <v>1.045939971742242</v>
+        <v>1.045939971742248</v>
       </c>
       <c r="E36">
-        <v>-0.06904094270922674</v>
+        <v>-0.06904094270922234</v>
       </c>
       <c r="F36">
-        <v>-0.1829978610226703</v>
+        <v>-0.1829978610226672</v>
       </c>
       <c r="G36">
-        <v>0.04491597560421674</v>
+        <v>0.04491597560422247</v>
       </c>
       <c r="H36">
-        <v>0.05814235323318242</v>
+        <v>0.05814235323318313</v>
       </c>
       <c r="I36">
-        <v>-1.187446652397007</v>
+        <v>-1.187446652396916</v>
       </c>
       <c r="J36">
-        <v>0.2350514874540256</v>
+        <v>0.2350514874540617</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3263,31 +3263,31 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.9131123879750846</v>
+        <v>0.913112387975085</v>
       </c>
       <c r="C37">
-        <v>0.8186336123494806</v>
+        <v>0.818633612349481</v>
       </c>
       <c r="D37">
-        <v>1.018494990305403</v>
+        <v>1.018494990305404</v>
       </c>
       <c r="E37">
-        <v>-0.09089630850949554</v>
+        <v>-0.09089630850949516</v>
       </c>
       <c r="F37">
-        <v>-0.2001186549929464</v>
+        <v>-0.200118654992946</v>
       </c>
       <c r="G37">
-        <v>0.01832603797395528</v>
+        <v>0.01832603797395572</v>
       </c>
       <c r="H37">
-        <v>0.05572671097274382</v>
+        <v>0.05572671097274381</v>
       </c>
       <c r="I37">
-        <v>-1.631108438356488</v>
+        <v>-1.631108438356481</v>
       </c>
       <c r="J37">
-        <v>0.1028674404614797</v>
+        <v>0.102867440461481</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3343,31 +3343,31 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.124742031865671</v>
+        <v>1.124742031865615</v>
       </c>
       <c r="C38">
-        <v>0.9555364707674747</v>
+        <v>0.9555364707674322</v>
       </c>
       <c r="D38">
-        <v>1.323910365482179</v>
+        <v>1.323910365482105</v>
       </c>
       <c r="E38">
-        <v>0.117553704353678</v>
+        <v>0.1175537043536281</v>
       </c>
       <c r="F38">
-        <v>-0.04548234672885215</v>
+        <v>-0.04548234672889666</v>
       </c>
       <c r="G38">
-        <v>0.2805897554362083</v>
+        <v>0.2805897554361527</v>
       </c>
       <c r="H38">
-        <v>0.08318318722616225</v>
+        <v>0.08318318722615939</v>
       </c>
       <c r="I38">
-        <v>1.413190673183365</v>
+        <v>1.413190673182811</v>
       </c>
       <c r="J38">
-        <v>0.1575996681498203</v>
+        <v>0.1575996681499831</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3423,31 +3423,31 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.9361323579687506</v>
+        <v>0.9361323579687542</v>
       </c>
       <c r="C39">
-        <v>0.8097132000490395</v>
+        <v>0.8097132000490441</v>
       </c>
       <c r="D39">
-        <v>1.082289126054828</v>
+        <v>1.08228912605483</v>
       </c>
       <c r="E39">
-        <v>-0.06599840441545397</v>
+        <v>-0.06599840441545018</v>
       </c>
       <c r="F39">
-        <v>-0.2110751680281882</v>
+        <v>-0.2110751680281824</v>
       </c>
       <c r="G39">
-        <v>0.07907835919728018</v>
+        <v>0.07907835919728202</v>
       </c>
       <c r="H39">
-        <v>0.07402011708229397</v>
+        <v>0.07402011708229302</v>
       </c>
       <c r="I39">
-        <v>-0.8916279386869707</v>
+        <v>-0.8916279386869305</v>
       </c>
       <c r="J39">
-        <v>0.3725923899043876</v>
+        <v>0.3725923899044091</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3503,31 +3503,31 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.17384400631166</v>
+        <v>1.173844006311655</v>
       </c>
       <c r="C40">
-        <v>0.9817397297025139</v>
+        <v>0.9817397297025148</v>
       </c>
       <c r="D40">
-        <v>1.403538748066497</v>
+        <v>1.403538748066485</v>
       </c>
       <c r="E40">
-        <v>0.1602838389076206</v>
+        <v>0.1602838389076168</v>
       </c>
       <c r="F40">
-        <v>-0.01842904679339048</v>
+        <v>-0.01842904679338957</v>
       </c>
       <c r="G40">
-        <v>0.3389967246086316</v>
+        <v>0.3389967246086233</v>
       </c>
       <c r="H40">
-        <v>0.09118171921049345</v>
+        <v>0.09118171921049112</v>
       </c>
       <c r="I40">
-        <v>1.757850589958767</v>
+        <v>1.757850589958772</v>
       </c>
       <c r="J40">
-        <v>0.07877293481622548</v>
+        <v>0.07877293481622485</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3583,31 +3583,31 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.9421871058040857</v>
+        <v>0.9421871058040547</v>
       </c>
       <c r="C41">
-        <v>0.8087206301254253</v>
+        <v>0.8087206301253982</v>
       </c>
       <c r="D41">
-        <v>1.097680100241542</v>
+        <v>1.097680100241506</v>
       </c>
       <c r="E41">
-        <v>-0.05955139801034291</v>
+        <v>-0.05955139801037579</v>
       </c>
       <c r="F41">
-        <v>-0.2123017489727433</v>
+        <v>-0.2123017489727768</v>
       </c>
       <c r="G41">
-        <v>0.0931989529520575</v>
+        <v>0.09319895295202535</v>
       </c>
       <c r="H41">
-        <v>0.07793528461098048</v>
+        <v>0.07793528461098084</v>
       </c>
       <c r="I41">
-        <v>-0.7641134347246947</v>
+        <v>-0.764113434725112</v>
       </c>
       <c r="J41">
-        <v>0.4447996468650712</v>
+        <v>0.4447996468648226</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3663,31 +3663,31 @@
         </is>
       </c>
       <c r="B42">
-        <v>1.142884923094827</v>
+        <v>1.142884923094843</v>
       </c>
       <c r="C42">
-        <v>0.9620808992155738</v>
+        <v>0.9620808992155919</v>
       </c>
       <c r="D42">
-        <v>1.357667477342558</v>
+        <v>1.357667477342571</v>
       </c>
       <c r="E42">
-        <v>0.1335557000370685</v>
+        <v>0.1335557000370825</v>
       </c>
       <c r="F42">
-        <v>-0.03865673703351779</v>
+        <v>-0.03865673703349898</v>
       </c>
       <c r="G42">
-        <v>0.3057681371076549</v>
+        <v>0.3057681371076642</v>
       </c>
       <c r="H42">
-        <v>0.08786510284320333</v>
+        <v>0.08786510284320088</v>
       </c>
       <c r="I42">
-        <v>1.520008464286451</v>
+        <v>1.520008464286652</v>
       </c>
       <c r="J42">
-        <v>0.1285088483285907</v>
+        <v>0.1285088483285407</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3743,31 +3743,31 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.9366153468433093</v>
+        <v>0.9366153468433017</v>
       </c>
       <c r="C43">
-        <v>0.8143433981794612</v>
+        <v>0.8143433981794549</v>
       </c>
       <c r="D43">
-        <v>1.07724617145983</v>
+        <v>1.077246171459821</v>
       </c>
       <c r="E43">
-        <v>-0.06548259667047457</v>
+        <v>-0.06548259667048263</v>
       </c>
       <c r="F43">
-        <v>-0.2053731368543201</v>
+        <v>-0.2053731368543279</v>
       </c>
       <c r="G43">
-        <v>0.07440794351337099</v>
+        <v>0.07440794351336275</v>
       </c>
       <c r="H43">
-        <v>0.07137403609825707</v>
+        <v>0.07137403609825696</v>
       </c>
       <c r="I43">
-        <v>-0.917456826741981</v>
+        <v>-0.9174568267420957</v>
       </c>
       <c r="J43">
-        <v>0.358903306409903</v>
+        <v>0.3589033064098429</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3823,31 +3823,31 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.9897328097240807</v>
+        <v>0.9897328097240939</v>
       </c>
       <c r="C44">
-        <v>0.8716634594009989</v>
+        <v>0.8716634594010123</v>
       </c>
       <c r="D44">
-        <v>1.123794996887306</v>
+        <v>1.123794996887318</v>
       </c>
       <c r="E44">
-        <v>-0.01032026144773231</v>
+        <v>-0.01032026144771896</v>
       </c>
       <c r="F44">
-        <v>-0.1373518706214739</v>
+        <v>-0.1373518706214585</v>
       </c>
       <c r="G44">
-        <v>0.1167113477260094</v>
+        <v>0.1167113477260207</v>
       </c>
       <c r="H44">
-        <v>0.06481323645523633</v>
+        <v>0.06481323645523526</v>
       </c>
       <c r="I44">
-        <v>-0.1592307684690305</v>
+        <v>-0.1592307684688272</v>
       </c>
       <c r="J44">
-        <v>0.8734870633738259</v>
+        <v>0.8734870633739861</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3903,31 +3903,31 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.8996293529752007</v>
+        <v>0.8996293529751991</v>
       </c>
       <c r="C45">
-        <v>0.7873443146709255</v>
+        <v>0.7873443146709224</v>
       </c>
       <c r="D45">
         <v>1.027927626648124</v>
       </c>
       <c r="E45">
-        <v>-0.1057724305106567</v>
+        <v>-0.1057724305106585</v>
       </c>
       <c r="F45">
-        <v>-0.2390896234826787</v>
+        <v>-0.2390896234826826</v>
       </c>
       <c r="G45">
         <v>0.02754476246136539</v>
       </c>
       <c r="H45">
-        <v>0.06802022589374657</v>
+        <v>0.06802022589374759</v>
       </c>
       <c r="I45">
-        <v>-1.555014396392659</v>
+        <v>-1.555014396392664</v>
       </c>
       <c r="J45">
-        <v>0.1199426406907853</v>
+        <v>0.1199426406907843</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3983,31 +3983,31 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.045815862408844</v>
+        <v>1.04581586240886</v>
       </c>
       <c r="C46">
-        <v>0.901807234553164</v>
+        <v>0.9018072345531774</v>
       </c>
       <c r="D46">
-        <v>1.212821073239544</v>
+        <v>1.212821073239563</v>
       </c>
       <c r="E46">
-        <v>0.04479731038381371</v>
+        <v>0.044797310383829</v>
       </c>
       <c r="F46">
-        <v>-0.103354490679623</v>
+        <v>-0.1033544906796083</v>
       </c>
       <c r="G46">
-        <v>0.1929491114472505</v>
+        <v>0.1929491114472662</v>
       </c>
       <c r="H46">
-        <v>0.07558904257018972</v>
+        <v>0.07558904257018997</v>
       </c>
       <c r="I46">
-        <v>0.5926429130547102</v>
+        <v>0.5926429130549098</v>
       </c>
       <c r="J46">
-        <v>0.5534201536292215</v>
+        <v>0.5534201536290878</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4063,31 +4063,31 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.9178971027838848</v>
+        <v>0.9178971027838962</v>
       </c>
       <c r="C47">
-        <v>0.78812257594289</v>
+        <v>0.7881225759428981</v>
       </c>
       <c r="D47">
-        <v>1.069040675926663</v>
+        <v>1.069040675926678</v>
       </c>
       <c r="E47">
-        <v>-0.0856699831147424</v>
+        <v>-0.08566998311472994</v>
       </c>
       <c r="F47">
-        <v>-0.2381016479943888</v>
+        <v>-0.2381016479943786</v>
       </c>
       <c r="G47">
-        <v>0.06676168176490414</v>
+        <v>0.06676168176491867</v>
       </c>
       <c r="H47">
-        <v>0.07777268668302482</v>
+        <v>0.07777268668302592</v>
       </c>
       <c r="I47">
-        <v>-1.101543315121725</v>
+        <v>-1.101543315121549</v>
       </c>
       <c r="J47">
-        <v>0.2706602634917908</v>
+        <v>0.2706602634918673</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4143,31 +4143,31 @@
         </is>
       </c>
       <c r="B48">
-        <v>1.034614485714549</v>
+        <v>1.034614485714529</v>
       </c>
       <c r="C48">
-        <v>0.9094616262497547</v>
+        <v>0.9094616262497385</v>
       </c>
       <c r="D48">
-        <v>1.176989884075024</v>
+        <v>1.176989884075</v>
       </c>
       <c r="E48">
-        <v>0.03402887975984786</v>
+        <v>0.03402887975982855</v>
       </c>
       <c r="F48">
-        <v>-0.09490247405288081</v>
+        <v>-0.09490247405289864</v>
       </c>
       <c r="G48">
-        <v>0.1629602335725763</v>
+        <v>0.1629602335725559</v>
       </c>
       <c r="H48">
-        <v>0.06578251173476793</v>
+        <v>0.06578251173476728</v>
       </c>
       <c r="I48">
-        <v>0.517293713214398</v>
+        <v>0.5172937132141114</v>
       </c>
       <c r="J48">
-        <v>0.6049511420007839</v>
+        <v>0.6049511420009839</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4223,31 +4223,31 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.9186131381833219</v>
+        <v>0.9186131381833419</v>
       </c>
       <c r="C49">
-        <v>0.8067231190677534</v>
+        <v>0.8067231190677707</v>
       </c>
       <c r="D49">
-        <v>1.046021959328699</v>
+        <v>1.046021959328722</v>
       </c>
       <c r="E49">
-        <v>-0.0848902047941572</v>
+        <v>-0.08489020479413545</v>
       </c>
       <c r="F49">
-        <v>-0.2147747686327659</v>
+        <v>-0.2147747686327444</v>
       </c>
       <c r="G49">
-        <v>0.04499435904445134</v>
+        <v>0.04499435904447363</v>
       </c>
       <c r="H49">
-        <v>0.06626885231724744</v>
+        <v>0.06626885231724765</v>
       </c>
       <c r="I49">
-        <v>-1.280997057075385</v>
+        <v>-1.280997057075051</v>
       </c>
       <c r="J49">
-        <v>0.2001946997844806</v>
+        <v>0.2001946997845979</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4303,31 +4303,31 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.9934794298591774</v>
+        <v>0.993479429859176</v>
       </c>
       <c r="C50">
-        <v>0.9867188718014238</v>
+        <v>0.9867188718014223</v>
       </c>
       <c r="D50">
-        <v>1.000286308248444</v>
+        <v>1.000286308248443</v>
       </c>
       <c r="E50">
-        <v>-0.006541921926123684</v>
+        <v>-0.006541921926125025</v>
       </c>
       <c r="F50">
-        <v>-0.01337011112230645</v>
+        <v>-0.01337011112230803</v>
       </c>
       <c r="G50">
-        <v>0.0002862672700592165</v>
+        <v>0.0002862672700578846</v>
       </c>
       <c r="H50">
-        <v>0.003483834014320002</v>
+        <v>0.003483834014320079</v>
       </c>
       <c r="I50">
-        <v>-1.877793803962425</v>
+        <v>-1.877793803962782</v>
       </c>
       <c r="J50">
-        <v>0.06040937822120501</v>
+        <v>0.06040937822115632</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4383,31 +4383,31 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.000541664902098</v>
+        <v>1.000541664902097</v>
       </c>
       <c r="C51">
-        <v>0.9966425464525559</v>
+        <v>0.9966425464525552</v>
       </c>
       <c r="D51">
-        <v>1.004456037692063</v>
+        <v>1.004456037692062</v>
       </c>
       <c r="E51">
-        <v>0.000541518254618117</v>
+        <v>0.0005415182546176731</v>
       </c>
       <c r="F51">
-        <v>-0.003363102442083921</v>
+        <v>-0.00336310244208459</v>
       </c>
       <c r="G51">
-        <v>0.004446138951320274</v>
+        <v>0.004446138951319832</v>
       </c>
       <c r="H51">
-        <v>0.001992190023643935</v>
+        <v>0.001992190023643964</v>
       </c>
       <c r="I51">
-        <v>0.2718205834740856</v>
+        <v>0.271820583473803</v>
       </c>
       <c r="J51">
-        <v>0.7857599775953503</v>
+        <v>0.7857599775955675</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4463,31 +4463,31 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.992051120944203</v>
+        <v>0.992051120944201</v>
       </c>
       <c r="C52">
-        <v>0.9850016966291842</v>
+        <v>0.985001696629182</v>
       </c>
       <c r="D52">
-        <v>0.9991509963227511</v>
+        <v>0.9991509963227494</v>
       </c>
       <c r="E52">
-        <v>-0.007980639815172445</v>
+        <v>-0.007980639815174459</v>
       </c>
       <c r="F52">
-        <v>-0.01511191534535472</v>
+        <v>-0.01511191534535697</v>
       </c>
       <c r="G52">
-        <v>-0.0008493642849902421</v>
+        <v>-0.0008493642849919089</v>
       </c>
       <c r="H52">
-        <v>0.003638472740536489</v>
+        <v>0.003638472740536637</v>
       </c>
       <c r="I52">
-        <v>-2.193403766987069</v>
+        <v>-2.193403766987514</v>
       </c>
       <c r="J52">
-        <v>0.02827830116427243</v>
+        <v>0.02827830116424045</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4543,31 +4543,31 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.7997794280112341</v>
+        <v>0.7997794280112126</v>
       </c>
       <c r="C53">
-        <v>0.4988558953638411</v>
+        <v>0.4988558953638328</v>
       </c>
       <c r="D53">
-        <v>1.282228273564753</v>
+        <v>1.282228273564705</v>
       </c>
       <c r="E53">
-        <v>-0.2234193043165318</v>
+        <v>-0.2234193043165587</v>
       </c>
       <c r="F53">
-        <v>-0.6954380117835792</v>
+        <v>-0.6954380117835958</v>
       </c>
       <c r="G53">
-        <v>0.2485994031505156</v>
+        <v>0.2485994031504784</v>
       </c>
       <c r="H53">
-        <v>0.2408302964698693</v>
+        <v>0.240830296469864</v>
       </c>
       <c r="I53">
-        <v>-0.9277043112575506</v>
+        <v>-0.9277043112576826</v>
       </c>
       <c r="J53">
-        <v>0.3535609715062375</v>
+        <v>0.353560971506169</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4623,31 +4623,31 @@
         </is>
       </c>
       <c r="B54">
-        <v>1.016515841850558</v>
+        <v>1.016515841850615</v>
       </c>
       <c r="C54">
-        <v>0.7992842728515895</v>
+        <v>0.7992842728516403</v>
       </c>
       <c r="D54">
-        <v>1.292787174513832</v>
+        <v>1.292787174513894</v>
       </c>
       <c r="E54">
-        <v>0.01638093866778365</v>
+        <v>0.01638093866783935</v>
       </c>
       <c r="F54">
-        <v>-0.2240386106958879</v>
+        <v>-0.2240386106958245</v>
       </c>
       <c r="G54">
-        <v>0.2568004880314551</v>
+        <v>0.2568004880315031</v>
       </c>
       <c r="H54">
-        <v>0.1226652893931064</v>
+        <v>0.1226652893931024</v>
       </c>
       <c r="I54">
-        <v>0.1335417602553196</v>
+        <v>0.1335417602557782</v>
       </c>
       <c r="J54">
-        <v>0.893764940098438</v>
+        <v>0.8937649400980754</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4703,31 +4703,31 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.7401636483022577</v>
+        <v>0.7401636483022348</v>
       </c>
       <c r="C55">
-        <v>0.4542055154297757</v>
+        <v>0.454205515429769</v>
       </c>
       <c r="D55">
-        <v>1.206154940126018</v>
+        <v>1.206154940125961</v>
       </c>
       <c r="E55">
-        <v>-0.3008839708787699</v>
+        <v>-0.3008839708788008</v>
       </c>
       <c r="F55">
-        <v>-0.7892055062100878</v>
+        <v>-0.7892055062101024</v>
       </c>
       <c r="G55">
-        <v>0.1874375644525481</v>
+        <v>0.187437564452501</v>
       </c>
       <c r="H55">
-        <v>0.2491482186321463</v>
+        <v>0.2491482186321381</v>
       </c>
       <c r="I55">
-        <v>-1.207650500295202</v>
+        <v>-1.207650500295366</v>
       </c>
       <c r="J55">
-        <v>0.227181725532624</v>
+        <v>0.2271817255325608</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4783,31 +4783,31 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.7647807904927398</v>
+        <v>0.7647807904926959</v>
       </c>
       <c r="C56">
-        <v>0.5129579956817398</v>
+        <v>0.5129579956816973</v>
       </c>
       <c r="D56">
-        <v>1.140229146305363</v>
+        <v>1.140229146305326</v>
       </c>
       <c r="E56">
-        <v>-0.268166034593935</v>
+        <v>-0.2681660345939925</v>
       </c>
       <c r="F56">
-        <v>-0.6675613169263886</v>
+        <v>-0.6675613169264716</v>
       </c>
       <c r="G56">
-        <v>0.1312292477385189</v>
+        <v>0.1312292477384866</v>
       </c>
       <c r="H56">
-        <v>0.2037768476782395</v>
+        <v>0.2037768476782524</v>
       </c>
       <c r="I56">
-        <v>-1.31597891345029</v>
+        <v>-1.315978913450489</v>
       </c>
       <c r="J56">
-        <v>0.1881811202340805</v>
+        <v>0.1881811202340138</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4863,31 +4863,31 @@
         </is>
       </c>
       <c r="B57">
-        <v>1.002066827640942</v>
+        <v>1.002066827641012</v>
       </c>
       <c r="C57">
-        <v>0.8034886082999183</v>
+        <v>0.8034886082999797</v>
       </c>
       <c r="D57">
-        <v>1.249722667733912</v>
+        <v>1.249722667733991</v>
       </c>
       <c r="E57">
-        <v>0.002064694691147758</v>
+        <v>0.002064694691217337</v>
       </c>
       <c r="F57">
-        <v>-0.2187922715031833</v>
+        <v>-0.2187922715031068</v>
       </c>
       <c r="G57">
-        <v>0.2229216608854788</v>
+        <v>0.2229216608855417</v>
       </c>
       <c r="H57">
-        <v>0.1126841962079011</v>
+        <v>0.1126841962078977</v>
       </c>
       <c r="I57">
-        <v>0.01832284171720452</v>
+        <v>0.01832284171782297</v>
       </c>
       <c r="J57">
-        <v>0.9853813054689791</v>
+        <v>0.9853813054684857</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4943,31 +4943,31 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.7066331760632824</v>
+        <v>0.7066331760632548</v>
       </c>
       <c r="C58">
-        <v>0.4654712438488985</v>
+        <v>0.4654712438488665</v>
       </c>
       <c r="D58">
-        <v>1.072741768931648</v>
+        <v>1.072741768931638</v>
       </c>
       <c r="E58">
-        <v>-0.3472435934705218</v>
+        <v>-0.3472435934705608</v>
       </c>
       <c r="F58">
-        <v>-0.7647049589338449</v>
+        <v>-0.7647049589339139</v>
       </c>
       <c r="G58">
-        <v>0.07021777199280119</v>
+        <v>0.07021777199279249</v>
       </c>
       <c r="H58">
-        <v>0.2129944064055285</v>
+        <v>0.2129944064055438</v>
       </c>
       <c r="I58">
-        <v>-1.630294425710838</v>
+        <v>-1.630294425710903</v>
       </c>
       <c r="J58">
-        <v>0.1030392851360556</v>
+        <v>0.1030392851360421</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5041,13 +5041,13 @@
         <v>0.0001031311890366878</v>
       </c>
       <c r="H59">
-        <v>0.001485755871342886</v>
+        <v>0.001485755871342851</v>
       </c>
       <c r="I59">
-        <v>-1.890550704050394</v>
+        <v>-1.890550704050445</v>
       </c>
       <c r="J59">
-        <v>0.05868434604012292</v>
+        <v>0.05868434604011617</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5103,31 +5103,31 @@
         </is>
       </c>
       <c r="B60">
-        <v>0.9998318524477749</v>
+        <v>0.9998318524477748</v>
       </c>
       <c r="C60">
-        <v>0.9974437410096419</v>
+        <v>0.9974437410096417</v>
       </c>
       <c r="D60">
         <v>1.002225681578051</v>
       </c>
       <c r="E60">
-        <v>-0.0001681616906096225</v>
+        <v>-0.0001681616906097336</v>
       </c>
       <c r="F60">
-        <v>-0.002559531798991676</v>
+        <v>-0.002559531798991898</v>
       </c>
       <c r="G60">
         <v>0.002223208417772404</v>
       </c>
       <c r="H60">
-        <v>0.001220109209783895</v>
+        <v>0.001220109209783911</v>
       </c>
       <c r="I60">
-        <v>-0.1378251137366648</v>
+        <v>-0.1378251137367968</v>
       </c>
       <c r="J60">
-        <v>0.8903786358790979</v>
+        <v>0.8903786358789937</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5183,31 +5183,31 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.9963614872570546</v>
+        <v>0.9963614872570548</v>
       </c>
       <c r="C61">
-        <v>0.9933123546970317</v>
+        <v>0.9933123546970318</v>
       </c>
       <c r="D61">
-        <v>0.9994199796214983</v>
+        <v>0.9994199796214984</v>
       </c>
       <c r="E61">
-        <v>-0.003645148230863684</v>
+        <v>-0.003645148230863573</v>
       </c>
       <c r="F61">
-        <v>-0.006710107806333368</v>
+        <v>-0.006710107806333256</v>
       </c>
       <c r="G61">
-        <v>-0.0005801886553939247</v>
+        <v>-0.0005801886553938137</v>
       </c>
       <c r="H61">
-        <v>0.001563783620334743</v>
+        <v>0.001563783620334728</v>
       </c>
       <c r="I61">
-        <v>-2.330979928081978</v>
+        <v>-2.330979928081923</v>
       </c>
       <c r="J61">
-        <v>0.01975441809784866</v>
+        <v>0.0197544180978515</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5263,31 +5263,31 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.7248329073224568</v>
+        <v>0.7248329073225136</v>
       </c>
       <c r="C62">
-        <v>0.4924432942386328</v>
+        <v>0.4924432942386952</v>
       </c>
       <c r="D62">
-        <v>1.066889832157873</v>
+        <v>1.066889832157906</v>
       </c>
       <c r="E62">
-        <v>-0.3218141233490472</v>
+        <v>-0.3218141233489688</v>
       </c>
       <c r="F62">
-        <v>-0.7083759636007119</v>
+        <v>-0.7083759636005852</v>
       </c>
       <c r="G62">
-        <v>0.06474771690261717</v>
+        <v>0.06474771690264776</v>
       </c>
       <c r="H62">
-        <v>0.1972290528299577</v>
+        <v>0.1972290528299331</v>
       </c>
       <c r="I62">
-        <v>-1.631677071564611</v>
+        <v>-1.631677071564416</v>
       </c>
       <c r="J62">
-        <v>0.1027475326619633</v>
+        <v>0.1027475326620048</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5343,31 +5343,31 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.9987480011686104</v>
+        <v>0.9987480011685663</v>
       </c>
       <c r="C63">
-        <v>0.7929146231752195</v>
+        <v>0.7929146231751938</v>
       </c>
       <c r="D63">
-        <v>1.258013839931245</v>
+        <v>1.258013839931176</v>
       </c>
       <c r="E63">
-        <v>-0.001252783236711219</v>
+        <v>-0.00125278323675535</v>
       </c>
       <c r="F63">
-        <v>-0.2320397262263262</v>
+        <v>-0.2320397262263587</v>
       </c>
       <c r="G63">
-        <v>0.2295341597529036</v>
+        <v>0.229534159752848</v>
       </c>
       <c r="H63">
-        <v>0.1177506039958045</v>
+        <v>0.1177506039957986</v>
       </c>
       <c r="I63">
-        <v>-0.01063929350847235</v>
+        <v>-0.01063929350884737</v>
       </c>
       <c r="J63">
-        <v>0.9915112321191083</v>
+        <v>0.9915112321188091</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5423,31 +5423,31 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.6830879795824009</v>
+        <v>0.6830879795824372</v>
       </c>
       <c r="C64">
-        <v>0.4569451261249047</v>
+        <v>0.4569451261249506</v>
       </c>
       <c r="D64">
-        <v>1.021149282862512</v>
+        <v>1.021149282862518</v>
       </c>
       <c r="E64">
-        <v>-0.3811316142628683</v>
+        <v>-0.3811316142628152</v>
       </c>
       <c r="F64">
-        <v>-0.7831919694223421</v>
+        <v>-0.7831919694222418</v>
       </c>
       <c r="G64">
-        <v>0.02092874089660555</v>
+        <v>0.02092874089661142</v>
       </c>
       <c r="H64">
-        <v>0.2051366036982693</v>
+        <v>0.2051366036982452</v>
       </c>
       <c r="I64">
-        <v>-1.857940549817555</v>
+        <v>-1.857940549817514</v>
       </c>
       <c r="J64">
-        <v>0.06317745716331929</v>
+        <v>0.06317745716332486</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5503,31 +5503,31 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.8678886852034716</v>
+        <v>0.8678886852034318</v>
       </c>
       <c r="C65">
-        <v>0.7013985172837164</v>
+        <v>0.7013985172836795</v>
       </c>
       <c r="D65">
-        <v>1.073898434831632</v>
+        <v>1.07389843483159</v>
       </c>
       <c r="E65">
-        <v>-0.141691815398748</v>
+        <v>-0.1416918153987939</v>
       </c>
       <c r="F65">
-        <v>-0.3546790552165366</v>
+        <v>-0.3546790552165892</v>
       </c>
       <c r="G65">
-        <v>0.07129542441904065</v>
+        <v>0.07129542441900157</v>
       </c>
       <c r="H65">
-        <v>0.1086689559082743</v>
+        <v>0.1086689559082777</v>
       </c>
       <c r="I65">
-        <v>-1.303884943169489</v>
+        <v>-1.303884943169871</v>
       </c>
       <c r="J65">
-        <v>0.1922728147301</v>
+        <v>0.1922728147299698</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5583,31 +5583,31 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.9815769945014058</v>
+        <v>0.9815769945014193</v>
       </c>
       <c r="C66">
-        <v>0.8392829489811737</v>
+        <v>0.8392829489811877</v>
       </c>
       <c r="D66">
-        <v>1.147995914016865</v>
+        <v>1.147995914016878</v>
       </c>
       <c r="E66">
-        <v>-0.01859482259458911</v>
+        <v>-0.01859482259457531</v>
       </c>
       <c r="F66">
-        <v>-0.1752073838614606</v>
+        <v>-0.1752073838614439</v>
       </c>
       <c r="G66">
-        <v>0.1380177386722823</v>
+        <v>0.1380177386722933</v>
       </c>
       <c r="H66">
-        <v>0.07990583628179468</v>
+        <v>0.07990583628179325</v>
       </c>
       <c r="I66">
-        <v>-0.2327091919670658</v>
+        <v>-0.2327091919668973</v>
       </c>
       <c r="J66">
-        <v>0.8159872309982419</v>
+        <v>0.8159872309983728</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5663,31 +5663,31 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.8222662277618924</v>
+        <v>0.8222662277618686</v>
       </c>
       <c r="C67">
-        <v>0.6571709476665661</v>
+        <v>0.6571709476665418</v>
       </c>
       <c r="D67">
-        <v>1.0288369437488</v>
+        <v>1.028836943748779</v>
       </c>
       <c r="E67">
-        <v>-0.1956910583073026</v>
+        <v>-0.1956910583073315</v>
       </c>
       <c r="F67">
-        <v>-0.419811100024745</v>
+        <v>-0.419811100024782</v>
       </c>
       <c r="G67">
-        <v>0.02842898341013991</v>
+        <v>0.02842898341011919</v>
       </c>
       <c r="H67">
-        <v>0.114349061250754</v>
+        <v>0.1143490612507582</v>
       </c>
       <c r="I67">
-        <v>-1.71134818394508</v>
+        <v>-1.71134818394527</v>
       </c>
       <c r="J67">
-        <v>0.08701685643615993</v>
+        <v>0.08701685643612486</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5743,31 +5743,31 @@
         </is>
       </c>
       <c r="B68">
-        <v>1.00606707258985</v>
+        <v>1.006067072589847</v>
       </c>
       <c r="C68">
-        <v>0.9968689683691948</v>
+        <v>0.9968689683691903</v>
       </c>
       <c r="D68">
-        <v>1.015350047665089</v>
+        <v>1.015350047665088</v>
       </c>
       <c r="E68">
-        <v>0.006048742009553862</v>
+        <v>0.006048742009551434</v>
       </c>
       <c r="F68">
-        <v>-0.003135943565970994</v>
+        <v>-0.00313594356597556</v>
       </c>
       <c r="G68">
-        <v>0.01523342758507876</v>
+        <v>0.01523342758507833</v>
       </c>
       <c r="H68">
-        <v>0.004686150178254553</v>
+        <v>0.004686150178255602</v>
       </c>
       <c r="I68">
-        <v>1.290769988043124</v>
+        <v>1.290769988042285</v>
       </c>
       <c r="J68">
-        <v>0.1967834475470139</v>
+        <v>0.1967834475473049</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5823,31 +5823,31 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.9974807752909531</v>
+        <v>0.9974807752909541</v>
       </c>
       <c r="C69">
-        <v>0.9924200050914116</v>
+        <v>0.9924200050914121</v>
       </c>
       <c r="D69">
-        <v>1.002567352502527</v>
+        <v>1.002567352502528</v>
       </c>
       <c r="E69">
-        <v>-0.002522403295118137</v>
+        <v>-0.002522403295117135</v>
       </c>
       <c r="F69">
-        <v>-0.007608869073217389</v>
+        <v>-0.007608869073216829</v>
       </c>
       <c r="G69">
-        <v>0.002564062482981211</v>
+        <v>0.00256406248298254</v>
       </c>
       <c r="H69">
-        <v>0.002595183288172982</v>
+        <v>0.002595183288173188</v>
       </c>
       <c r="I69">
-        <v>-0.9719557407037368</v>
+        <v>-0.9719557407032928</v>
       </c>
       <c r="J69">
-        <v>0.3310725675122333</v>
+        <v>0.3310725675124542</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5903,31 +5903,31 @@
         </is>
       </c>
       <c r="B70">
-        <v>1.001417136102431</v>
+        <v>1.001417136102428</v>
       </c>
       <c r="C70">
-        <v>0.9928973543537358</v>
+        <v>0.9928973543537305</v>
       </c>
       <c r="D70">
         <v>1.010010023777661</v>
       </c>
       <c r="E70">
-        <v>0.001416132912723313</v>
+        <v>0.001416132912720209</v>
       </c>
       <c r="F70">
-        <v>-0.007127989510811943</v>
+        <v>-0.00712798951081731</v>
       </c>
       <c r="G70">
-        <v>0.009960255336258326</v>
+        <v>0.009960255336257667</v>
       </c>
       <c r="H70">
-        <v>0.004359326238099336</v>
+        <v>0.004359326238100546</v>
       </c>
       <c r="I70">
-        <v>0.3248513268740076</v>
+        <v>0.3248513268732204</v>
       </c>
       <c r="J70">
-        <v>0.7452935961302187</v>
+        <v>0.7452935961308146</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5983,31 +5983,31 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.55459445920953</v>
+        <v>1.554594459209461</v>
       </c>
       <c r="C71">
-        <v>0.8806674587714096</v>
+        <v>0.880667458771364</v>
       </c>
       <c r="D71">
-        <v>2.744241209930156</v>
+        <v>2.744241209930056</v>
       </c>
       <c r="E71">
-        <v>0.4412147136815079</v>
+        <v>0.4412147136814638</v>
       </c>
       <c r="F71">
-        <v>-0.1270751831307467</v>
+        <v>-0.1270751831307985</v>
       </c>
       <c r="G71">
-        <v>1.009504610493762</v>
+        <v>1.009504610493726</v>
       </c>
       <c r="H71">
-        <v>0.2899491527879354</v>
+        <v>0.2899491527879393</v>
       </c>
       <c r="I71">
-        <v>1.521696854221215</v>
+        <v>1.521696854221043</v>
       </c>
       <c r="J71">
-        <v>0.1280850562093416</v>
+        <v>0.1280850562093849</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6063,31 +6063,31 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.8722706583012321</v>
+        <v>0.8722706583012381</v>
       </c>
       <c r="C72">
-        <v>0.6428776936289086</v>
+        <v>0.6428776936289061</v>
       </c>
       <c r="D72">
-        <v>1.183516100921768</v>
+        <v>1.183516100921788</v>
       </c>
       <c r="E72">
-        <v>-0.1366555152734064</v>
+        <v>-0.1366555152733996</v>
       </c>
       <c r="F72">
-        <v>-0.4418007849228095</v>
+        <v>-0.4418007849228133</v>
       </c>
       <c r="G72">
-        <v>0.1684897543759965</v>
+        <v>0.168489754376014</v>
       </c>
       <c r="H72">
-        <v>0.1556892228920276</v>
+        <v>0.1556892228920331</v>
       </c>
       <c r="I72">
-        <v>-0.8777455030922643</v>
+        <v>-0.8777455030921896</v>
       </c>
       <c r="J72">
-        <v>0.3800818448198391</v>
+        <v>0.3800818448198796</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6143,31 +6143,31 @@
         </is>
       </c>
       <c r="B73">
-        <v>1.199274017343537</v>
+        <v>1.199274017343454</v>
       </c>
       <c r="C73">
-        <v>0.6935133980681454</v>
+        <v>0.6935133980681155</v>
       </c>
       <c r="D73">
-        <v>2.073872217439096</v>
+        <v>2.073872217438899</v>
       </c>
       <c r="E73">
-        <v>0.1817163881693032</v>
+        <v>0.1817163881692339</v>
       </c>
       <c r="F73">
-        <v>-0.3659847199212304</v>
+        <v>-0.3659847199212735</v>
       </c>
       <c r="G73">
-        <v>0.7294174962598368</v>
+        <v>0.7294174962597414</v>
       </c>
       <c r="H73">
-        <v>0.2794444757203348</v>
+        <v>0.2794444757203214</v>
       </c>
       <c r="I73">
-        <v>0.6502772606289166</v>
+        <v>0.6502772606287004</v>
       </c>
       <c r="J73">
-        <v>0.515513142712127</v>
+        <v>0.5155131427122666</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6223,31 +6223,31 @@
         </is>
       </c>
       <c r="B74">
-        <v>1.449187722930896</v>
+        <v>1.449187722930992</v>
       </c>
       <c r="C74">
-        <v>0.876549561794553</v>
+        <v>0.8765495617945672</v>
       </c>
       <c r="D74">
-        <v>2.395922772460265</v>
+        <v>2.395922772460543</v>
       </c>
       <c r="E74">
-        <v>0.3710032083846949</v>
+        <v>0.3710032083847609</v>
       </c>
       <c r="F74">
-        <v>-0.1317620311030303</v>
+        <v>-0.1317620311030141</v>
       </c>
       <c r="G74">
-        <v>0.87376844787242</v>
+        <v>0.8737684478725362</v>
       </c>
       <c r="H74">
-        <v>0.2565175908605839</v>
+        <v>0.2565175908606093</v>
       </c>
       <c r="I74">
-        <v>1.446307082255164</v>
+        <v>1.446307082255278</v>
       </c>
       <c r="J74">
-        <v>0.1480910902040035</v>
+        <v>0.1480910902039715</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6303,31 +6303,31 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.8611924733738935</v>
+        <v>0.8611924733740343</v>
       </c>
       <c r="C75">
-        <v>0.6451140831016962</v>
+        <v>0.6451140831018081</v>
       </c>
       <c r="D75">
-        <v>1.1496454590326</v>
+        <v>1.149645459032776</v>
       </c>
       <c r="E75">
-        <v>-0.1494372532260175</v>
+        <v>-0.149437253225854</v>
       </c>
       <c r="F75">
-        <v>-0.4383281048006685</v>
+        <v>-0.438328104800495</v>
       </c>
       <c r="G75">
-        <v>0.1394535983486335</v>
+        <v>0.139453598348787</v>
       </c>
       <c r="H75">
-        <v>0.1473960000558099</v>
+        <v>0.1473960000558048</v>
       </c>
       <c r="I75">
-        <v>-1.013848769094376</v>
+        <v>-1.013848769093302</v>
       </c>
       <c r="J75">
-        <v>0.3106549201801448</v>
+        <v>0.3106549201806574</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6383,31 +6383,31 @@
         </is>
       </c>
       <c r="B76">
-        <v>1.11163860259182</v>
+        <v>1.111638602592027</v>
       </c>
       <c r="C76">
-        <v>0.6914733027571711</v>
+        <v>0.6914733027572656</v>
       </c>
       <c r="D76">
-        <v>1.787112210760588</v>
+        <v>1.787112210761009</v>
       </c>
       <c r="E76">
-        <v>0.1058351453359762</v>
+        <v>0.1058351453361621</v>
       </c>
       <c r="F76">
-        <v>-0.3689307363490553</v>
+        <v>-0.3689307363489187</v>
       </c>
       <c r="G76">
-        <v>0.5806010270210074</v>
+        <v>0.5806010270212428</v>
       </c>
       <c r="H76">
-        <v>0.2422319417244012</v>
+        <v>0.2422319417244264</v>
       </c>
       <c r="I76">
-        <v>0.4369165543675069</v>
+        <v>0.4369165543682296</v>
       </c>
       <c r="J76">
-        <v>0.6621718658478989</v>
+        <v>0.6621718658473749</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6466,28 +6466,28 @@
         <v>1.001803925163679</v>
       </c>
       <c r="C77">
-        <v>0.998194566827224</v>
+        <v>0.9981945668272232</v>
       </c>
       <c r="D77">
         <v>1.005426334530499</v>
       </c>
       <c r="E77">
-        <v>0.001802300044783096</v>
+        <v>0.001802300044782874</v>
       </c>
       <c r="F77">
-        <v>-0.001807064931563459</v>
+        <v>-0.001807064931564238</v>
       </c>
       <c r="G77">
-        <v>0.005411665021129638</v>
+        <v>0.00541166502112986</v>
       </c>
       <c r="H77">
-        <v>0.001841546581884549</v>
+        <v>0.001841546581884781</v>
       </c>
       <c r="I77">
-        <v>0.97868827349383</v>
+        <v>0.9786882734935641</v>
       </c>
       <c r="J77">
-        <v>0.3277340279230055</v>
+        <v>0.3277340279231369</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6543,31 +6543,31 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.9981407923935078</v>
+        <v>0.9981407923935086</v>
       </c>
       <c r="C78">
-        <v>0.99516625459228</v>
+        <v>0.9951662545922805</v>
       </c>
       <c r="D78">
-        <v>1.001124221045978</v>
+        <v>1.001124221045979</v>
       </c>
       <c r="E78">
-        <v>-0.001860938078157548</v>
+        <v>-0.00186093807815677</v>
       </c>
       <c r="F78">
-        <v>-0.004845465739038134</v>
+        <v>-0.004845465739037687</v>
       </c>
       <c r="G78">
-        <v>0.00112358958272319</v>
+        <v>0.001123589582724077</v>
       </c>
       <c r="H78">
-        <v>0.001522746175145153</v>
+        <v>0.00152274617514527</v>
       </c>
       <c r="I78">
-        <v>-1.222093418149694</v>
+        <v>-1.222093418149136</v>
       </c>
       <c r="J78">
-        <v>0.2216723018351153</v>
+        <v>0.2216723018353264</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6623,31 +6623,31 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.9989153807720859</v>
+        <v>0.9989153807720863</v>
       </c>
       <c r="C79">
-        <v>0.9957317984324562</v>
+        <v>0.9957317984324565</v>
       </c>
       <c r="D79">
-        <v>1.00210914175272</v>
+        <v>1.002109141752721</v>
       </c>
       <c r="E79">
-        <v>-0.001085207853010145</v>
+        <v>-0.0010852078530097</v>
       </c>
       <c r="F79">
-        <v>-0.004277336341825961</v>
+        <v>-0.004277336341825626</v>
       </c>
       <c r="G79">
-        <v>0.002106920635805809</v>
+        <v>0.002106920635806252</v>
       </c>
       <c r="H79">
-        <v>0.001628666911226418</v>
+        <v>0.001628666911226458</v>
       </c>
       <c r="I79">
-        <v>-0.666316633272154</v>
+        <v>-0.666316633271848</v>
       </c>
       <c r="J79">
-        <v>0.5052087361240269</v>
+        <v>0.5052087361242226</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6703,31 +6703,31 @@
         </is>
       </c>
       <c r="B80">
-        <v>1.221558009999678</v>
+        <v>1.221558009999896</v>
       </c>
       <c r="C80">
-        <v>0.773383261368304</v>
+        <v>0.7733832613684525</v>
       </c>
       <c r="D80">
-        <v>1.929449532117232</v>
+        <v>1.929449532117551</v>
       </c>
       <c r="E80">
-        <v>0.2001271013777548</v>
+        <v>0.2001271013779333</v>
       </c>
       <c r="F80">
-        <v>-0.2569805429597484</v>
+        <v>-0.2569805429595565</v>
       </c>
       <c r="G80">
-        <v>0.6572347457152583</v>
+        <v>0.6572347457154233</v>
       </c>
       <c r="H80">
-        <v>0.2332224714041229</v>
+        <v>0.233222471404116</v>
       </c>
       <c r="I80">
-        <v>0.8580952777529698</v>
+        <v>0.8580952777537603</v>
       </c>
       <c r="J80">
-        <v>0.3908398546949115</v>
+        <v>0.3908398546944751</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6783,31 +6783,31 @@
         </is>
       </c>
       <c r="B81">
-        <v>0.8633351285612002</v>
+        <v>0.8633351285612184</v>
       </c>
       <c r="C81">
-        <v>0.646818577025531</v>
+        <v>0.6468185770255536</v>
       </c>
       <c r="D81">
-        <v>1.152328598283849</v>
+        <v>1.152328598283858</v>
       </c>
       <c r="E81">
-        <v>-0.1469523335443077</v>
+        <v>-0.1469523335442866</v>
       </c>
       <c r="F81">
-        <v>-0.4356894302545151</v>
+        <v>-0.4356894302544802</v>
       </c>
       <c r="G81">
-        <v>0.1417847631658997</v>
+        <v>0.141784763165907</v>
       </c>
       <c r="H81">
-        <v>0.1473175522549031</v>
+        <v>0.147317552254896</v>
       </c>
       <c r="I81">
-        <v>-0.9975208744307439</v>
+        <v>-0.9975208744306482</v>
       </c>
       <c r="J81">
-        <v>0.318511746649183</v>
+        <v>0.3185117466492295</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6863,31 +6863,31 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.9642005826530335</v>
+        <v>0.9642005826532338</v>
       </c>
       <c r="C82">
-        <v>0.6267282281839046</v>
+        <v>0.6267282281840258</v>
       </c>
       <c r="D82">
-        <v>1.483390601828209</v>
+        <v>1.483390601828538</v>
       </c>
       <c r="E82">
-        <v>-0.03645593272430785</v>
+        <v>-0.03645593272410013</v>
       </c>
       <c r="F82">
-        <v>-0.4672422801874597</v>
+        <v>-0.4672422801872663</v>
       </c>
       <c r="G82">
-        <v>0.3943304147388438</v>
+        <v>0.394330414739066</v>
       </c>
       <c r="H82">
-        <v>0.2197929915351199</v>
+        <v>0.2197929915351272</v>
       </c>
       <c r="I82">
-        <v>-0.1658648552425874</v>
+        <v>-0.1658648552416364</v>
       </c>
       <c r="J82">
-        <v>0.8682633057877416</v>
+        <v>0.8682633057884901</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6943,31 +6943,31 @@
         </is>
       </c>
       <c r="B83">
-        <v>1.1890271547912</v>
+        <v>1.18902715479119</v>
       </c>
       <c r="C83">
-        <v>0.9193517298526421</v>
+        <v>0.9193517298526359</v>
       </c>
       <c r="D83">
-        <v>1.537807053517442</v>
+        <v>1.537807053517428</v>
       </c>
       <c r="E83">
-        <v>0.1731354557920083</v>
+        <v>0.173135455792</v>
       </c>
       <c r="F83">
-        <v>-0.08408649878005167</v>
+        <v>-0.08408649878005844</v>
       </c>
       <c r="G83">
-        <v>0.430357410364068</v>
+        <v>0.4303574103640586</v>
       </c>
       <c r="H83">
-        <v>0.131238102639127</v>
+        <v>0.1312381026391263</v>
       </c>
       <c r="I83">
-        <v>1.31924686741387</v>
+        <v>1.319246867413815</v>
       </c>
       <c r="J83">
-        <v>0.1870865944448657</v>
+        <v>0.1870865944448841</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7023,31 +7023,31 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.8838436018264756</v>
+        <v>0.8838436018264688</v>
       </c>
       <c r="C84">
-        <v>0.7251003765000708</v>
+        <v>0.7251003765000669</v>
       </c>
       <c r="D84">
-        <v>1.077339824673945</v>
+        <v>1.077339824673934</v>
       </c>
       <c r="E84">
-        <v>-0.123475153007636</v>
+        <v>-0.1234751530076437</v>
       </c>
       <c r="F84">
-        <v>-0.3214451833659016</v>
+        <v>-0.3214451833659069</v>
       </c>
       <c r="G84">
-        <v>0.0744948773506295</v>
+        <v>0.0744948773506196</v>
       </c>
       <c r="H84">
-        <v>0.1010069735565694</v>
+        <v>0.1010069735565682</v>
       </c>
       <c r="I84">
-        <v>-1.222441863763825</v>
+        <v>-1.222441863763914</v>
       </c>
       <c r="J84">
-        <v>0.2215405761367469</v>
+        <v>0.221540576136713</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7103,31 +7103,31 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.9854771309658066</v>
+        <v>0.9854771309657905</v>
       </c>
       <c r="C85">
-        <v>0.7799968273756749</v>
+        <v>0.7799968273756587</v>
       </c>
       <c r="D85">
-        <v>1.245088622891089</v>
+        <v>1.245088622891074</v>
       </c>
       <c r="E85">
-        <v>-0.01462935817276284</v>
+        <v>-0.01462935817277918</v>
       </c>
       <c r="F85">
-        <v>-0.2484654267738553</v>
+        <v>-0.2484654267738761</v>
       </c>
       <c r="G85">
-        <v>0.2192067104283295</v>
+        <v>0.2192067104283178</v>
       </c>
       <c r="H85">
-        <v>0.119306308914634</v>
+        <v>0.1193063089146363</v>
       </c>
       <c r="I85">
-        <v>-0.1226201556803708</v>
+        <v>-0.1226201556805051</v>
       </c>
       <c r="J85">
-        <v>0.9024078929664701</v>
+        <v>0.9024078929663637</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7183,31 +7183,31 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.7650164298018256</v>
+        <v>0.7650164298017781</v>
       </c>
       <c r="C86">
-        <v>0.5784303682804943</v>
+        <v>0.5784303682804557</v>
       </c>
       <c r="D86">
-        <v>1.011790130602081</v>
+        <v>1.011790130602023</v>
       </c>
       <c r="E86">
-        <v>-0.2678579685210943</v>
+        <v>-0.2678579685211564</v>
       </c>
       <c r="F86">
-        <v>-0.5474371055731025</v>
+        <v>-0.5474371055731693</v>
       </c>
       <c r="G86">
-        <v>0.01172116853091364</v>
+        <v>0.01172116853085636</v>
       </c>
       <c r="H86">
-        <v>0.1426450379993167</v>
+        <v>0.1426450379993191</v>
       </c>
       <c r="I86">
-        <v>-1.877793803962374</v>
+        <v>-1.877793803962778</v>
       </c>
       <c r="J86">
-        <v>0.06040937822121208</v>
+        <v>0.06040937822115692</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7263,31 +7263,31 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.02276314450941</v>
+        <v>1.022763144509395</v>
       </c>
       <c r="C87">
-        <v>0.8695446140350145</v>
+        <v>0.8695446140350003</v>
       </c>
       <c r="D87">
-        <v>1.202979620462181</v>
+        <v>1.202979620462165</v>
       </c>
       <c r="E87">
-        <v>0.02250792986838085</v>
+        <v>0.02250792986836609</v>
       </c>
       <c r="F87">
-        <v>-0.139785636515596</v>
+        <v>-0.1397856365156123</v>
       </c>
       <c r="G87">
-        <v>0.1848014962523579</v>
+        <v>0.1848014962523444</v>
       </c>
       <c r="H87">
-        <v>0.08280436154139968</v>
+        <v>0.0828043615414004</v>
       </c>
       <c r="I87">
-        <v>0.2718205834740681</v>
+        <v>0.2718205834738855</v>
       </c>
       <c r="J87">
-        <v>0.7857599775953636</v>
+        <v>0.7857599775955041</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7343,31 +7343,31 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.7274308196543935</v>
+        <v>0.7274308196543312</v>
       </c>
       <c r="C88">
-        <v>0.5473846829147747</v>
+        <v>0.5473846829147222</v>
       </c>
       <c r="D88">
-        <v>0.9666978523501173</v>
+        <v>0.9666978523500447</v>
       </c>
       <c r="E88">
-        <v>-0.3182363777167057</v>
+        <v>-0.3182363777167913</v>
       </c>
       <c r="F88">
-        <v>-0.6026034642891991</v>
+        <v>-0.6026034642892951</v>
       </c>
       <c r="G88">
-        <v>-0.03386929114421242</v>
+        <v>-0.03386929114428752</v>
       </c>
       <c r="H88">
-        <v>0.1450879142757442</v>
+        <v>0.1450879142757495</v>
       </c>
       <c r="I88">
-        <v>-2.19340376698701</v>
+        <v>-2.193403766987519</v>
       </c>
       <c r="J88">
-        <v>0.02827830116427677</v>
+        <v>0.02827830116424008</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7423,31 +7423,31 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.8543368443325563</v>
+        <v>0.8543368443325269</v>
       </c>
       <c r="C89">
-        <v>0.6126067601622384</v>
+        <v>0.6126067601622188</v>
       </c>
       <c r="D89">
-        <v>1.191451826928602</v>
+        <v>1.191451826928558</v>
       </c>
       <c r="E89">
-        <v>-0.1574297316583857</v>
+        <v>-0.1574297316584201</v>
       </c>
       <c r="F89">
-        <v>-0.4900320494464416</v>
+        <v>-0.4900320494464735</v>
       </c>
       <c r="G89">
-        <v>0.1751725861296703</v>
+        <v>0.1751725861296334</v>
       </c>
       <c r="H89">
-        <v>0.1696981783397964</v>
+        <v>0.1696981783397951</v>
       </c>
       <c r="I89">
-        <v>-0.9277043112575732</v>
+        <v>-0.9277043112577833</v>
       </c>
       <c r="J89">
-        <v>0.3535609715062257</v>
+        <v>0.3535609715061167</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7503,31 +7503,31 @@
         </is>
       </c>
       <c r="B90">
-        <v>1.011806552951649</v>
+        <v>1.011806552951692</v>
       </c>
       <c r="C90">
-        <v>0.8516923469426316</v>
+        <v>0.8516923469426735</v>
       </c>
       <c r="D90">
-        <v>1.202021486128085</v>
+        <v>1.202021486128129</v>
       </c>
       <c r="E90">
-        <v>0.01173739938333777</v>
+        <v>0.01173739938338034</v>
       </c>
       <c r="F90">
-        <v>-0.1605299125011255</v>
+        <v>-0.1605299125010763</v>
       </c>
       <c r="G90">
-        <v>0.184004711267801</v>
+        <v>0.1840047112678372</v>
       </c>
       <c r="H90">
-        <v>0.08789310071168953</v>
+        <v>0.08789310071168624</v>
       </c>
       <c r="I90">
-        <v>0.1335417602553269</v>
+        <v>0.1335417602558171</v>
       </c>
       <c r="J90">
-        <v>0.8937649400984322</v>
+        <v>0.8937649400980445</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7583,31 +7583,31 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.8146159312749522</v>
+        <v>0.8146159312749234</v>
       </c>
       <c r="C91">
-        <v>0.5840275660999614</v>
+        <v>0.584027566099945</v>
       </c>
       <c r="D91">
-        <v>1.136246221934971</v>
+        <v>1.136246221934923</v>
       </c>
       <c r="E91">
-        <v>-0.2050385267838218</v>
+        <v>-0.2050385267838572</v>
       </c>
       <c r="F91">
-        <v>-0.5378070950419387</v>
+        <v>-0.5378070950419668</v>
       </c>
       <c r="G91">
-        <v>0.1277300414742951</v>
+        <v>0.1277300414742527</v>
       </c>
       <c r="H91">
-        <v>0.1697830015668416</v>
+        <v>0.1697830015668379</v>
       </c>
       <c r="I91">
-        <v>-1.207650500295228</v>
+        <v>-1.207650500295463</v>
       </c>
       <c r="J91">
-        <v>0.2271817255326138</v>
+        <v>0.2271817255325235</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7663,31 +7663,31 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.8266609214846395</v>
+        <v>0.8266609214846141</v>
       </c>
       <c r="C92">
-        <v>0.622584500932633</v>
+        <v>0.6225845009326036</v>
       </c>
       <c r="D92">
-        <v>1.097631370659157</v>
+        <v>1.097631370659141</v>
       </c>
       <c r="E92">
-        <v>-0.1903606783323373</v>
+        <v>-0.190360678332368</v>
       </c>
       <c r="F92">
-        <v>-0.4738759153856282</v>
+        <v>-0.4738759153856753</v>
       </c>
       <c r="G92">
-        <v>0.0931545587209536</v>
+        <v>0.09315455872093903</v>
       </c>
       <c r="H92">
-        <v>0.1446532891877723</v>
+        <v>0.1446532891877806</v>
       </c>
       <c r="I92">
-        <v>-1.315978913450304</v>
+        <v>-1.315978913450441</v>
       </c>
       <c r="J92">
-        <v>0.188181120234076</v>
+        <v>0.1881811202340299</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7743,31 +7743,31 @@
         </is>
       </c>
       <c r="B93">
-        <v>1.001502445008739</v>
+        <v>1.001502445008788</v>
       </c>
       <c r="C93">
-        <v>0.8529177831638785</v>
+        <v>0.8529177831639237</v>
       </c>
       <c r="D93">
-        <v>1.175971667090644</v>
+        <v>1.175971667090695</v>
       </c>
       <c r="E93">
-        <v>0.001501317467474815</v>
+        <v>0.00150131746752337</v>
       </c>
       <c r="F93">
-        <v>-0.1590921216412572</v>
+        <v>-0.1590921216412041</v>
       </c>
       <c r="G93">
-        <v>0.1620947565762069</v>
+        <v>0.1620947565762507</v>
       </c>
       <c r="H93">
-        <v>0.08193693372708516</v>
+        <v>0.08193693372708276</v>
       </c>
       <c r="I93">
-        <v>0.01832284171720917</v>
+        <v>0.01832284171780118</v>
       </c>
       <c r="J93">
-        <v>0.9853813054689753</v>
+        <v>0.985381305468503</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7823,31 +7823,31 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.7876710552953002</v>
+        <v>0.7876710552952869</v>
       </c>
       <c r="C94">
-        <v>0.5911928620252238</v>
+        <v>0.5911928620252027</v>
       </c>
       <c r="D94">
-        <v>1.049447196004103</v>
+        <v>1.049447196004105</v>
       </c>
       <c r="E94">
-        <v>-0.2386747187962958</v>
+        <v>-0.2386747187963127</v>
       </c>
       <c r="F94">
-        <v>-0.5256129831266759</v>
+        <v>-0.5256129831267116</v>
       </c>
       <c r="G94">
-        <v>0.04826354553408421</v>
+        <v>0.04826354553408611</v>
       </c>
       <c r="H94">
-        <v>0.1463997637679633</v>
+        <v>0.146399763767973</v>
       </c>
       <c r="I94">
-        <v>-1.63029442571085</v>
+        <v>-1.630294425710857</v>
       </c>
       <c r="J94">
-        <v>0.1030392851360528</v>
+        <v>0.103039285136052</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7903,31 +7903,31 @@
         </is>
       </c>
       <c r="B95">
-        <v>0.8381146954177647</v>
+        <v>0.8381146954177654</v>
       </c>
       <c r="C95">
-        <v>0.6978963518778306</v>
+        <v>0.6978963518778343</v>
       </c>
       <c r="D95">
-        <v>1.006505107506532</v>
+        <v>1.006505107506529</v>
       </c>
       <c r="E95">
-        <v>-0.1766003198253376</v>
+        <v>-0.1766003198253368</v>
       </c>
       <c r="F95">
-        <v>-0.3596846802576474</v>
+        <v>-0.3596846802576422</v>
       </c>
       <c r="G95">
-        <v>0.006484040606972205</v>
+        <v>0.006484040606968455</v>
       </c>
       <c r="H95">
-        <v>0.09341210444500814</v>
+        <v>0.09341210444500583</v>
       </c>
       <c r="I95">
-        <v>-1.890550704050378</v>
+        <v>-1.890550704050417</v>
       </c>
       <c r="J95">
-        <v>0.05868434604012487</v>
+        <v>0.05868434604011988</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7983,31 +7983,31 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.989177480358411</v>
+        <v>0.9891774803583988</v>
       </c>
       <c r="C96">
-        <v>0.8473650015198414</v>
+        <v>0.8473650015198293</v>
       </c>
       <c r="D96">
-        <v>1.154723272607694</v>
+        <v>1.154723272607681</v>
       </c>
       <c r="E96">
-        <v>-0.01088150910310117</v>
+        <v>-0.01088150910311351</v>
       </c>
       <c r="F96">
-        <v>-0.1656237426576448</v>
+        <v>-0.1656237426576591</v>
       </c>
       <c r="G96">
-        <v>0.1438607244514424</v>
+        <v>0.1438607244514319</v>
       </c>
       <c r="H96">
-        <v>0.0789515699141059</v>
+        <v>0.07895156991410687</v>
       </c>
       <c r="I96">
-        <v>-0.1378251137366812</v>
+        <v>-0.1378251137368363</v>
       </c>
       <c r="J96">
-        <v>0.8903786358790848</v>
+        <v>0.8903786358789624</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -8063,31 +8063,31 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.7987662166310049</v>
+        <v>0.7987662166310111</v>
       </c>
       <c r="C97">
-        <v>0.6612580593477123</v>
+        <v>0.6612580593477188</v>
       </c>
       <c r="D97">
-        <v>0.9648691003636034</v>
+        <v>0.964869100363609</v>
       </c>
       <c r="E97">
-        <v>-0.2246869709850555</v>
+        <v>-0.2246869709850477</v>
       </c>
       <c r="F97">
-        <v>-0.4136111078344312</v>
+        <v>-0.4136111078344215</v>
       </c>
       <c r="G97">
-        <v>-0.03576283413567974</v>
+        <v>-0.03576283413567399</v>
       </c>
       <c r="H97">
-        <v>0.0963916369584264</v>
+        <v>0.09639163695842544</v>
       </c>
       <c r="I97">
-        <v>-2.330979928081963</v>
+        <v>-2.330979928081906</v>
       </c>
       <c r="J97">
-        <v>0.01975441809784941</v>
+        <v>0.01975441809785242</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -8143,31 +8143,31 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.7962091388972491</v>
+        <v>0.7962091388972883</v>
       </c>
       <c r="C98">
-        <v>0.605537962981414</v>
+        <v>0.6055379629814645</v>
       </c>
       <c r="D98">
-        <v>1.046918660131894</v>
+        <v>1.046918660131911</v>
       </c>
       <c r="E98">
-        <v>-0.2278933903390542</v>
+        <v>-0.227893390339005</v>
       </c>
       <c r="F98">
-        <v>-0.5016380210403809</v>
+        <v>-0.5016380210402976</v>
       </c>
       <c r="G98">
-        <v>0.04585124036227214</v>
+        <v>0.04585124036228762</v>
       </c>
       <c r="H98">
-        <v>0.1396681943446866</v>
+        <v>0.1396681943446693</v>
       </c>
       <c r="I98">
-        <v>-1.631677071564605</v>
+        <v>-1.631677071564454</v>
       </c>
       <c r="J98">
-        <v>0.1027475326619648</v>
+        <v>0.1027475326619963</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -8223,31 +8223,31 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.9990918868657405</v>
+        <v>0.9990918868657127</v>
       </c>
       <c r="C99">
-        <v>0.8451200722039003</v>
+        <v>0.8451200722038836</v>
       </c>
       <c r="D99">
-        <v>1.181115715069794</v>
+        <v>1.181115715069752</v>
       </c>
       <c r="E99">
-        <v>-0.0009085257187930444</v>
+        <v>-0.0009085257188208252</v>
       </c>
       <c r="F99">
-        <v>-0.1682765644371036</v>
+        <v>-0.1682765644371233</v>
       </c>
       <c r="G99">
-        <v>0.1664595129995175</v>
+        <v>0.1664595129994816</v>
       </c>
       <c r="H99">
-        <v>0.08539342561316857</v>
+        <v>0.08539342561316443</v>
       </c>
       <c r="I99">
-        <v>-0.01063929350847977</v>
+        <v>-0.01063929350880622</v>
       </c>
       <c r="J99">
-        <v>0.9915112321191025</v>
+        <v>0.9915112321188421</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -8303,31 +8303,31 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.7675928336404753</v>
+        <v>0.7675928336404981</v>
       </c>
       <c r="C100">
-        <v>0.5807030658706005</v>
+        <v>0.5807030658706368</v>
       </c>
       <c r="D100">
-        <v>1.014630011248308</v>
+        <v>1.014630011248305</v>
       </c>
       <c r="E100">
-        <v>-0.2644958509520025</v>
+        <v>-0.2644958509519727</v>
       </c>
       <c r="F100">
-        <v>-0.5435157270062213</v>
+        <v>-0.5435157270061588</v>
       </c>
       <c r="G100">
-        <v>0.01452402510221635</v>
+        <v>0.01452402510221351</v>
       </c>
       <c r="H100">
-        <v>0.1423596955123115</v>
+        <v>0.1423596955122949</v>
       </c>
       <c r="I100">
-        <v>-1.857940549817545</v>
+        <v>-1.857940549817553</v>
       </c>
       <c r="J100">
-        <v>0.06317745716332046</v>
+        <v>0.06317745716331907</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -8383,31 +8383,31 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.8730330107149061</v>
+        <v>0.8730330107148625</v>
       </c>
       <c r="C101">
-        <v>0.7118517932307076</v>
+        <v>0.7118517932306667</v>
       </c>
       <c r="D101">
-        <v>1.070709725038106</v>
+        <v>1.07070972503806</v>
       </c>
       <c r="E101">
-        <v>-0.1357819108964805</v>
+        <v>-0.1357819108965305</v>
       </c>
       <c r="F101">
-        <v>-0.3398855448123887</v>
+        <v>-0.3398855448124461</v>
       </c>
       <c r="G101">
-        <v>0.06832172301942763</v>
+        <v>0.06832172301938511</v>
       </c>
       <c r="H101">
-        <v>0.1041364206311196</v>
+        <v>0.1041364206311234</v>
       </c>
       <c r="I101">
-        <v>-1.303884943169481</v>
+        <v>-1.303884943169914</v>
       </c>
       <c r="J101">
-        <v>0.1922728147301029</v>
+        <v>0.1922728147299552</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -8463,31 +8463,31 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.9818855594631384</v>
+        <v>0.981885559463166</v>
       </c>
       <c r="C102">
-        <v>0.8417721845345669</v>
+        <v>0.8417721845345928</v>
       </c>
       <c r="D102">
-        <v>1.145320871365345</v>
+        <v>1.145320871365374</v>
       </c>
       <c r="E102">
-        <v>-0.01828051564368772</v>
+        <v>-0.01828051564365956</v>
       </c>
       <c r="F102">
-        <v>-0.172245866034826</v>
+        <v>-0.1722458660347953</v>
       </c>
       <c r="G102">
-        <v>0.1356848347474506</v>
+        <v>0.135684834747476</v>
       </c>
       <c r="H102">
-        <v>0.07855519366967829</v>
+        <v>0.07855519366967699</v>
       </c>
       <c r="I102">
-        <v>-0.2327091919670725</v>
+        <v>-0.2327091919667184</v>
       </c>
       <c r="J102">
-        <v>0.8159872309982368</v>
+        <v>0.8159872309985117</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -8543,31 +8543,31 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.834018362417584</v>
+        <v>0.834018362417555</v>
       </c>
       <c r="C103">
-        <v>0.677485533843916</v>
+        <v>0.6774855338438867</v>
       </c>
       <c r="D103">
-        <v>1.026718053894214</v>
+        <v>1.026718053894188</v>
       </c>
       <c r="E103">
-        <v>-0.1814998595784962</v>
+        <v>-0.181499859578531</v>
       </c>
       <c r="F103">
-        <v>-0.3893670787161465</v>
+        <v>-0.3893670787161898</v>
       </c>
       <c r="G103">
-        <v>0.02636735955915383</v>
+        <v>0.02636735955912788</v>
       </c>
       <c r="H103">
-        <v>0.1060566524575351</v>
+        <v>0.1060566524575395</v>
       </c>
       <c r="I103">
-        <v>-1.711348183945072</v>
+        <v>-1.711348183945328</v>
       </c>
       <c r="J103">
-        <v>0.08701685643616117</v>
+        <v>0.08701685643611427</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -8623,31 +8623,31 @@
         </is>
       </c>
       <c r="B104">
-        <v>1.281030451237831</v>
+        <v>1.28103045123808</v>
       </c>
       <c r="C104">
-        <v>0.8795008766142652</v>
+        <v>0.8795008766144096</v>
       </c>
       <c r="D104">
-        <v>1.865875362530574</v>
+        <v>1.865875362530995</v>
       </c>
       <c r="E104">
-        <v>0.247664794090164</v>
+        <v>0.247664794090359</v>
       </c>
       <c r="F104">
-        <v>-0.1284007180861292</v>
+        <v>-0.1284007180859651</v>
       </c>
       <c r="G104">
-        <v>0.6237303062664574</v>
+        <v>0.623730306266683</v>
       </c>
       <c r="H104">
-        <v>0.1918736849976072</v>
+        <v>0.1918736849976229</v>
       </c>
       <c r="I104">
-        <v>1.290769988043189</v>
+        <v>1.290769988044099</v>
       </c>
       <c r="J104">
-        <v>0.1967834475469913</v>
+        <v>0.1967834475466755</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -8703,31 +8703,31 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.9004664199102392</v>
+        <v>0.9004664199101355</v>
       </c>
       <c r="C105">
-        <v>0.7288708234799756</v>
+        <v>0.7288708234798871</v>
       </c>
       <c r="D105">
-        <v>1.112460188095648</v>
+        <v>1.112460188095526</v>
       </c>
       <c r="E105">
-        <v>-0.1048424055553383</v>
+        <v>-0.1048424055554534</v>
       </c>
       <c r="F105">
-        <v>-0.316258759547161</v>
+        <v>-0.3162587595472824</v>
       </c>
       <c r="G105">
-        <v>0.1065739484364845</v>
+        <v>0.1065739484363755</v>
       </c>
       <c r="H105">
-        <v>0.1078674688205743</v>
+        <v>0.1078674688205775</v>
       </c>
       <c r="I105">
-        <v>-0.9719557407037349</v>
+        <v>-0.971955740704774</v>
       </c>
       <c r="J105">
-        <v>0.3310725675122342</v>
+        <v>0.3310725675117173</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8783,31 +8783,31 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.058094643190106</v>
+        <v>1.058094643190241</v>
       </c>
       <c r="C106">
-        <v>0.7525889727726252</v>
+        <v>0.7525889727727081</v>
       </c>
       <c r="D106">
-        <v>1.487617164815732</v>
+        <v>1.487617164815948</v>
       </c>
       <c r="E106">
-        <v>0.05646978424632862</v>
+        <v>0.05646978424645621</v>
       </c>
       <c r="F106">
-        <v>-0.2842360531057687</v>
+        <v>-0.2842360531056585</v>
       </c>
       <c r="G106">
-        <v>0.3971756215984258</v>
+        <v>0.3971756215985709</v>
       </c>
       <c r="H106">
-        <v>0.1738327030698225</v>
+        <v>0.1738327030698314</v>
       </c>
       <c r="I106">
-        <v>0.3248513268740157</v>
+        <v>0.3248513268747332</v>
       </c>
       <c r="J106">
-        <v>0.7452935961302125</v>
+        <v>0.7452935961296695</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8863,31 +8863,31 @@
         </is>
       </c>
       <c r="B107">
-        <v>1.364648181914232</v>
+        <v>1.364648181914058</v>
       </c>
       <c r="C107">
-        <v>0.9143498590305762</v>
+        <v>0.9143498590305716</v>
       </c>
       <c r="D107">
-        <v>2.036709080237901</v>
+        <v>2.036709080237392</v>
       </c>
       <c r="E107">
-        <v>0.3108966532283213</v>
+        <v>0.3108966532281939</v>
       </c>
       <c r="F107">
-        <v>-0.08954200283597387</v>
+        <v>-0.08954200283597885</v>
       </c>
       <c r="G107">
-        <v>0.7113353092926167</v>
+        <v>0.7113353092923665</v>
       </c>
       <c r="H107">
-        <v>0.2043091909968267</v>
+        <v>0.2043091909967642</v>
       </c>
       <c r="I107">
-        <v>1.521696854221062</v>
+        <v>1.521696854220904</v>
       </c>
       <c r="J107">
-        <v>0.1280850562093793</v>
+        <v>0.1280850562094186</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8943,31 +8943,31 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.9067237165166034</v>
+        <v>0.9067237165166969</v>
       </c>
       <c r="C108">
-        <v>0.7286494088945964</v>
+        <v>0.7286494088946953</v>
       </c>
       <c r="D108">
-        <v>1.128317525627212</v>
+        <v>1.128317525627292</v>
       </c>
       <c r="E108">
-        <v>-0.09791748771114256</v>
+        <v>-0.09791748771103946</v>
       </c>
       <c r="F108">
-        <v>-0.3165625832364167</v>
+        <v>-0.3165625832362809</v>
       </c>
       <c r="G108">
-        <v>0.1207276078141315</v>
+        <v>0.1207276078142022</v>
       </c>
       <c r="H108">
-        <v>0.1115556700275713</v>
+        <v>0.1115556700275547</v>
       </c>
       <c r="I108">
-        <v>-0.8777455030922408</v>
+        <v>-0.8777455030914471</v>
       </c>
       <c r="J108">
-        <v>0.3800818448198519</v>
+        <v>0.3800818448202827</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -9023,31 +9023,31 @@
         </is>
       </c>
       <c r="B109">
-        <v>1.131824943337541</v>
+        <v>1.131824943337507</v>
       </c>
       <c r="C109">
-        <v>0.7792668946465979</v>
+        <v>0.7792668946466561</v>
       </c>
       <c r="D109">
-        <v>1.643888263650648</v>
+        <v>1.643888263650427</v>
       </c>
       <c r="E109">
-        <v>0.1238313241276707</v>
+        <v>0.1238313241276407</v>
       </c>
       <c r="F109">
-        <v>-0.2494016799196029</v>
+        <v>-0.2494016799195282</v>
       </c>
       <c r="G109">
-        <v>0.4970643281749442</v>
+        <v>0.4970643281748095</v>
       </c>
       <c r="H109">
-        <v>0.1904285012333328</v>
+        <v>0.1904285012332794</v>
       </c>
       <c r="I109">
-        <v>0.6502772606288575</v>
+        <v>0.6502772606288822</v>
       </c>
       <c r="J109">
-        <v>0.5155131427121651</v>
+        <v>0.5155131427121491</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -9103,31 +9103,31 @@
         </is>
       </c>
       <c r="B110">
-        <v>1.301296146802599</v>
+        <v>1.301296146802622</v>
       </c>
       <c r="C110">
-        <v>0.9107081812361618</v>
+        <v>0.9107081812361413</v>
       </c>
       <c r="D110">
-        <v>1.85940095474356</v>
+        <v>1.859400954743669</v>
       </c>
       <c r="E110">
-        <v>0.2633608037592265</v>
+        <v>0.2633608037592448</v>
       </c>
       <c r="F110">
-        <v>-0.09353276098965971</v>
+        <v>-0.09353276098968226</v>
       </c>
       <c r="G110">
-        <v>0.6202543685081128</v>
+        <v>0.6202543685081718</v>
       </c>
       <c r="H110">
-        <v>0.1820918994246921</v>
+        <v>0.1820918994247129</v>
       </c>
       <c r="I110">
-        <v>1.44630708225516</v>
+        <v>1.446307082255095</v>
       </c>
       <c r="J110">
-        <v>0.1480910902040046</v>
+        <v>0.1480910902040223</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -9183,31 +9183,31 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.8970340397667041</v>
+        <v>0.8970340397668227</v>
       </c>
       <c r="C111">
-        <v>0.727075529270888</v>
+        <v>0.7270755292709925</v>
       </c>
       <c r="D111">
-        <v>1.106721428662435</v>
+        <v>1.106721428662568</v>
       </c>
       <c r="E111">
-        <v>-0.1086614691855013</v>
+        <v>-0.1086614691853691</v>
       </c>
       <c r="F111">
-        <v>-0.3187249151381262</v>
+        <v>-0.3187249151379825</v>
       </c>
       <c r="G111">
-        <v>0.1014019767671236</v>
+        <v>0.1014019767672443</v>
       </c>
       <c r="H111">
-        <v>0.107177196932994</v>
+        <v>0.1071771969329881</v>
       </c>
       <c r="I111">
-        <v>-1.013848769094374</v>
+        <v>-1.013848769093196</v>
       </c>
       <c r="J111">
-        <v>0.3106549201801459</v>
+        <v>0.3106549201807082</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -9263,31 +9263,31 @@
         </is>
       </c>
       <c r="B112">
-        <v>1.07545606964581</v>
+        <v>1.075456069645927</v>
       </c>
       <c r="C112">
-        <v>0.7760167462812669</v>
+        <v>0.7760167462813203</v>
       </c>
       <c r="D112">
-        <v>1.490439173227328</v>
+        <v>1.490439173227551</v>
       </c>
       <c r="E112">
-        <v>0.0727448224439981</v>
+        <v>0.07274482244410732</v>
       </c>
       <c r="F112">
-        <v>-0.2535811787724042</v>
+        <v>-0.2535811787723353</v>
       </c>
       <c r="G112">
-        <v>0.3990708236604004</v>
+        <v>0.39907082366055</v>
       </c>
       <c r="H112">
-        <v>0.1664959171650195</v>
+        <v>0.1664959171650401</v>
       </c>
       <c r="I112">
-        <v>0.436916554367507</v>
+        <v>0.4369165543681085</v>
       </c>
       <c r="J112">
-        <v>0.6621718658478989</v>
+        <v>0.6621718658474625</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -9343,31 +9343,31 @@
         </is>
       </c>
       <c r="B113">
-        <v>1.119983325844153</v>
+        <v>1.119983325844139</v>
       </c>
       <c r="C113">
-        <v>0.8926029923166406</v>
+        <v>0.8926029923166039</v>
       </c>
       <c r="D113">
-        <v>1.405286180940742</v>
+        <v>1.405286180940765</v>
       </c>
       <c r="E113">
-        <v>0.113313797557032</v>
+        <v>0.1133137975570197</v>
       </c>
       <c r="F113">
-        <v>-0.1136133744324694</v>
+        <v>-0.1136133744325106</v>
       </c>
       <c r="G113">
-        <v>0.3402409695465335</v>
+        <v>0.3402409695465503</v>
       </c>
       <c r="H113">
-        <v>0.1157812968908991</v>
+        <v>0.1157812968909138</v>
       </c>
       <c r="I113">
-        <v>0.978688273493843</v>
+        <v>0.9786882734936123</v>
       </c>
       <c r="J113">
-        <v>0.327734027922999</v>
+        <v>0.327734027923113</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -9423,31 +9423,31 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.8865491478680815</v>
+        <v>0.8865491478681167</v>
       </c>
       <c r="C114">
-        <v>0.7308526970142354</v>
+        <v>0.7308526970142527</v>
       </c>
       <c r="D114">
-        <v>1.075414231618157</v>
+        <v>1.075414231618216</v>
       </c>
       <c r="E114">
-        <v>-0.1204187146571081</v>
+        <v>-0.1204187146570684</v>
       </c>
       <c r="F114">
-        <v>-0.3135433484104543</v>
+        <v>-0.3135433484104306</v>
       </c>
       <c r="G114">
-        <v>0.07270591909623797</v>
+        <v>0.07270591909629372</v>
       </c>
       <c r="H114">
-        <v>0.0985347870046025</v>
+        <v>0.09853478700461066</v>
       </c>
       <c r="I114">
-        <v>-1.222093418149708</v>
+        <v>-1.222093418149204</v>
       </c>
       <c r="J114">
-        <v>0.2216723018351101</v>
+        <v>0.2216723018353007</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -9503,31 +9503,31 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.9352960000573777</v>
+        <v>0.9352960000574054</v>
       </c>
       <c r="C115">
-        <v>0.7682384962522797</v>
+        <v>0.7682384962523002</v>
       </c>
       <c r="D115">
-        <v>1.138681037191951</v>
+        <v>1.138681037191988</v>
       </c>
       <c r="E115">
-        <v>-0.06689222219209204</v>
+        <v>-0.06689222219206237</v>
       </c>
       <c r="F115">
-        <v>-0.2636550520474942</v>
+        <v>-0.2636550520474675</v>
       </c>
       <c r="G115">
-        <v>0.1298706076633103</v>
+        <v>0.1298706076633429</v>
       </c>
       <c r="H115">
-        <v>0.1003910436148023</v>
+        <v>0.1003910436148038</v>
       </c>
       <c r="I115">
-        <v>-0.6663166332721437</v>
+        <v>-0.6663166332718379</v>
       </c>
       <c r="J115">
-        <v>0.5052087361240335</v>
+        <v>0.5052087361242289</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -9583,31 +9583,31 @@
         </is>
       </c>
       <c r="B116">
-        <v>1.152254495257689</v>
+        <v>1.15225449525784</v>
       </c>
       <c r="C116">
-        <v>0.8336168909295558</v>
+        <v>0.8336168909296718</v>
       </c>
       <c r="D116">
-        <v>1.592686564161459</v>
+        <v>1.592686564161654</v>
       </c>
       <c r="E116">
-        <v>0.141720453897648</v>
+        <v>0.1417204538977788</v>
       </c>
       <c r="F116">
-        <v>-0.181981345556894</v>
+        <v>-0.1819813455567548</v>
       </c>
       <c r="G116">
-        <v>0.4654222533521901</v>
+        <v>0.4654222533523125</v>
       </c>
       <c r="H116">
-        <v>0.165157014112433</v>
+        <v>0.1651570141124287</v>
       </c>
       <c r="I116">
-        <v>0.8580952777529013</v>
+        <v>0.8580952777537151</v>
       </c>
       <c r="J116">
-        <v>0.3908398546949494</v>
+        <v>0.3908398546945</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -9663,31 +9663,31 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.8989115014989303</v>
+        <v>0.8989115014989399</v>
       </c>
       <c r="C117">
-        <v>0.7290853183886721</v>
+        <v>0.7290853183886858</v>
       </c>
       <c r="D117">
-        <v>1.108295376613657</v>
+        <v>1.10829537661366</v>
       </c>
       <c r="E117">
-        <v>-0.1065706904029508</v>
+        <v>-0.10657069040294</v>
       </c>
       <c r="F117">
-        <v>-0.3159645189948093</v>
+        <v>-0.3159645189947904</v>
       </c>
       <c r="G117">
-        <v>0.1028231381889077</v>
+        <v>0.1028231381889103</v>
       </c>
       <c r="H117">
-        <v>0.1068355491445406</v>
+        <v>0.1068355491445365</v>
       </c>
       <c r="I117">
-        <v>-0.9975208744307426</v>
+        <v>-0.9975208744306808</v>
       </c>
       <c r="J117">
-        <v>0.3185117466491837</v>
+        <v>0.3185117466492136</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -9743,31 +9743,31 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.9750178410514264</v>
+        <v>0.975017841051569</v>
       </c>
       <c r="C118">
-        <v>0.7230661920079309</v>
+        <v>0.7230661920080294</v>
       </c>
       <c r="D118">
-        <v>1.314761775444975</v>
+        <v>1.314761775445181</v>
       </c>
       <c r="E118">
-        <v>-0.02529950963742214</v>
+        <v>-0.02529950963727594</v>
       </c>
       <c r="F118">
-        <v>-0.3242545091358005</v>
+        <v>-0.3242545091356643</v>
       </c>
       <c r="G118">
-        <v>0.2736554898609563</v>
+        <v>0.2736554898611125</v>
       </c>
       <c r="H118">
-        <v>0.1525308637589758</v>
+        <v>0.152530863758981</v>
       </c>
       <c r="I118">
-        <v>-0.1658648552426712</v>
+        <v>-0.165864855241707</v>
       </c>
       <c r="J118">
-        <v>0.8682633057876756</v>
+        <v>0.8682633057884345</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -9823,31 +9823,31 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.180471636548174</v>
+        <v>1.180471636548168</v>
       </c>
       <c r="C119">
-        <v>0.9225817517726546</v>
+        <v>0.9225817517726481</v>
       </c>
       <c r="D119">
-        <v>1.510449650686478</v>
+        <v>1.510449650686472</v>
       </c>
       <c r="E119">
-        <v>0.165914050611986</v>
+        <v>0.1659140506119806</v>
       </c>
       <c r="F119">
-        <v>-0.08057928718620237</v>
+        <v>-0.08057928718620935</v>
       </c>
       <c r="G119">
-        <v>0.4124073884101745</v>
+        <v>0.4124073884101704</v>
       </c>
       <c r="H119">
-        <v>0.1257642179869103</v>
+        <v>0.125764217986911</v>
       </c>
       <c r="I119">
-        <v>1.319246867413867</v>
+        <v>1.319246867413816</v>
       </c>
       <c r="J119">
-        <v>0.1870865944448666</v>
+        <v>0.1870865944448838</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -9903,31 +9903,31 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.8856901907520733</v>
+        <v>0.8856901907520637</v>
       </c>
       <c r="C120">
-        <v>0.7290508338173802</v>
+        <v>0.7290508338173728</v>
       </c>
       <c r="D120">
-        <v>1.075984111954174</v>
+        <v>1.075984111954162</v>
       </c>
       <c r="E120">
-        <v>-0.1213880613638973</v>
+        <v>-0.1213880613639082</v>
       </c>
       <c r="F120">
-        <v>-0.3160118185165255</v>
+        <v>-0.3160118185165358</v>
       </c>
       <c r="G120">
-        <v>0.07323569578873082</v>
+        <v>0.07323569578871926</v>
       </c>
       <c r="H120">
-        <v>0.09929965993650684</v>
+        <v>0.09929965993650643</v>
       </c>
       <c r="I120">
-        <v>-1.222441863763824</v>
+        <v>-1.222441863763939</v>
       </c>
       <c r="J120">
-        <v>0.2215405761367472</v>
+        <v>0.2215405761367037</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9983,31 +9983,31 @@
         </is>
       </c>
       <c r="B121">
-        <v>0.9865231758373281</v>
+        <v>0.986523175837313</v>
       </c>
       <c r="C121">
-        <v>0.7941784329980794</v>
+        <v>0.7941784329980625</v>
       </c>
       <c r="D121">
-        <v>1.225452538153377</v>
+        <v>1.225452538153365</v>
       </c>
       <c r="E121">
-        <v>-0.01356846080269312</v>
+        <v>-0.01356846080270843</v>
       </c>
       <c r="F121">
-        <v>-0.2304471162844302</v>
+        <v>-0.2304471162844516</v>
       </c>
       <c r="G121">
-        <v>0.203310194679044</v>
+        <v>0.2033101946790347</v>
       </c>
       <c r="H121">
-        <v>0.1106544085465082</v>
+        <v>0.1106544085465113</v>
       </c>
       <c r="I121">
-        <v>-0.1226201556803791</v>
+        <v>-0.1226201556805144</v>
       </c>
       <c r="J121">
-        <v>0.9024078929664636</v>
+        <v>0.9024078929663564</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -10063,31 +10063,31 @@
         </is>
       </c>
       <c r="B122">
-        <v>1.002209414343084</v>
+        <v>1.002209414343082</v>
       </c>
       <c r="C122">
-        <v>0.9940009585700824</v>
+        <v>0.9940009585700802</v>
       </c>
       <c r="D122">
-        <v>1.010485655509647</v>
+        <v>1.010485655509645</v>
       </c>
       <c r="E122">
-        <v>0.002206977176361497</v>
+        <v>0.002206977176359282</v>
       </c>
       <c r="F122">
-        <v>-0.006017107969808273</v>
+        <v>-0.006017107969810507</v>
       </c>
       <c r="G122">
-        <v>0.0104310623225314</v>
+        <v>0.01043106232252921</v>
       </c>
       <c r="H122">
-        <v>0.004196038912470015</v>
+        <v>0.004196038912470008</v>
       </c>
       <c r="I122">
-        <v>0.5259668040262357</v>
+        <v>0.5259668040257054</v>
       </c>
       <c r="J122">
-        <v>0.5989112717814786</v>
+        <v>0.5989112717818471</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -10143,31 +10143,31 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.9985004941353791</v>
+        <v>0.998500494135379</v>
       </c>
       <c r="C123">
-        <v>0.9959814412294484</v>
+        <v>0.9959814412294483</v>
       </c>
       <c r="D123">
         <v>1.001025918272018</v>
       </c>
       <c r="E123">
-        <v>-0.001500631248693941</v>
+        <v>-0.001500631248694052</v>
       </c>
       <c r="F123">
-        <v>-0.004026654874907619</v>
+        <v>-0.00402665487490773</v>
       </c>
       <c r="G123">
-        <v>0.001025392377519831</v>
+        <v>0.001025392377519609</v>
       </c>
       <c r="H123">
-        <v>0.001288811246603827</v>
+        <v>0.001288811246603833</v>
       </c>
       <c r="I123">
-        <v>-1.164353005646302</v>
+        <v>-1.164353005646368</v>
       </c>
       <c r="J123">
-        <v>0.2442809839407369</v>
+        <v>0.2442809839407103</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -10223,31 +10223,31 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.287508411703458</v>
+        <v>1.287508411703629</v>
       </c>
       <c r="C124">
-        <v>0.7354781992761469</v>
+        <v>0.7354781992762409</v>
       </c>
       <c r="D124">
-        <v>2.253877697311269</v>
+        <v>2.253877697311579</v>
       </c>
       <c r="E124">
-        <v>0.2527088868963207</v>
+        <v>0.2527088868964535</v>
       </c>
       <c r="F124">
-        <v>-0.307234380064987</v>
+        <v>-0.3072343800648592</v>
       </c>
       <c r="G124">
-        <v>0.8126521538576286</v>
+        <v>0.8126521538577663</v>
       </c>
       <c r="H124">
-        <v>0.2856905899180133</v>
+        <v>0.2856905899180158</v>
       </c>
       <c r="I124">
-        <v>0.8845544649154962</v>
+        <v>0.8845544649159534</v>
       </c>
       <c r="J124">
-        <v>0.37639697488941</v>
+        <v>0.3763969748891633</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -10303,31 +10303,31 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.9138854707853394</v>
+        <v>0.9138854707853444</v>
       </c>
       <c r="C125">
-        <v>0.7802286146349866</v>
+        <v>0.780228614634989</v>
       </c>
       <c r="D125">
-        <v>1.070438379273318</v>
+        <v>1.070438379273327</v>
       </c>
       <c r="E125">
-        <v>-0.09005002086587492</v>
+        <v>-0.09005002086586945</v>
       </c>
       <c r="F125">
-        <v>-0.2481683065567689</v>
+        <v>-0.2481683065567658</v>
       </c>
       <c r="G125">
-        <v>0.0680682648250191</v>
+        <v>0.06806826482502698</v>
       </c>
       <c r="H125">
-        <v>0.08067407714535114</v>
+        <v>0.08067407714535232</v>
       </c>
       <c r="I125">
-        <v>-1.11622003067517</v>
+        <v>-1.116220030675086</v>
       </c>
       <c r="J125">
-        <v>0.2643279624238918</v>
+        <v>0.2643279624239276</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -10383,31 +10383,31 @@
         </is>
       </c>
       <c r="B126">
-        <v>1.229988540962823</v>
+        <v>1.229988540962793</v>
       </c>
       <c r="C126">
-        <v>0.7426173749449062</v>
+        <v>0.7426173749448839</v>
       </c>
       <c r="D126">
-        <v>2.037215747897214</v>
+        <v>2.037215747897177</v>
       </c>
       <c r="E126">
-        <v>0.2070048530505411</v>
+        <v>0.2070048530505169</v>
       </c>
       <c r="F126">
-        <v>-0.2975743400648445</v>
+        <v>-0.2975743400648746</v>
       </c>
       <c r="G126">
-        <v>0.7115840461659266</v>
+        <v>0.7115840461659083</v>
       </c>
       <c r="H126">
-        <v>0.2574430944116535</v>
+        <v>0.2574430944116565</v>
       </c>
       <c r="I126">
-        <v>0.8040800376627648</v>
+        <v>0.8040800376626615</v>
       </c>
       <c r="J126">
-        <v>0.4213507525519318</v>
+        <v>0.4213507525519915</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -10463,31 +10463,31 @@
         </is>
       </c>
       <c r="B127">
-        <v>0.9123892762117893</v>
+        <v>0.9123892762118</v>
       </c>
       <c r="C127">
-        <v>0.7894289354393864</v>
+        <v>0.7894289354393965</v>
       </c>
       <c r="D127">
-        <v>1.054501746737899</v>
+        <v>1.05450174673791</v>
       </c>
       <c r="E127">
-        <v>-0.09168854202568703</v>
+        <v>-0.09168854202567535</v>
       </c>
       <c r="F127">
-        <v>-0.2364454614474802</v>
+        <v>-0.2364454614474674</v>
       </c>
       <c r="G127">
-        <v>0.05306837739610602</v>
+        <v>0.05306837739611676</v>
       </c>
       <c r="H127">
-        <v>0.0738569282719567</v>
+        <v>0.07385692827195611</v>
       </c>
       <c r="I127">
-        <v>-1.241434543392743</v>
+        <v>-1.241434543392593</v>
       </c>
       <c r="J127">
-        <v>0.2144452648678584</v>
+        <v>0.2144452648679135</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -10543,31 +10543,31 @@
         </is>
       </c>
       <c r="B128">
-        <v>0.9958614064722446</v>
+        <v>0.9958614064722453</v>
       </c>
       <c r="C128">
-        <v>0.9922282994487591</v>
+        <v>0.9922282994487598</v>
       </c>
       <c r="D128">
-        <v>0.9995078163481599</v>
+        <v>0.9995078163481605</v>
       </c>
       <c r="E128">
-        <v>-0.004147181208084558</v>
+        <v>-0.004147181208083888</v>
       </c>
       <c r="F128">
-        <v>-0.007802057602197715</v>
+        <v>-0.007802057602197043</v>
       </c>
       <c r="G128">
-        <v>-0.0004923048139713306</v>
+        <v>-0.0004923048139706641</v>
       </c>
       <c r="H128">
-        <v>0.00186476711967279</v>
+        <v>0.001864767119672809</v>
       </c>
       <c r="I128">
-        <v>-2.223967359963013</v>
+        <v>-2.223967359962646</v>
       </c>
       <c r="J128">
-        <v>0.02615064037337679</v>
+        <v>0.0261506403734015</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -10623,31 +10623,31 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.9982696212414801</v>
+        <v>0.99826962124148</v>
       </c>
       <c r="C129">
-        <v>0.9967665828608251</v>
+        <v>0.996766582860825</v>
       </c>
       <c r="D129">
-        <v>0.999774926074896</v>
+        <v>0.9997749260748959</v>
       </c>
       <c r="E129">
-        <v>-0.001731877593127792</v>
+        <v>-0.001731877593127903</v>
       </c>
       <c r="F129">
-        <v>-0.003238655928214495</v>
+        <v>-0.003238655928214607</v>
       </c>
       <c r="G129">
-        <v>-0.0002250992580410992</v>
+        <v>-0.0002250992580412102</v>
       </c>
       <c r="H129">
-        <v>0.0007687785831637583</v>
+        <v>0.0007687785831637533</v>
       </c>
       <c r="I129">
-        <v>-2.252765140777771</v>
+        <v>-2.252765140777875</v>
       </c>
       <c r="J129">
-        <v>0.02427396122432133</v>
+        <v>0.02427396122431472</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -10703,31 +10703,31 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.8543195317350952</v>
+        <v>0.8543195317349587</v>
       </c>
       <c r="C130">
-        <v>0.5319203147786437</v>
+        <v>0.5319203147785634</v>
       </c>
       <c r="D130">
-        <v>1.372126316716821</v>
+        <v>1.37212631671659</v>
       </c>
       <c r="E130">
-        <v>-0.1574499962331758</v>
+        <v>-0.1574499962333356</v>
       </c>
       <c r="F130">
-        <v>-0.6312615851099437</v>
+        <v>-0.6312615851100946</v>
       </c>
       <c r="G130">
-        <v>0.3163615926435921</v>
+        <v>0.3163615926434233</v>
       </c>
       <c r="H130">
-        <v>0.2417450486917787</v>
+        <v>0.2417450486917742</v>
       </c>
       <c r="I130">
-        <v>-0.65130598159188</v>
+        <v>-0.6513059815925535</v>
       </c>
       <c r="J130">
-        <v>0.5148489878948005</v>
+        <v>0.5148489878943658</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -10783,31 +10783,31 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.8836385405016304</v>
+        <v>0.8836385405016344</v>
       </c>
       <c r="C131">
-        <v>0.7599600954981006</v>
+        <v>0.7599600954981056</v>
       </c>
       <c r="D131">
-        <v>1.027444828860495</v>
+        <v>1.027444828860497</v>
       </c>
       <c r="E131">
-        <v>-0.1237071907984057</v>
+        <v>-0.1237071907984011</v>
       </c>
       <c r="F131">
-        <v>-0.2744893530037963</v>
+        <v>-0.2744893530037898</v>
       </c>
       <c r="G131">
-        <v>0.02707497140698514</v>
+        <v>0.02707497140698729</v>
       </c>
       <c r="H131">
-        <v>0.07693108822138633</v>
+        <v>0.07693108822138522</v>
       </c>
       <c r="I131">
-        <v>-1.608026009490606</v>
+        <v>-1.608026009490571</v>
       </c>
       <c r="J131">
-        <v>0.1078294824776333</v>
+        <v>0.1078294824776412</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -10863,31 +10863,31 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.7788456904505772</v>
+        <v>0.7788456904505714</v>
       </c>
       <c r="C132">
-        <v>0.5885575626271002</v>
+        <v>0.5885575626270931</v>
       </c>
       <c r="D132">
-        <v>1.030656384442328</v>
+        <v>1.030656384442325</v>
       </c>
       <c r="E132">
-        <v>-0.2499423394461476</v>
+        <v>-0.249942339446155</v>
       </c>
       <c r="F132">
-        <v>-0.5300805446146638</v>
+        <v>-0.5300805446146758</v>
       </c>
       <c r="G132">
-        <v>0.03019586572236856</v>
+        <v>0.03019586572236576</v>
       </c>
       <c r="H132">
-        <v>0.1429302820756966</v>
+        <v>0.142930282075699</v>
       </c>
       <c r="I132">
-        <v>-1.748701085706784</v>
+        <v>-1.748701085706807</v>
       </c>
       <c r="J132">
-        <v>0.08034270228197612</v>
+        <v>0.08034270228197203</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -10943,31 +10943,31 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.8939422440043834</v>
+        <v>0.8939422440043826</v>
       </c>
       <c r="C133">
-        <v>0.8073470203558699</v>
+        <v>0.80734702035587</v>
       </c>
       <c r="D133">
-        <v>0.9898255836298788</v>
+        <v>0.9898255836298767</v>
       </c>
       <c r="E133">
-        <v>-0.1121141099174952</v>
+        <v>-0.112114109917496</v>
       </c>
       <c r="F133">
-        <v>-0.2140016903086576</v>
+        <v>-0.2140016903086575</v>
       </c>
       <c r="G133">
-        <v>-0.01022652952633257</v>
+        <v>-0.0102265295263347</v>
       </c>
       <c r="H133">
-        <v>0.05198441460906365</v>
+        <v>0.05198441460906304</v>
       </c>
       <c r="I133">
-        <v>-2.156686975521846</v>
+        <v>-2.156686975521889</v>
       </c>
       <c r="J133">
-        <v>0.03103006249216381</v>
+        <v>0.03103006249216039</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -11023,31 +11023,31 @@
         </is>
       </c>
       <c r="B134">
-        <v>1.002944450612309</v>
+        <v>1.002944450612314</v>
       </c>
       <c r="C134">
-        <v>0.9922805692696679</v>
+        <v>0.9922805692696738</v>
       </c>
       <c r="D134">
-        <v>1.013722934990433</v>
+        <v>1.013722934990439</v>
       </c>
       <c r="E134">
-        <v>0.002940124208112894</v>
+        <v>0.00294012420811865</v>
       </c>
       <c r="F134">
-        <v>-0.00774937976160472</v>
+        <v>-0.00774937976159879</v>
       </c>
       <c r="G134">
-        <v>0.01362962817783062</v>
+        <v>0.01362962817783632</v>
       </c>
       <c r="H134">
-        <v>0.005453928773199479</v>
+        <v>0.005453928773199398</v>
       </c>
       <c r="I134">
-        <v>0.5390837193475457</v>
+        <v>0.539083719348609</v>
       </c>
       <c r="J134">
-        <v>0.5898290888248251</v>
+        <v>0.5898290888240915</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -11103,31 +11103,31 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.9978162742419464</v>
+        <v>0.997816274241946</v>
       </c>
       <c r="C135">
-        <v>0.9947274296154465</v>
+        <v>0.9947274296154459</v>
       </c>
       <c r="D135">
-        <v>1.000914710401607</v>
+        <v>1.000914710401606</v>
       </c>
       <c r="E135">
-        <v>-0.002186113563988996</v>
+        <v>-0.002186113563989441</v>
       </c>
       <c r="F135">
-        <v>-0.005286519436961638</v>
+        <v>-0.005286519436962196</v>
       </c>
       <c r="G135">
-        <v>0.0009142923089836854</v>
+        <v>0.0009142923089832417</v>
       </c>
       <c r="H135">
-        <v>0.001581868798318917</v>
+        <v>0.001581868798318902</v>
       </c>
       <c r="I135">
-        <v>-1.381981594372541</v>
+        <v>-1.381981594372861</v>
       </c>
       <c r="J135">
-        <v>0.1669773525766935</v>
+        <v>0.1669773525765951</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -11183,31 +11183,31 @@
         </is>
       </c>
       <c r="B136">
-        <v>1.322101587910663</v>
+        <v>1.322101587910957</v>
       </c>
       <c r="C136">
-        <v>0.6582260515582928</v>
+        <v>0.6582260515584265</v>
       </c>
       <c r="D136">
-        <v>2.65555063434176</v>
+        <v>2.655550634342401</v>
       </c>
       <c r="E136">
-        <v>0.2792225825850518</v>
+        <v>0.279222582585274</v>
       </c>
       <c r="F136">
-        <v>-0.4182068632526817</v>
+        <v>-0.4182068632524786</v>
       </c>
       <c r="G136">
-        <v>0.9766520284227853</v>
+        <v>0.9766520284230267</v>
       </c>
       <c r="H136">
-        <v>0.3558378885219158</v>
+        <v>0.3558378885219255</v>
       </c>
       <c r="I136">
-        <v>0.7846904210928475</v>
+        <v>0.7846904210934503</v>
       </c>
       <c r="J136">
-        <v>0.4326351003604124</v>
+        <v>0.4326351003600589</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -11263,31 +11263,31 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.8802534340996269</v>
+        <v>0.8802534340995767</v>
       </c>
       <c r="C137">
-        <v>0.7274562054032945</v>
+        <v>0.7274562054032493</v>
       </c>
       <c r="D137">
-        <v>1.065144681547694</v>
+        <v>1.065144681547639</v>
       </c>
       <c r="E137">
-        <v>-0.127545419676963</v>
+        <v>-0.12754541967702</v>
       </c>
       <c r="F137">
-        <v>-0.3182014805068655</v>
+        <v>-0.3182014805069276</v>
       </c>
       <c r="G137">
-        <v>0.06311064115293967</v>
+        <v>0.06311064115288777</v>
       </c>
       <c r="H137">
-        <v>0.09727528787966173</v>
+        <v>0.09727528787966436</v>
       </c>
       <c r="I137">
-        <v>-1.311180079310052</v>
+        <v>-1.311180079310602</v>
       </c>
       <c r="J137">
-        <v>0.1897969309108858</v>
+        <v>0.1897969309106999</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -11343,31 +11343,31 @@
         </is>
       </c>
       <c r="B138">
-        <v>1.29478554988374</v>
+        <v>1.294785549883574</v>
       </c>
       <c r="C138">
-        <v>0.6846581232825615</v>
+        <v>0.6846581232824723</v>
       </c>
       <c r="D138">
-        <v>2.448622988872143</v>
+        <v>2.448622988871836</v>
       </c>
       <c r="E138">
-        <v>0.2583450828931732</v>
+        <v>0.2583450828930454</v>
       </c>
       <c r="F138">
-        <v>-0.3788356554052805</v>
+        <v>-0.3788356554054107</v>
       </c>
       <c r="G138">
-        <v>0.8955258211916269</v>
+        <v>0.8955258211915014</v>
       </c>
       <c r="H138">
-        <v>0.3250981871730574</v>
+        <v>0.3250981871730586</v>
       </c>
       <c r="I138">
-        <v>0.7946678667748155</v>
+        <v>0.7946678667744193</v>
       </c>
       <c r="J138">
-        <v>0.4268067288927439</v>
+        <v>0.4268067288929744</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -11423,31 +11423,31 @@
         </is>
       </c>
       <c r="B139">
-        <v>0.8795428999880751</v>
+        <v>0.8795428999880956</v>
       </c>
       <c r="C139">
-        <v>0.7382691769713785</v>
+        <v>0.7382691769713945</v>
       </c>
       <c r="D139">
-        <v>1.04785048197864</v>
+        <v>1.047850481978666</v>
       </c>
       <c r="E139">
-        <v>-0.1283529382930657</v>
+        <v>-0.1283529382930424</v>
       </c>
       <c r="F139">
-        <v>-0.3034467824389586</v>
+        <v>-0.3034467824389369</v>
       </c>
       <c r="G139">
-        <v>0.04674090585282709</v>
+        <v>0.04674090585285209</v>
       </c>
       <c r="H139">
-        <v>0.08933523550790257</v>
+        <v>0.08933523550790347</v>
       </c>
       <c r="I139">
-        <v>-1.436756029838995</v>
+        <v>-1.436756029838719</v>
       </c>
       <c r="J139">
-        <v>0.1507873282369838</v>
+        <v>0.1507873282370616</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -11503,31 +11503,31 @@
         </is>
       </c>
       <c r="B140">
-        <v>0.9969514820559268</v>
+        <v>0.9969514820559272</v>
       </c>
       <c r="C140">
-        <v>0.9927422932072644</v>
+        <v>0.9927422932072648</v>
       </c>
       <c r="D140">
         <v>1.001178517702177</v>
       </c>
       <c r="E140">
-        <v>-0.003053174140307345</v>
+        <v>-0.0030531741403069</v>
       </c>
       <c r="F140">
-        <v>-0.007284172075938624</v>
+        <v>-0.007284172075938177</v>
       </c>
       <c r="G140">
-        <v>0.001177823795323799</v>
+        <v>0.001177823795324242</v>
       </c>
       <c r="H140">
-        <v>0.002158712082979495</v>
+        <v>0.002158712082979478</v>
       </c>
       <c r="I140">
-        <v>-1.414349863689697</v>
+        <v>-1.414349863689517</v>
       </c>
       <c r="J140">
-        <v>0.157259203017668</v>
+        <v>0.1572592030177205</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>0.9979418394320886</v>
       </c>
       <c r="C141">
-        <v>0.9961223257975312</v>
+        <v>0.9961223257975313</v>
       </c>
       <c r="D141">
         <v>0.9997646765840299</v>
@@ -11595,19 +11595,19 @@
         <v>-0.002060281491006265</v>
       </c>
       <c r="F141">
-        <v>-0.003885211873142759</v>
+        <v>-0.003885211873142648</v>
       </c>
       <c r="G141">
         <v>-0.0002353511088697635</v>
       </c>
       <c r="H141">
-        <v>0.0009311040389166767</v>
+        <v>0.0009311040389166702</v>
       </c>
       <c r="I141">
-        <v>-2.212729625148411</v>
+        <v>-2.212729625148371</v>
       </c>
       <c r="J141">
-        <v>0.02691629166755095</v>
+        <v>0.02691629166755382</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -11663,31 +11663,31 @@
         </is>
       </c>
       <c r="B142">
-        <v>0.8873981711565539</v>
+        <v>0.8873981711565836</v>
       </c>
       <c r="C142">
-        <v>0.5016799117438673</v>
+        <v>0.5016799117438774</v>
       </c>
       <c r="D142">
-        <v>1.569677190052693</v>
+        <v>1.569677190052766</v>
       </c>
       <c r="E142">
-        <v>-0.1194615009403374</v>
+        <v>-0.119461500940304</v>
       </c>
       <c r="F142">
-        <v>-0.6897929886685574</v>
+        <v>-0.6897929886685373</v>
       </c>
       <c r="G142">
-        <v>0.4508699867878828</v>
+        <v>0.4508699867879293</v>
       </c>
       <c r="H142">
-        <v>0.2909907999467961</v>
+        <v>0.2909907999468029</v>
       </c>
       <c r="I142">
-        <v>-0.4105336009323297</v>
+        <v>-0.4105336009322054</v>
       </c>
       <c r="J142">
-        <v>0.681414560303847</v>
+        <v>0.6814145603039381</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -11743,31 +11743,31 @@
         </is>
       </c>
       <c r="B143">
-        <v>0.8507586169714522</v>
+        <v>0.8507586169714305</v>
       </c>
       <c r="C143">
-        <v>0.7091869480162112</v>
+        <v>0.7091869480161969</v>
       </c>
       <c r="D143">
-        <v>1.020591575149284</v>
+        <v>1.020591575149252</v>
       </c>
       <c r="E143">
-        <v>-0.1616268369760109</v>
+        <v>-0.1616268369760364</v>
       </c>
       <c r="F143">
-        <v>-0.3436361087638855</v>
+        <v>-0.3436361087639057</v>
       </c>
       <c r="G143">
-        <v>0.02038243481186359</v>
+        <v>0.02038243481183291</v>
       </c>
       <c r="H143">
-        <v>0.09286357975123037</v>
+        <v>0.09286357975122768</v>
       </c>
       <c r="I143">
-        <v>-1.740476055402866</v>
+        <v>-1.740476055403191</v>
       </c>
       <c r="J143">
-        <v>0.08177546098466064</v>
+        <v>0.08177546098460386</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -11823,31 +11823,31 @@
         </is>
       </c>
       <c r="B144">
-        <v>0.8207805809235952</v>
+        <v>0.8207805809235702</v>
       </c>
       <c r="C144">
-        <v>0.5920771273523673</v>
+        <v>0.5920771273523472</v>
       </c>
       <c r="D144">
-        <v>1.137826021136503</v>
+        <v>1.137826021136472</v>
       </c>
       <c r="E144">
-        <v>-0.1974994635643207</v>
+        <v>-0.1974994635643511</v>
       </c>
       <c r="F144">
-        <v>-0.5241183698943743</v>
+        <v>-0.5241183698944083</v>
       </c>
       <c r="G144">
-        <v>0.1291194427657332</v>
+        <v>0.1291194427657061</v>
       </c>
       <c r="H144">
-        <v>0.1666453612956066</v>
+        <v>0.1666453612956083</v>
       </c>
       <c r="I144">
-        <v>-1.185148281529319</v>
+        <v>-1.18514828152949</v>
       </c>
       <c r="J144">
-        <v>0.235958824266938</v>
+        <v>0.2359588242668705</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -11903,31 +11903,31 @@
         </is>
       </c>
       <c r="B145">
-        <v>0.870678626553039</v>
+        <v>0.8706786265530128</v>
       </c>
       <c r="C145">
-        <v>0.7702545304825278</v>
+        <v>0.7702545304825027</v>
       </c>
       <c r="D145">
-        <v>0.9841957959810825</v>
+        <v>0.9841957959810552</v>
       </c>
       <c r="E145">
-        <v>-0.1384823408784698</v>
+        <v>-0.1384823408784999</v>
       </c>
       <c r="F145">
-        <v>-0.2610342596888014</v>
+        <v>-0.261034259688834</v>
       </c>
       <c r="G145">
-        <v>-0.01593042206813795</v>
+        <v>-0.01593042206816569</v>
       </c>
       <c r="H145">
-        <v>0.0625276381489689</v>
+        <v>0.06252763814897012</v>
       </c>
       <c r="I145">
-        <v>-2.214738073882506</v>
+        <v>-2.214738073882944</v>
       </c>
       <c r="J145">
-        <v>0.02677804791446909</v>
+        <v>0.02677804791443906</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -11983,31 +11983,31 @@
         </is>
       </c>
       <c r="B146">
-        <v>1.02937487219774</v>
+        <v>1.029374872197711</v>
       </c>
       <c r="C146">
-        <v>0.9241009318930581</v>
+        <v>0.9241009318930312</v>
       </c>
       <c r="D146">
-        <v>1.146641661037453</v>
+        <v>1.146641661037421</v>
       </c>
       <c r="E146">
-        <v>0.0289516977945593</v>
+        <v>0.02895169779453082</v>
       </c>
       <c r="F146">
-        <v>-0.07893397965551791</v>
+        <v>-0.07893397965554698</v>
       </c>
       <c r="G146">
-        <v>0.1368373752446364</v>
+        <v>0.1368373752446085</v>
       </c>
       <c r="H146">
-        <v>0.05504472444446206</v>
+        <v>0.05504472444446235</v>
       </c>
       <c r="I146">
-        <v>0.5259668040262485</v>
+        <v>0.5259668040257288</v>
       </c>
       <c r="J146">
-        <v>0.5989112717814697</v>
+        <v>0.5989112717818308</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -12063,31 +12063,31 @@
         </is>
       </c>
       <c r="B147">
-        <v>0.9394185086156317</v>
+        <v>0.9394185086156273</v>
       </c>
       <c r="C147">
-        <v>0.8456149584220751</v>
+        <v>0.8456149584220706</v>
       </c>
       <c r="D147">
-        <v>1.043627629265669</v>
+        <v>1.043627629265665</v>
       </c>
       <c r="E147">
-        <v>-0.06249420299058336</v>
+        <v>-0.06249420299058809</v>
       </c>
       <c r="F147">
-        <v>-0.1676911548686688</v>
+        <v>-0.1676911548686742</v>
       </c>
       <c r="G147">
-        <v>0.04270274888750209</v>
+        <v>0.04270274888749805</v>
       </c>
       <c r="H147">
-        <v>0.05367290047565444</v>
+        <v>0.0536729004756548</v>
       </c>
       <c r="I147">
-        <v>-1.164353005646307</v>
+        <v>-1.164353005646387</v>
       </c>
       <c r="J147">
-        <v>0.2442809839407348</v>
+        <v>0.2442809839407025</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -12143,31 +12143,31 @@
         </is>
       </c>
       <c r="B148">
-        <v>1.057629585755625</v>
+        <v>1.057629585755656</v>
       </c>
       <c r="C148">
-        <v>0.9341488740941299</v>
+        <v>0.9341488740941563</v>
       </c>
       <c r="D148">
-        <v>1.19743262737466</v>
+        <v>1.197432627374697</v>
       </c>
       <c r="E148">
-        <v>0.05603016415254884</v>
+        <v>0.05603016415257823</v>
       </c>
       <c r="F148">
-        <v>-0.0681194593501209</v>
+        <v>-0.06811945935009273</v>
       </c>
       <c r="G148">
-        <v>0.1801797876552185</v>
+        <v>0.1801797876552491</v>
       </c>
       <c r="H148">
-        <v>0.06334280858319137</v>
+        <v>0.06334280858319201</v>
       </c>
       <c r="I148">
-        <v>0.8845544649154836</v>
+        <v>0.8845544649159391</v>
       </c>
       <c r="J148">
-        <v>0.3763969748894168</v>
+        <v>0.376396974889171</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -12223,31 +12223,31 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.9371515747506396</v>
+        <v>0.9371515747506429</v>
       </c>
       <c r="C149">
-        <v>0.8362014321242266</v>
+        <v>0.8362014321242282</v>
       </c>
       <c r="D149">
-        <v>1.050288890114135</v>
+        <v>1.05028889011414</v>
       </c>
       <c r="E149">
-        <v>-0.06491024381720438</v>
+        <v>-0.06491024381720083</v>
       </c>
       <c r="F149">
-        <v>-0.178885747403609</v>
+        <v>-0.1788857474036071</v>
       </c>
       <c r="G149">
-        <v>0.04906525976920036</v>
+        <v>0.04906525976920544</v>
       </c>
       <c r="H149">
-        <v>0.05815183568954784</v>
+        <v>0.05815183568954867</v>
       </c>
       <c r="I149">
-        <v>-1.116220030675167</v>
+        <v>-1.11622003067509</v>
       </c>
       <c r="J149">
-        <v>0.2643279624238933</v>
+        <v>0.2643279624239261</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -12303,31 +12303,31 @@
         </is>
       </c>
       <c r="B150">
-        <v>1.049301039047941</v>
+        <v>1.049301039047937</v>
       </c>
       <c r="C150">
-        <v>0.9331589182437674</v>
+        <v>0.9331589182437623</v>
       </c>
       <c r="D150">
-        <v>1.1798983528114</v>
+        <v>1.179898352811397</v>
       </c>
       <c r="E150">
-        <v>0.04812426541085904</v>
+        <v>0.04812426541085481</v>
       </c>
       <c r="F150">
-        <v>-0.06917976226019332</v>
+        <v>-0.0691797622601988</v>
       </c>
       <c r="G150">
-        <v>0.1654282930819115</v>
+        <v>0.1654282930819087</v>
       </c>
       <c r="H150">
-        <v>0.05985009346923293</v>
+        <v>0.05985009346923361</v>
       </c>
       <c r="I150">
-        <v>0.8040800376627364</v>
+        <v>0.804080037662657</v>
       </c>
       <c r="J150">
-        <v>0.4213507525519482</v>
+        <v>0.4213507525519941</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -12383,31 +12383,31 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.9366773133541352</v>
+        <v>0.9366773133541433</v>
       </c>
       <c r="C151">
-        <v>0.8447663201169436</v>
+        <v>0.8447663201169515</v>
       </c>
       <c r="D151">
-        <v>1.038588268091541</v>
+        <v>1.038588268091549</v>
       </c>
       <c r="E151">
-        <v>-0.06541643881680319</v>
+        <v>-0.06541643881679453</v>
       </c>
       <c r="F151">
-        <v>-0.1686952341106762</v>
+        <v>-0.1686952341106669</v>
       </c>
       <c r="G151">
-        <v>0.03786235647706994</v>
+        <v>0.03786235647707764</v>
       </c>
       <c r="H151">
-        <v>0.05269423117390067</v>
+        <v>0.05269423117390028</v>
       </c>
       <c r="I151">
-        <v>-1.241434543392746</v>
+        <v>-1.241434543392592</v>
       </c>
       <c r="J151">
-        <v>0.2144452648678571</v>
+        <v>0.2144452648679141</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -12463,31 +12463,31 @@
         </is>
       </c>
       <c r="B152">
-        <v>0.8931743067303083</v>
+        <v>0.8931743067303234</v>
       </c>
       <c r="C152">
-        <v>0.8085310832898223</v>
+        <v>0.808531083289835</v>
       </c>
       <c r="D152">
-        <v>0.9866786307796226</v>
+        <v>0.9866786307796404</v>
       </c>
       <c r="E152">
-        <v>-0.1129735248460017</v>
+        <v>-0.1129735248459848</v>
       </c>
       <c r="F152">
-        <v>-0.2125361550765039</v>
+        <v>-0.2125361550764881</v>
       </c>
       <c r="G152">
-        <v>-0.01341089461549946</v>
+        <v>-0.01341089461548145</v>
       </c>
       <c r="H152">
-        <v>0.05079819375041562</v>
+        <v>0.05079819375041618</v>
       </c>
       <c r="I152">
-        <v>-2.223967359963019</v>
+        <v>-2.223967359962661</v>
       </c>
       <c r="J152">
-        <v>0.02615064037337635</v>
+        <v>0.02615064037340047</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -12543,31 +12543,31 @@
         </is>
       </c>
       <c r="B153">
-        <v>0.8909860474780992</v>
+        <v>0.8909860474780948</v>
       </c>
       <c r="C153">
-        <v>0.8058557172126436</v>
+        <v>0.8058557172126403</v>
       </c>
       <c r="D153">
-        <v>0.9851095175529645</v>
+        <v>0.9851095175529592</v>
       </c>
       <c r="E153">
-        <v>-0.1154265110300101</v>
+        <v>-0.115426511030015</v>
       </c>
       <c r="F153">
-        <v>-0.2158505634023</v>
+        <v>-0.2158505634023042</v>
       </c>
       <c r="G153">
-        <v>-0.0150024586577203</v>
+        <v>-0.01500245865772571</v>
       </c>
       <c r="H153">
-        <v>0.05123770291924853</v>
+        <v>0.05123770291924818</v>
       </c>
       <c r="I153">
-        <v>-2.252765140777764</v>
+        <v>-2.252765140777873</v>
       </c>
       <c r="J153">
-        <v>0.02427396122432181</v>
+        <v>0.02427396122431492</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -12623,31 +12623,31 @@
         </is>
       </c>
       <c r="B154">
-        <v>0.9642543083622273</v>
+        <v>0.9642543083621915</v>
       </c>
       <c r="C154">
-        <v>0.8642106288200971</v>
+        <v>0.8642106288200671</v>
       </c>
       <c r="D154">
-        <v>1.075879351847998</v>
+        <v>1.075879351847956</v>
       </c>
       <c r="E154">
-        <v>-0.0364002138070981</v>
+        <v>-0.03640021380713517</v>
       </c>
       <c r="F154">
-        <v>-0.1459387565318215</v>
+        <v>-0.1459387565318563</v>
       </c>
       <c r="G154">
-        <v>0.07313832891762523</v>
+        <v>0.07313832891758601</v>
       </c>
       <c r="H154">
-        <v>0.05588803855007004</v>
+        <v>0.05588803855006894</v>
       </c>
       <c r="I154">
-        <v>-0.6513059815918785</v>
+        <v>-0.6513059815925535</v>
       </c>
       <c r="J154">
-        <v>0.5148489878948016</v>
+        <v>0.5148489878943658</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -12703,31 +12703,31 @@
         </is>
       </c>
       <c r="B155">
-        <v>0.9102098541666768</v>
+        <v>0.9102098541666802</v>
       </c>
       <c r="C155">
-        <v>0.8115973953594019</v>
+        <v>0.8115973953594062</v>
       </c>
       <c r="D155">
-        <v>1.020804136828512</v>
+        <v>1.020804136828515</v>
       </c>
       <c r="E155">
-        <v>-0.09408009708303353</v>
+        <v>-0.09408009708302974</v>
       </c>
       <c r="F155">
-        <v>-0.2087508803020121</v>
+        <v>-0.2087508803020068</v>
       </c>
       <c r="G155">
-        <v>0.02059068613594524</v>
+        <v>0.02059068613594742</v>
       </c>
       <c r="H155">
-        <v>0.05850657671441271</v>
+        <v>0.0585065767144119</v>
       </c>
       <c r="I155">
-        <v>-1.608026009490612</v>
+        <v>-1.608026009490571</v>
       </c>
       <c r="J155">
-        <v>0.1078294824776318</v>
+        <v>0.1078294824776412</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -12783,31 +12783,31 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.9142534806502266</v>
+        <v>0.9142534806502262</v>
       </c>
       <c r="C156">
-        <v>0.8268555614353568</v>
+        <v>0.826855561435356</v>
       </c>
       <c r="D156">
         <v>1.010889284496155</v>
       </c>
       <c r="E156">
-        <v>-0.0896474148499929</v>
+        <v>-0.08964741484999339</v>
       </c>
       <c r="F156">
-        <v>-0.1901252528574457</v>
+        <v>-0.1901252528574467</v>
       </c>
       <c r="G156">
-        <v>0.01083042315745979</v>
+        <v>0.01083042315746</v>
       </c>
       <c r="H156">
-        <v>0.05126514507409791</v>
+        <v>0.05126514507409816</v>
       </c>
       <c r="I156">
-        <v>-1.748701085706826</v>
+        <v>-1.748701085706825</v>
       </c>
       <c r="J156">
-        <v>0.08034270228196899</v>
+        <v>0.08034270228196901</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -12863,31 +12863,31 @@
         </is>
       </c>
       <c r="B157">
-        <v>0.8959279611422823</v>
+        <v>0.8959279611422816</v>
       </c>
       <c r="C157">
-        <v>0.8107736187102983</v>
+        <v>0.8107736187102985</v>
       </c>
       <c r="D157">
-        <v>0.9900259369975619</v>
+        <v>0.9900259369975599</v>
       </c>
       <c r="E157">
-        <v>-0.1098952697503465</v>
+        <v>-0.1098952697503474</v>
       </c>
       <c r="F157">
-        <v>-0.2097664022914403</v>
+        <v>-0.20976640229144</v>
       </c>
       <c r="G157">
-        <v>-0.01002413720925264</v>
+        <v>-0.01002413720925466</v>
       </c>
       <c r="H157">
-        <v>0.05095559578077179</v>
+        <v>0.05095559578077121</v>
       </c>
       <c r="I157">
-        <v>-2.156686975521846</v>
+        <v>-2.156686975521889</v>
       </c>
       <c r="J157">
-        <v>0.03103006249216375</v>
+        <v>0.03103006249216039</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -12943,31 +12943,31 @@
         </is>
       </c>
       <c r="B158">
-        <v>1.039322761639521</v>
+        <v>1.0393227616396</v>
       </c>
       <c r="C158">
-        <v>0.9033381069397776</v>
+        <v>0.9033381069398491</v>
       </c>
       <c r="D158">
-        <v>1.195777964599929</v>
+        <v>1.195777964600017</v>
       </c>
       <c r="E158">
-        <v>0.03856931030527649</v>
+        <v>0.03856931030535276</v>
       </c>
       <c r="F158">
-        <v>-0.1016583693552846</v>
+        <v>-0.1016583693552055</v>
       </c>
       <c r="G158">
-        <v>0.1787969899658374</v>
+        <v>0.1787969899659108</v>
       </c>
       <c r="H158">
-        <v>0.07154604919613786</v>
+        <v>0.07154604919613639</v>
       </c>
       <c r="I158">
-        <v>0.5390837193475455</v>
+        <v>0.5390837193486225</v>
       </c>
       <c r="J158">
-        <v>0.5898290888248252</v>
+        <v>0.5898290888240821</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -13023,31 +13023,31 @@
         </is>
       </c>
       <c r="B159">
-        <v>0.9129800009274022</v>
+        <v>0.9129800009273873</v>
       </c>
       <c r="C159">
-        <v>0.8023915585287282</v>
+        <v>0.8023915585287164</v>
       </c>
       <c r="D159">
-        <v>1.038810133573403</v>
+        <v>1.038810133573385</v>
       </c>
       <c r="E159">
-        <v>-0.09104130341634577</v>
+        <v>-0.09104130341636206</v>
       </c>
       <c r="F159">
-        <v>-0.2201585626680047</v>
+        <v>-0.2201585626680195</v>
       </c>
       <c r="G159">
-        <v>0.03807595583531313</v>
+        <v>0.03807595583529561</v>
       </c>
       <c r="H159">
-        <v>0.0658773631914257</v>
+        <v>0.06587736319142497</v>
       </c>
       <c r="I159">
-        <v>-1.381981594372547</v>
+        <v>-1.381981594372808</v>
       </c>
       <c r="J159">
-        <v>0.1669773525766918</v>
+        <v>0.1669773525766115</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -13103,31 +13103,31 @@
         </is>
       </c>
       <c r="B160">
-        <v>1.063865245062446</v>
+        <v>1.063865245062501</v>
       </c>
       <c r="C160">
-        <v>0.9114449509453854</v>
+        <v>0.911444950945434</v>
       </c>
       <c r="D160">
-        <v>1.24177467709687</v>
+        <v>1.241774677096932</v>
       </c>
       <c r="E160">
-        <v>0.06190873352134281</v>
+        <v>0.06190873352139416</v>
       </c>
       <c r="F160">
-        <v>-0.09272408060340349</v>
+        <v>-0.09272408060335013</v>
       </c>
       <c r="G160">
-        <v>0.216541547646089</v>
+        <v>0.2165415476461385</v>
       </c>
       <c r="H160">
-        <v>0.07889574264857428</v>
+        <v>0.07889574264857326</v>
       </c>
       <c r="I160">
-        <v>0.784690421092848</v>
+        <v>0.7846904210935102</v>
       </c>
       <c r="J160">
-        <v>0.432635100360412</v>
+        <v>0.4326351003600237</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -13183,31 +13183,31 @@
         </is>
       </c>
       <c r="B161">
-        <v>0.9121618489927029</v>
+        <v>0.9121618489927288</v>
       </c>
       <c r="C161">
-        <v>0.7950364141379124</v>
+        <v>0.7950364141379369</v>
       </c>
       <c r="D161">
-        <v>1.046542301662997</v>
+        <v>1.046542301663024</v>
       </c>
       <c r="E161">
-        <v>-0.09193783865226283</v>
+        <v>-0.09193783865223447</v>
       </c>
       <c r="F161">
-        <v>-0.2293673614297143</v>
+        <v>-0.2293673614296834</v>
       </c>
       <c r="G161">
-        <v>0.04549168412518868</v>
+        <v>0.04549168412521436</v>
       </c>
       <c r="H161">
-        <v>0.07011839189978901</v>
+        <v>0.07011839189978769</v>
       </c>
       <c r="I161">
-        <v>-1.311180079310112</v>
+        <v>-1.311180079309732</v>
       </c>
       <c r="J161">
-        <v>0.1897969309108655</v>
+        <v>0.1897969309109938</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -13263,31 +13263,31 @@
         </is>
       </c>
       <c r="B162">
-        <v>1.061900032231667</v>
+        <v>1.061900032231643</v>
       </c>
       <c r="C162">
-        <v>0.9156955803755235</v>
+        <v>0.9156955803754997</v>
       </c>
       <c r="D162">
-        <v>1.231448204643706</v>
+        <v>1.231448204643682</v>
       </c>
       <c r="E162">
-        <v>0.06005978678048911</v>
+        <v>0.06005978678046632</v>
       </c>
       <c r="F162">
-        <v>-0.08807130537837987</v>
+        <v>-0.08807130537840581</v>
       </c>
       <c r="G162">
-        <v>0.2081908789393583</v>
+        <v>0.2081908789393384</v>
       </c>
       <c r="H162">
-        <v>0.07557847660840113</v>
+        <v>0.07557847660840268</v>
       </c>
       <c r="I162">
-        <v>0.7946678667748257</v>
+        <v>0.7946678667745074</v>
       </c>
       <c r="J162">
-        <v>0.426806728892738</v>
+        <v>0.4268067288929232</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -13343,31 +13343,31 @@
         </is>
       </c>
       <c r="B163">
-        <v>0.9124927382976492</v>
+        <v>0.912492738297657</v>
       </c>
       <c r="C163">
-        <v>0.8053339531800817</v>
+        <v>0.8053339531800879</v>
       </c>
       <c r="D163">
-        <v>1.033910210985173</v>
+        <v>1.033910210985183</v>
       </c>
       <c r="E163">
-        <v>-0.09157515158712924</v>
+        <v>-0.09157515158712072</v>
       </c>
       <c r="F163">
-        <v>-0.2164982389185836</v>
+        <v>-0.2164982389185759</v>
       </c>
       <c r="G163">
-        <v>0.03334793574432505</v>
+        <v>0.0333479357443345</v>
       </c>
       <c r="H163">
-        <v>0.06373744023708178</v>
+        <v>0.06373744023708221</v>
       </c>
       <c r="I163">
-        <v>-1.436756029838987</v>
+        <v>-1.436756029838842</v>
       </c>
       <c r="J163">
-        <v>0.1507873282369847</v>
+        <v>0.1507873282370266</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -13423,31 +13423,31 @@
         </is>
       </c>
       <c r="B164">
-        <v>0.9201931956669478</v>
+        <v>0.9201931956669576</v>
       </c>
       <c r="C164">
-        <v>0.8200184694310743</v>
+        <v>0.8200184694310833</v>
       </c>
       <c r="D164">
-        <v>1.032605421606205</v>
+        <v>1.032605421606216</v>
       </c>
       <c r="E164">
-        <v>-0.08317163569481505</v>
+        <v>-0.08317163569480443</v>
       </c>
       <c r="F164">
-        <v>-0.1984284152810609</v>
+        <v>-0.1984284152810499</v>
       </c>
       <c r="G164">
-        <v>0.03208514389143068</v>
+        <v>0.032085143891441</v>
       </c>
       <c r="H164">
-        <v>0.05880555994670137</v>
+        <v>0.05880555994670124</v>
       </c>
       <c r="I164">
-        <v>-1.414349863689725</v>
+        <v>-1.414349863689548</v>
       </c>
       <c r="J164">
-        <v>0.1572592030176589</v>
+        <v>0.1572592030177117</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -13503,31 +13503,31 @@
         </is>
       </c>
       <c r="B165">
-        <v>0.8716964380369131</v>
+        <v>0.8716964380369292</v>
       </c>
       <c r="C165">
-        <v>0.7718675211481628</v>
+        <v>0.7718675211481775</v>
       </c>
       <c r="D165">
-        <v>0.9844366543055839</v>
+        <v>0.9844366543056015</v>
       </c>
       <c r="E165">
-        <v>-0.1373140371988208</v>
+        <v>-0.1373140371988023</v>
       </c>
       <c r="F165">
-        <v>-0.2589423484134964</v>
+        <v>-0.2589423484134774</v>
       </c>
       <c r="G165">
-        <v>-0.01568572598414511</v>
+        <v>-0.01568572598412729</v>
       </c>
       <c r="H165">
-        <v>0.06205640112474734</v>
+        <v>0.06205640112474706</v>
       </c>
       <c r="I165">
-        <v>-2.212729625148397</v>
+        <v>-2.212729625148111</v>
       </c>
       <c r="J165">
-        <v>0.02691629166755192</v>
+        <v>0.02691629166757173</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -13583,31 +13583,31 @@
         </is>
       </c>
       <c r="B166">
-        <v>0.9727600743483188</v>
+        <v>0.9727600743483292</v>
       </c>
       <c r="C166">
-        <v>0.8525952125544284</v>
+        <v>0.8525952125544357</v>
       </c>
       <c r="D166">
-        <v>1.10986098480554</v>
+        <v>1.109860984805555</v>
       </c>
       <c r="E166">
-        <v>-0.02761781060639588</v>
+        <v>-0.02761781060638515</v>
       </c>
       <c r="F166">
-        <v>-0.1594703897800591</v>
+        <v>-0.1594703897800505</v>
       </c>
       <c r="G166">
-        <v>0.1042347685672673</v>
+        <v>0.1042347685672803</v>
       </c>
       <c r="H166">
-        <v>0.06727296022462637</v>
+        <v>0.06727296022462745</v>
       </c>
       <c r="I166">
-        <v>-0.4105336009323693</v>
+        <v>-0.4105336009322025</v>
       </c>
       <c r="J166">
-        <v>0.6814145603038179</v>
+        <v>0.6814145603039402</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -13663,31 +13663,31 @@
         </is>
       </c>
       <c r="B167">
-        <v>0.8843359747398467</v>
+        <v>0.8843359747398238</v>
       </c>
       <c r="C167">
-        <v>0.7700210528124231</v>
+        <v>0.7700210528124022</v>
       </c>
       <c r="D167">
-        <v>1.015621733149654</v>
+        <v>1.01562173314963</v>
       </c>
       <c r="E167">
-        <v>-0.1229182266268283</v>
+        <v>-0.1229182266268542</v>
       </c>
       <c r="F167">
-        <v>-0.2613374231933393</v>
+        <v>-0.2613374231933664</v>
       </c>
       <c r="G167">
-        <v>0.01550096993968253</v>
+        <v>0.01550096993965826</v>
       </c>
       <c r="H167">
-        <v>0.07062333678493279</v>
+        <v>0.07062333678493346</v>
       </c>
       <c r="I167">
-        <v>-1.740476055402872</v>
+        <v>-1.74047605540322</v>
       </c>
       <c r="J167">
-        <v>0.08177546098465997</v>
+        <v>0.08177546098459852</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -13743,31 +13743,31 @@
         </is>
       </c>
       <c r="B168">
-        <v>0.9316131705498447</v>
+        <v>0.93161317054982</v>
       </c>
       <c r="C168">
-        <v>0.828625657088478</v>
+        <v>0.828625657088455</v>
       </c>
       <c r="D168">
-        <v>1.047400707566146</v>
+        <v>1.047400707566119</v>
       </c>
       <c r="E168">
-        <v>-0.07083760351301394</v>
+        <v>-0.07083760351304051</v>
       </c>
       <c r="F168">
-        <v>-0.1879867854343482</v>
+        <v>-0.187986785434376</v>
       </c>
       <c r="G168">
-        <v>0.04631157840832049</v>
+        <v>0.04631157840829505</v>
       </c>
       <c r="H168">
-        <v>0.05977108908397921</v>
+        <v>0.05977108908397979</v>
       </c>
       <c r="I168">
-        <v>-1.18514828152932</v>
+        <v>-1.185148281529754</v>
       </c>
       <c r="J168">
-        <v>0.2359588242669376</v>
+        <v>0.2359588242667662</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -13823,31 +13823,31 @@
         </is>
       </c>
       <c r="B169">
-        <v>0.8730681609968344</v>
+        <v>0.8730681609968033</v>
       </c>
       <c r="C169">
-        <v>0.7742440427625026</v>
+        <v>0.7742440427624731</v>
       </c>
       <c r="D169">
-        <v>0.9845061397265564</v>
+        <v>0.9845061397265239</v>
       </c>
       <c r="E169">
-        <v>-0.1357416494471413</v>
+        <v>-0.1357416494471769</v>
       </c>
       <c r="F169">
-        <v>-0.2558681543624906</v>
+        <v>-0.2558681543625287</v>
       </c>
       <c r="G169">
-        <v>-0.01561514453179213</v>
+        <v>-0.01561514453182517</v>
       </c>
       <c r="H169">
-        <v>0.06129015934113678</v>
+        <v>0.06129015934113808</v>
       </c>
       <c r="I169">
-        <v>-2.214738073882508</v>
+        <v>-2.214738073883044</v>
       </c>
       <c r="J169">
-        <v>0.02677804791446896</v>
+        <v>0.0267780479144322</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -13903,31 +13903,31 @@
         </is>
       </c>
       <c r="B170">
-        <v>1.00145924032718</v>
+        <v>1.001459240327187</v>
       </c>
       <c r="C170">
-        <v>0.9954077180563549</v>
+        <v>0.9954077180563616</v>
       </c>
       <c r="D170">
-        <v>1.007547552469262</v>
+        <v>1.007547552469269</v>
       </c>
       <c r="E170">
-        <v>0.001458176670642188</v>
+        <v>0.001458176670649061</v>
       </c>
       <c r="F170">
-        <v>-0.00460285886426032</v>
+        <v>-0.004602858864253516</v>
       </c>
       <c r="G170">
-        <v>0.007519212205544691</v>
+        <v>0.007519212205551523</v>
       </c>
       <c r="H170">
-        <v>0.003092421892805754</v>
+        <v>0.003092421892805792</v>
       </c>
       <c r="I170">
-        <v>0.4715322556842761</v>
+        <v>0.471532255686503</v>
       </c>
       <c r="J170">
-        <v>0.6372606910156047</v>
+        <v>0.6372606910140147</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -13983,31 +13983,31 @@
         </is>
       </c>
       <c r="B171">
-        <v>1.000009373786332</v>
+        <v>1.000009373786331</v>
       </c>
       <c r="C171">
-        <v>0.9965081464482632</v>
+        <v>0.9965081464482622</v>
       </c>
       <c r="D171">
-        <v>1.003522902672478</v>
+        <v>1.003522902672477</v>
       </c>
       <c r="E171">
-        <v>9.373742398373679E-06</v>
+        <v>9.37374239770755E-06</v>
       </c>
       <c r="F171">
-        <v>-0.00349796430172661</v>
+        <v>-0.003497964301727613</v>
       </c>
       <c r="G171">
-        <v>0.003516711786523691</v>
+        <v>0.003516711786522806</v>
       </c>
       <c r="H171">
-        <v>0.001789491068096436</v>
+        <v>0.001789491068096481</v>
       </c>
       <c r="I171">
-        <v>0.0052382169241292</v>
+        <v>0.005238216923641739</v>
       </c>
       <c r="J171">
-        <v>0.9958205267034795</v>
+        <v>0.9958205267038686</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -14063,31 +14063,31 @@
         </is>
       </c>
       <c r="B172">
-        <v>0.9986735842912035</v>
+        <v>0.9986735842912092</v>
       </c>
       <c r="C172">
-        <v>0.9923605098857563</v>
+        <v>0.992360509885762</v>
       </c>
       <c r="D172">
-        <v>1.005026820420189</v>
+        <v>1.005026820420195</v>
       </c>
       <c r="E172">
-        <v>-0.001327296176776645</v>
+        <v>-0.001327296176770864</v>
       </c>
       <c r="F172">
-        <v>-0.007668820493764053</v>
+        <v>-0.007668820493758347</v>
       </c>
       <c r="G172">
-        <v>0.005014228140210818</v>
+        <v>0.005014228140216562</v>
       </c>
       <c r="H172">
-        <v>0.003235531043941912</v>
+        <v>0.003235531043941934</v>
       </c>
       <c r="I172">
-        <v>-0.4102251404021546</v>
+        <v>-0.4102251404003652</v>
       </c>
       <c r="J172">
-        <v>0.6816408004263538</v>
+        <v>0.6816408004276662</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -14143,31 +14143,31 @@
         </is>
       </c>
       <c r="B173">
-        <v>1.219164300367866</v>
+        <v>1.21916430036748</v>
       </c>
       <c r="C173">
-        <v>0.8022258162858393</v>
+        <v>0.802225816285568</v>
       </c>
       <c r="D173">
-        <v>1.852797006923877</v>
+        <v>1.852797006923333</v>
       </c>
       <c r="E173">
-        <v>0.1981656243272063</v>
+        <v>0.1981656243268901</v>
       </c>
       <c r="F173">
-        <v>-0.2203651443068175</v>
+        <v>-0.2203651443071558</v>
       </c>
       <c r="G173">
-        <v>0.6166963929612302</v>
+        <v>0.6166963929609363</v>
       </c>
       <c r="H173">
-        <v>0.2135400302940979</v>
+        <v>0.2135400302941092</v>
       </c>
       <c r="I173">
-        <v>0.9280022300937338</v>
+        <v>0.9280022300922044</v>
       </c>
       <c r="J173">
-        <v>0.3534064128172049</v>
+        <v>0.3534064128179982</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -14223,31 +14223,31 @@
         </is>
       </c>
       <c r="B174">
-        <v>0.994602720351053</v>
+        <v>0.9946027203511111</v>
       </c>
       <c r="C174">
-        <v>0.8007640463958238</v>
+        <v>0.8007640463958745</v>
       </c>
       <c r="D174">
-        <v>1.235363370498691</v>
+        <v>1.235363370498757</v>
       </c>
       <c r="E174">
-        <v>-0.005411897584534496</v>
+        <v>-0.005411897584476116</v>
       </c>
       <c r="F174">
-        <v>-0.2221889490971437</v>
+        <v>-0.2221889490970804</v>
       </c>
       <c r="G174">
-        <v>0.2113651539280746</v>
+        <v>0.2113651539281282</v>
       </c>
       <c r="H174">
-        <v>0.1106025688341822</v>
+        <v>0.1106025688341797</v>
       </c>
       <c r="I174">
-        <v>-0.04893102973628172</v>
+        <v>-0.0489310297357544</v>
       </c>
       <c r="J174">
-        <v>0.9609742603183151</v>
+        <v>0.9609742603187355</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -14303,31 +14303,31 @@
         </is>
       </c>
       <c r="B175">
-        <v>1.029040352741819</v>
+        <v>1.029040352741528</v>
       </c>
       <c r="C175">
-        <v>0.6665620690217102</v>
+        <v>0.6665620690215207</v>
       </c>
       <c r="D175">
-        <v>1.588635322626675</v>
+        <v>1.588635322626227</v>
       </c>
       <c r="E175">
-        <v>0.02862667157554117</v>
+        <v>0.02862667157525829</v>
       </c>
       <c r="F175">
-        <v>-0.4056220168851374</v>
+        <v>-0.4056220168854217</v>
       </c>
       <c r="G175">
-        <v>0.4628753600362199</v>
+        <v>0.4628753600359381</v>
       </c>
       <c r="H175">
-        <v>0.22155952450452</v>
+        <v>0.2215595245045207</v>
       </c>
       <c r="I175">
-        <v>0.1292053304391221</v>
+        <v>0.1292053304378442</v>
       </c>
       <c r="J175">
-        <v>0.8971951784867221</v>
+        <v>0.8971951784877332</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -14383,31 +14383,31 @@
         </is>
       </c>
       <c r="B176">
-        <v>1.180717248689811</v>
+        <v>1.18071724868962</v>
       </c>
       <c r="C176">
-        <v>0.8280618861424277</v>
+        <v>0.8280618861423081</v>
       </c>
       <c r="D176">
-        <v>1.68356163311428</v>
+        <v>1.683561633113978</v>
       </c>
       <c r="E176">
-        <v>0.1661220916916792</v>
+        <v>0.1661220916915174</v>
       </c>
       <c r="F176">
-        <v>-0.1886673856719925</v>
+        <v>-0.1886673856721369</v>
       </c>
       <c r="G176">
-        <v>0.5209115690553506</v>
+        <v>0.5209115690551719</v>
       </c>
       <c r="H176">
-        <v>0.1810183657262102</v>
+        <v>0.1810183657262014</v>
       </c>
       <c r="I176">
-        <v>0.9177084934184981</v>
+        <v>0.9177084934176497</v>
       </c>
       <c r="J176">
-        <v>0.3587714998783195</v>
+        <v>0.3587714998787638</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -14463,31 +14463,31 @@
         </is>
       </c>
       <c r="B177">
-        <v>0.9872734297673305</v>
+        <v>0.9872734297673537</v>
       </c>
       <c r="C177">
-        <v>0.8094614965204919</v>
+        <v>0.8094614965205185</v>
       </c>
       <c r="D177">
-        <v>1.20414476700174</v>
+        <v>1.204144767001758</v>
       </c>
       <c r="E177">
-        <v>-0.01280824674213128</v>
+        <v>-0.01280824674210777</v>
       </c>
       <c r="F177">
-        <v>-0.2113860715163767</v>
+        <v>-0.2113860715163439</v>
       </c>
       <c r="G177">
-        <v>0.185769578032114</v>
+        <v>0.1857695780321284</v>
       </c>
       <c r="H177">
-        <v>0.1013170784466459</v>
+        <v>0.1013170784466413</v>
       </c>
       <c r="I177">
-        <v>-0.1264174504289144</v>
+        <v>-0.1264174504286878</v>
       </c>
       <c r="J177">
-        <v>0.8994014895242791</v>
+        <v>0.8994014895244583</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -14543,31 +14543,31 @@
         </is>
       </c>
       <c r="B178">
-        <v>1.004830478738262</v>
+        <v>1.00483047873812</v>
       </c>
       <c r="C178">
-        <v>0.6921180780195272</v>
+        <v>0.6921180780194485</v>
       </c>
       <c r="D178">
-        <v>1.45883242046002</v>
+        <v>1.458832420459776</v>
       </c>
       <c r="E178">
-        <v>0.004818849410950276</v>
+        <v>0.004818849410809513</v>
       </c>
       <c r="F178">
-        <v>-0.3679987049444226</v>
+        <v>-0.3679987049445363</v>
       </c>
       <c r="G178">
-        <v>0.3776364037663232</v>
+        <v>0.3776364037661554</v>
       </c>
       <c r="H178">
-        <v>0.1902165332098499</v>
+        <v>0.1902165332098362</v>
       </c>
       <c r="I178">
-        <v>0.0253334940429919</v>
+        <v>0.02533349404225359</v>
       </c>
       <c r="J178">
-        <v>0.9797889581153789</v>
+        <v>0.9797889581159677</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -14638,16 +14638,16 @@
         <v>-0.004951603531801096</v>
       </c>
       <c r="G179">
-        <v>0.0003682743607523933</v>
+        <v>0.0003682743607526152</v>
       </c>
       <c r="H179">
-        <v>0.001357136644988385</v>
+        <v>0.001357136644988427</v>
       </c>
       <c r="I179">
-        <v>-1.688602687125872</v>
+        <v>-1.688602687125756</v>
       </c>
       <c r="J179">
-        <v>0.09129559538852751</v>
+        <v>0.09129559538855032</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>1.000359251084722</v>
       </c>
       <c r="C180">
-        <v>0.9982169529767991</v>
+        <v>0.9982169529767989</v>
       </c>
       <c r="D180">
         <v>1.002506146831635</v>
@@ -14715,19 +14715,19 @@
         <v>0.0003591865695021654</v>
       </c>
       <c r="F180">
-        <v>-0.001784638543662926</v>
+        <v>-0.001784638543663148</v>
       </c>
       <c r="G180">
         <v>0.002503011682667388</v>
       </c>
       <c r="H180">
-        <v>0.001093808422029906</v>
+        <v>0.001093808422029922</v>
       </c>
       <c r="I180">
-        <v>0.3283816089436289</v>
+        <v>0.3283816089434928</v>
       </c>
       <c r="J180">
-        <v>0.7426231466602106</v>
+        <v>0.7426231466603135</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -14783,31 +14783,31 @@
         </is>
       </c>
       <c r="B181">
-        <v>0.9951841120644304</v>
+        <v>0.9951841120644308</v>
       </c>
       <c r="C181">
-        <v>0.9923505080054191</v>
+        <v>0.9923505080054194</v>
       </c>
       <c r="D181">
-        <v>0.9980258073290172</v>
+        <v>0.9980258073290177</v>
       </c>
       <c r="E181">
-        <v>-0.00482752169014105</v>
+        <v>-0.004827521690140604</v>
       </c>
       <c r="F181">
-        <v>-0.007678899422380961</v>
+        <v>-0.007678899422380737</v>
       </c>
       <c r="G181">
-        <v>-0.001976143957901004</v>
+        <v>-0.001976143957900559</v>
       </c>
       <c r="H181">
-        <v>0.001454811289764147</v>
+        <v>0.001454811289764185</v>
       </c>
       <c r="I181">
-        <v>-3.318314701093395</v>
+        <v>-3.318314701093043</v>
       </c>
       <c r="J181">
-        <v>0.0009056238800003865</v>
+        <v>0.0009056238800015281</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -14863,31 +14863,31 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.8730426530047248</v>
+        <v>0.8730426530046508</v>
       </c>
       <c r="C182">
-        <v>0.616566177729043</v>
+        <v>0.616566177728997</v>
       </c>
       <c r="D182">
-        <v>1.236207079624285</v>
+        <v>1.236207079624168</v>
       </c>
       <c r="E182">
-        <v>-0.1357708663695804</v>
+        <v>-0.1357708663696652</v>
       </c>
       <c r="F182">
-        <v>-0.4835896178904747</v>
+        <v>-0.4835896178905493</v>
       </c>
       <c r="G182">
-        <v>0.2120478851513139</v>
+        <v>0.2120478851512189</v>
       </c>
       <c r="H182">
-        <v>0.1774618075966928</v>
+        <v>0.1774618075966876</v>
       </c>
       <c r="I182">
-        <v>-0.7650709085424114</v>
+        <v>-0.7650709085429117</v>
       </c>
       <c r="J182">
-        <v>0.4442293218425395</v>
+        <v>0.4442293218422416</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -14943,31 +14943,31 @@
         </is>
       </c>
       <c r="B183">
-        <v>1.019096697935836</v>
+        <v>1.019096697935841</v>
       </c>
       <c r="C183">
-        <v>0.828654542455197</v>
+        <v>0.8286545424552034</v>
       </c>
       <c r="D183">
-        <v>1.253306446214138</v>
+        <v>1.253306446214139</v>
       </c>
       <c r="E183">
-        <v>0.01891664467047458</v>
+        <v>0.01891664467047894</v>
       </c>
       <c r="F183">
-        <v>-0.1879519266739167</v>
+        <v>-0.1879519266739089</v>
       </c>
       <c r="G183">
-        <v>0.2257852160148658</v>
+        <v>0.2257852160148666</v>
       </c>
       <c r="H183">
-        <v>0.1055471289146863</v>
+        <v>0.1055471289146845</v>
       </c>
       <c r="I183">
-        <v>0.1792246256718631</v>
+        <v>0.179224625671907</v>
       </c>
       <c r="J183">
-        <v>0.8577613282877334</v>
+        <v>0.857761328287699</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -15023,31 +15023,31 @@
         </is>
       </c>
       <c r="B184">
-        <v>0.7232930516258406</v>
+        <v>0.7232930516257924</v>
       </c>
       <c r="C184">
-        <v>0.5035422351741202</v>
+        <v>0.5035422351740902</v>
       </c>
       <c r="D184">
-        <v>1.038945299889928</v>
+        <v>1.038945299889851</v>
       </c>
       <c r="E184">
-        <v>-0.323940811662965</v>
+        <v>-0.3239408116630316</v>
       </c>
       <c r="F184">
-        <v>-0.6860876871754382</v>
+        <v>-0.6860876871754977</v>
       </c>
       <c r="G184">
-        <v>0.03820606384950839</v>
+        <v>0.03820606384943444</v>
       </c>
       <c r="H184">
-        <v>0.1847722092696814</v>
+        <v>0.1847722092696777</v>
       </c>
       <c r="I184">
-        <v>-1.753190119571294</v>
+        <v>-1.75319011957169</v>
       </c>
       <c r="J184">
-        <v>0.07956937843209243</v>
+        <v>0.07956937843202483</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -15103,31 +15103,31 @@
         </is>
       </c>
       <c r="B185">
-        <v>0.8785266016626847</v>
+        <v>0.8785266016626153</v>
       </c>
       <c r="C185">
-        <v>0.7225841335078388</v>
+        <v>0.7225841335077788</v>
       </c>
       <c r="D185">
-        <v>1.068123356213457</v>
+        <v>1.068123356213377</v>
       </c>
       <c r="E185">
-        <v>-0.129509091036336</v>
+        <v>-0.1295090910364149</v>
       </c>
       <c r="F185">
-        <v>-0.3249214180133496</v>
+        <v>-0.3249214180134325</v>
       </c>
       <c r="G185">
-        <v>0.06590323594067747</v>
+        <v>0.06590323594060264</v>
       </c>
       <c r="H185">
-        <v>0.09970199887263292</v>
+        <v>0.09970199887263494</v>
       </c>
       <c r="I185">
-        <v>-1.298961831264596</v>
+        <v>-1.298961831265362</v>
       </c>
       <c r="J185">
-        <v>0.1939570283544077</v>
+        <v>0.193957028354145</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -15183,31 +15183,31 @@
         </is>
       </c>
       <c r="B186">
-        <v>1.000442830922416</v>
+        <v>1.000442830922447</v>
       </c>
       <c r="C186">
-        <v>0.8687130502432604</v>
+        <v>0.8687130502432845</v>
       </c>
       <c r="D186">
-        <v>1.152147832548143</v>
+        <v>1.152147832548181</v>
       </c>
       <c r="E186">
-        <v>0.0004427329017402143</v>
+        <v>0.0004427329017706209</v>
       </c>
       <c r="F186">
-        <v>-0.1407424151017391</v>
+        <v>-0.1407424151017113</v>
       </c>
       <c r="G186">
-        <v>0.1416278809052195</v>
+        <v>0.1416278809052525</v>
       </c>
       <c r="H186">
-        <v>0.07203456242927411</v>
+        <v>0.07203456242927542</v>
       </c>
       <c r="I186">
-        <v>0.006146117735842935</v>
+        <v>0.006146117736263953</v>
       </c>
       <c r="J186">
-        <v>0.9950961384234154</v>
+        <v>0.9950961384230794</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -15263,31 +15263,31 @@
         </is>
       </c>
       <c r="B187">
-        <v>0.7494394516424256</v>
+        <v>0.7494394516423666</v>
       </c>
       <c r="C187">
-        <v>0.6081085216255948</v>
+        <v>0.608108521625545</v>
       </c>
       <c r="D187">
-        <v>0.9236172026938093</v>
+        <v>0.9236172026937391</v>
       </c>
       <c r="E187">
-        <v>-0.2884297497028677</v>
+        <v>-0.2884297497029465</v>
       </c>
       <c r="F187">
-        <v>-0.4974019234275475</v>
+        <v>-0.4974019234276295</v>
       </c>
       <c r="G187">
-        <v>-0.07945757597818781</v>
+        <v>-0.07945757597826378</v>
       </c>
       <c r="H187">
-        <v>0.1066204151571283</v>
+        <v>0.1066204151571298</v>
       </c>
       <c r="I187">
-        <v>-2.705201900384686</v>
+        <v>-2.705201900385388</v>
       </c>
       <c r="J187">
-        <v>0.006826288576053897</v>
+        <v>0.006826288576039475</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -15343,31 +15343,31 @@
         </is>
       </c>
       <c r="B188">
-        <v>1.007173542425785</v>
+        <v>1.007173542425791</v>
       </c>
       <c r="C188">
-        <v>0.9993206083297244</v>
+        <v>0.9993206083297311</v>
       </c>
       <c r="D188">
-        <v>1.015088187021362</v>
+        <v>1.015088187021368</v>
       </c>
       <c r="E188">
-        <v>0.007147934961541983</v>
+        <v>0.007147934961548376</v>
       </c>
       <c r="F188">
-        <v>-0.0006796225613793799</v>
+        <v>-0.0006796225613726029</v>
       </c>
       <c r="G188">
-        <v>0.01497549248446336</v>
+        <v>0.01497549248446948</v>
       </c>
       <c r="H188">
-        <v>0.003993725183046287</v>
+        <v>0.003993725183046169</v>
       </c>
       <c r="I188">
-        <v>1.789791393730751</v>
+        <v>1.78979139373242</v>
       </c>
       <c r="J188">
-        <v>0.07348745324851486</v>
+        <v>0.07348745324824647</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -15423,31 +15423,31 @@
         </is>
       </c>
       <c r="B189">
-        <v>0.9961094415200524</v>
+        <v>0.9961094415200502</v>
       </c>
       <c r="C189">
-        <v>0.9915632579660186</v>
+        <v>0.9915632579660159</v>
       </c>
       <c r="D189">
-        <v>1.000676468711384</v>
+        <v>1.000676468711382</v>
       </c>
       <c r="E189">
-        <v>-0.003898146389789219</v>
+        <v>-0.003898146389791448</v>
       </c>
       <c r="F189">
-        <v>-0.008472532789137767</v>
+        <v>-0.008472532789140567</v>
       </c>
       <c r="G189">
-        <v>0.0006762400095594698</v>
+        <v>0.0006762400095574728</v>
       </c>
       <c r="H189">
-        <v>0.002333913498120747</v>
+        <v>0.002333913498120988</v>
       </c>
       <c r="I189">
-        <v>-1.670218880403215</v>
+        <v>-1.670218880404031</v>
       </c>
       <c r="J189">
-        <v>0.09487606582620133</v>
+        <v>0.09487606582603986</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -15503,31 +15503,31 @@
         </is>
       </c>
       <c r="B190">
-        <v>0.9998308435384052</v>
+        <v>0.9998308435384095</v>
       </c>
       <c r="C190">
-        <v>0.9923360769542915</v>
+        <v>0.9923360769542967</v>
       </c>
       <c r="D190">
-        <v>1.007382215467679</v>
+        <v>1.007382215467682</v>
       </c>
       <c r="E190">
-        <v>-0.0001691707701626296</v>
+        <v>-0.00016917077015841</v>
       </c>
       <c r="F190">
-        <v>-0.007693441820397106</v>
+        <v>-0.007693441820391848</v>
       </c>
       <c r="G190">
-        <v>0.00735510028007205</v>
+        <v>0.007355100280075137</v>
       </c>
       <c r="H190">
-        <v>0.003838984343378253</v>
+        <v>0.003838984343377717</v>
       </c>
       <c r="I190">
-        <v>-0.04406654339561892</v>
+        <v>-0.04406654339452749</v>
       </c>
       <c r="J190">
-        <v>0.9648513613686783</v>
+        <v>0.9648513613695483</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -15583,31 +15583,31 @@
         </is>
       </c>
       <c r="B191">
-        <v>1.562919692499381</v>
+        <v>1.562919692499719</v>
       </c>
       <c r="C191">
-        <v>0.9683449343872873</v>
+        <v>0.9683449343874628</v>
       </c>
       <c r="D191">
-        <v>2.522570086813094</v>
+        <v>2.522570086813727</v>
       </c>
       <c r="E191">
-        <v>0.4465556697606423</v>
+        <v>0.4465556697608584</v>
       </c>
       <c r="F191">
-        <v>-0.0321669180016241</v>
+        <v>-0.03216691800144283</v>
       </c>
       <c r="G191">
-        <v>0.9252782575229087</v>
+        <v>0.9252782575231594</v>
       </c>
       <c r="H191">
-        <v>0.2442507064101021</v>
+        <v>0.2442507064101198</v>
       </c>
       <c r="I191">
-        <v>1.828267669412042</v>
+        <v>1.828267669412794</v>
       </c>
       <c r="J191">
-        <v>0.06750938950961752</v>
+        <v>0.06750938950950477</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -15663,31 +15663,31 @@
         </is>
       </c>
       <c r="B192">
-        <v>0.8153605188585885</v>
+        <v>0.8153605188585092</v>
       </c>
       <c r="C192">
-        <v>0.6206981910744797</v>
+        <v>0.620698191074423</v>
       </c>
       <c r="D192">
-        <v>1.07107252006406</v>
+        <v>1.07107252006395</v>
       </c>
       <c r="E192">
-        <v>-0.2041249091234349</v>
+        <v>-0.2041249091235321</v>
       </c>
       <c r="F192">
-        <v>-0.4769103198982095</v>
+        <v>-0.4769103198983007</v>
       </c>
       <c r="G192">
-        <v>0.06866050165133954</v>
+        <v>0.06866050165123649</v>
       </c>
       <c r="H192">
-        <v>0.1391787874300095</v>
+        <v>0.1391787874300065</v>
       </c>
       <c r="I192">
-        <v>-1.466638076769319</v>
+        <v>-1.466638076770049</v>
       </c>
       <c r="J192">
-        <v>0.1424745361595191</v>
+        <v>0.1424745361593206</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -15743,31 +15743,31 @@
         </is>
       </c>
       <c r="B193">
-        <v>1.025427153271878</v>
+        <v>1.025427153272034</v>
       </c>
       <c r="C193">
-        <v>0.6364574891179041</v>
+        <v>0.6364574891179752</v>
       </c>
       <c r="D193">
-        <v>1.652114814651</v>
+        <v>1.65211481465132</v>
       </c>
       <c r="E193">
-        <v>0.02510926067989318</v>
+        <v>0.02510926068004584</v>
       </c>
       <c r="F193">
-        <v>-0.4518376517180273</v>
+        <v>-0.4518376517179156</v>
       </c>
       <c r="G193">
-        <v>0.5020561730778136</v>
+        <v>0.5020561730780071</v>
       </c>
       <c r="H193">
-        <v>0.2433447329440832</v>
+        <v>0.243344732944104</v>
       </c>
       <c r="I193">
-        <v>0.1031839085897241</v>
+        <v>0.1031839085903426</v>
       </c>
       <c r="J193">
-        <v>0.9178170108233331</v>
+        <v>0.9178170108228422</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -15823,31 +15823,31 @@
         </is>
       </c>
       <c r="B194">
-        <v>1.580680731015136</v>
+        <v>1.580680731016043</v>
       </c>
       <c r="C194">
-        <v>1.033328339978296</v>
+        <v>1.033328339978901</v>
       </c>
       <c r="D194">
-        <v>2.417964819831637</v>
+        <v>2.417964819832996</v>
       </c>
       <c r="E194">
-        <v>0.4578555966675753</v>
+        <v>0.4578555966681492</v>
       </c>
       <c r="F194">
-        <v>0.03278499053224697</v>
+        <v>0.03278499053283274</v>
       </c>
       <c r="G194">
-        <v>0.8829262028029035</v>
+        <v>0.8829262028034656</v>
       </c>
       <c r="H194">
-        <v>0.216876743393364</v>
+        <v>0.2168767433933578</v>
       </c>
       <c r="I194">
-        <v>2.11113275450255</v>
+        <v>2.111132754505257</v>
       </c>
       <c r="J194">
-        <v>0.03476090278141041</v>
+        <v>0.03476090278117784</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -15903,31 +15903,31 @@
         </is>
       </c>
       <c r="B195">
-        <v>0.7981804359084189</v>
+        <v>0.7981804359082458</v>
       </c>
       <c r="C195">
-        <v>0.6170819072185439</v>
+        <v>0.6170819072184047</v>
       </c>
       <c r="D195">
-        <v>1.032426977382312</v>
+        <v>1.032426977382097</v>
       </c>
       <c r="E195">
-        <v>-0.225420596930452</v>
+        <v>-0.2254205969306689</v>
       </c>
       <c r="F195">
-        <v>-0.4827535131279611</v>
+        <v>-0.4827535131281867</v>
       </c>
       <c r="G195">
-        <v>0.03191231926705716</v>
+        <v>0.03191231926684875</v>
       </c>
       <c r="H195">
-        <v>0.1312947167536334</v>
+        <v>0.1312947167536378</v>
       </c>
       <c r="I195">
-        <v>-1.716905314274298</v>
+        <v>-1.716905314275894</v>
       </c>
       <c r="J195">
-        <v>0.08599647375706335</v>
+        <v>0.08599647375677187</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -15983,31 +15983,31 @@
         </is>
       </c>
       <c r="B196">
-        <v>1.042153285040306</v>
+        <v>1.042153285040765</v>
       </c>
       <c r="C196">
-        <v>0.6868030075907893</v>
+        <v>0.6868030075911039</v>
       </c>
       <c r="D196">
-        <v>1.581360968889947</v>
+        <v>1.581360968890617</v>
       </c>
       <c r="E196">
-        <v>0.04128903907665832</v>
+        <v>0.04128903907709894</v>
       </c>
       <c r="F196">
-        <v>-0.3757077708321364</v>
+        <v>-0.3757077708316783</v>
       </c>
       <c r="G196">
-        <v>0.4582858489854529</v>
+        <v>0.4582858489858762</v>
       </c>
       <c r="H196">
-        <v>0.212757383910119</v>
+        <v>0.2127573839101101</v>
       </c>
       <c r="I196">
-        <v>0.1940663036827955</v>
+        <v>0.1940663036848753</v>
       </c>
       <c r="J196">
-        <v>0.8461239657666013</v>
+        <v>0.846123965764973</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -16063,31 +16063,31 @@
         </is>
       </c>
       <c r="B197">
-        <v>1.001940964182562</v>
+        <v>1.001940964182563</v>
       </c>
       <c r="C197">
-        <v>0.9986610471578637</v>
+        <v>0.9986610471578643</v>
       </c>
       <c r="D197">
-        <v>1.005231653486523</v>
+        <v>1.005231653486524</v>
       </c>
       <c r="E197">
-        <v>0.001939082945465624</v>
+        <v>0.001939082945466067</v>
       </c>
       <c r="F197">
-        <v>-0.001339850040453235</v>
+        <v>-0.001339850040452679</v>
       </c>
       <c r="G197">
-        <v>0.00521801593138458</v>
+        <v>0.0052180159313848</v>
       </c>
       <c r="H197">
-        <v>0.001672955733769952</v>
+        <v>0.001672955733769889</v>
       </c>
       <c r="I197">
-        <v>1.159076062996606</v>
+        <v>1.159076062996875</v>
       </c>
       <c r="J197">
-        <v>0.2464251819836818</v>
+        <v>0.2464251819835725</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -16143,31 +16143,31 @@
         </is>
       </c>
       <c r="B198">
-        <v>0.9974596332719438</v>
+        <v>0.9974596332719434</v>
       </c>
       <c r="C198">
-        <v>0.9947151275885194</v>
+        <v>0.9947151275885191</v>
       </c>
       <c r="D198">
-        <v>1.000211711285614</v>
+        <v>1.000211711285613</v>
       </c>
       <c r="E198">
-        <v>-0.002543598934766743</v>
+        <v>-0.002543598934767076</v>
       </c>
       <c r="F198">
-        <v>-0.005298886747475476</v>
+        <v>-0.00529888674747581</v>
       </c>
       <c r="G198">
-        <v>0.0002116888779420568</v>
+        <v>0.0002116888779416128</v>
       </c>
       <c r="H198">
-        <v>0.001405784919744483</v>
+        <v>0.001405784919744465</v>
       </c>
       <c r="I198">
-        <v>-1.809379869595606</v>
+        <v>-1.809379869595876</v>
       </c>
       <c r="J198">
-        <v>0.07039200836150875</v>
+        <v>0.07039200836146679</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>0.9963045803558083</v>
       </c>
       <c r="C199">
-        <v>0.9932890868459305</v>
+        <v>0.9932890868459306</v>
       </c>
       <c r="D199">
         <v>0.9993292285027685</v>
@@ -16235,19 +16235,19 @@
         <v>-0.003702264575831631</v>
       </c>
       <c r="F199">
-        <v>-0.00673353258657935</v>
+        <v>-0.006733532586579238</v>
       </c>
       <c r="G199">
         <v>-0.0006709965650839366</v>
       </c>
       <c r="H199">
-        <v>0.00154659373062869</v>
+        <v>0.001546593730628677</v>
       </c>
       <c r="I199">
-        <v>-2.393818429825572</v>
+        <v>-2.393818429825557</v>
       </c>
       <c r="J199">
-        <v>0.01667400074674012</v>
+        <v>0.01667400074674077</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -16303,31 +16303,31 @@
         </is>
       </c>
       <c r="B200">
-        <v>1.221430796423645</v>
+        <v>1.221430796423945</v>
       </c>
       <c r="C200">
-        <v>0.821552108136659</v>
+        <v>0.8215521081368297</v>
       </c>
       <c r="D200">
-        <v>1.815944692584168</v>
+        <v>1.815944692584682</v>
       </c>
       <c r="E200">
-        <v>0.20002295552509</v>
+        <v>0.2000229555253356</v>
       </c>
       <c r="F200">
-        <v>-0.1965599130396811</v>
+        <v>-0.1965599130394734</v>
       </c>
       <c r="G200">
-        <v>0.5966058240898612</v>
+        <v>0.5966058240901446</v>
       </c>
       <c r="H200">
-        <v>0.2023419163275276</v>
+        <v>0.2023419163275469</v>
       </c>
       <c r="I200">
-        <v>0.9885393948790923</v>
+        <v>0.9885393948802116</v>
       </c>
       <c r="J200">
-        <v>0.3228885507731393</v>
+        <v>0.3228885507725914</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -16383,31 +16383,31 @@
         </is>
       </c>
       <c r="B201">
-        <v>0.8130489680709797</v>
+        <v>0.813048968070923</v>
       </c>
       <c r="C201">
-        <v>0.6267104536711283</v>
+        <v>0.6267104536710902</v>
       </c>
       <c r="D201">
-        <v>1.05479112500679</v>
+        <v>1.054791125006707</v>
       </c>
       <c r="E201">
-        <v>-0.2069639399185418</v>
+        <v>-0.2069639399186116</v>
       </c>
       <c r="F201">
-        <v>-0.4672706413877877</v>
+        <v>-0.4672706413878485</v>
       </c>
       <c r="G201">
-        <v>0.05334276155070401</v>
+        <v>0.05334276155062528</v>
       </c>
       <c r="H201">
-        <v>0.1328119820172779</v>
+        <v>0.1328119820172733</v>
       </c>
       <c r="I201">
-        <v>-1.558322801715416</v>
+        <v>-1.558322801715995</v>
       </c>
       <c r="J201">
-        <v>0.1191567463872836</v>
+        <v>0.1191567463871461</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -16463,31 +16463,31 @@
         </is>
       </c>
       <c r="B202">
-        <v>0.7798971386189057</v>
+        <v>0.7798971386190301</v>
       </c>
       <c r="C202">
-        <v>0.5288339685954848</v>
+        <v>0.5288339685955524</v>
       </c>
       <c r="D202">
-        <v>1.15015218943171</v>
+        <v>1.150152189431929</v>
       </c>
       <c r="E202">
-        <v>-0.2485932415600882</v>
+        <v>-0.2485932415599288</v>
       </c>
       <c r="F202">
-        <v>-0.6370807553756194</v>
+        <v>-0.6370807553754915</v>
       </c>
       <c r="G202">
-        <v>0.1398942722554432</v>
+        <v>0.1398942722556341</v>
       </c>
       <c r="H202">
-        <v>0.1982115573958866</v>
+        <v>0.1982115573959026</v>
       </c>
       <c r="I202">
-        <v>-1.254181364730285</v>
+        <v>-1.254181364729379</v>
       </c>
       <c r="J202">
-        <v>0.2097760916870026</v>
+        <v>0.2097760916873318</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -16543,31 +16543,31 @@
         </is>
       </c>
       <c r="B203">
-        <v>1.15129831446241</v>
+        <v>1.151298314462562</v>
       </c>
       <c r="C203">
-        <v>0.9141110774168814</v>
+        <v>0.914111077417003</v>
       </c>
       <c r="D203">
-        <v>1.450029259714897</v>
+        <v>1.450029259715085</v>
       </c>
       <c r="E203">
-        <v>0.1408902746665399</v>
+        <v>0.1408902746666712</v>
       </c>
       <c r="F203">
-        <v>-0.08980318600952986</v>
+        <v>-0.08980318600939674</v>
       </c>
       <c r="G203">
-        <v>0.3715837353426096</v>
+        <v>0.3715837353427392</v>
       </c>
       <c r="H203">
-        <v>0.1177029080614493</v>
+        <v>0.1177029080614484</v>
       </c>
       <c r="I203">
-        <v>1.196999097023033</v>
+        <v>1.196999097024158</v>
       </c>
       <c r="J203">
-        <v>0.2313069067036692</v>
+        <v>0.2313069067032309</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -16623,31 +16623,31 @@
         </is>
       </c>
       <c r="B204">
-        <v>0.830610471459333</v>
+        <v>0.8306104714592668</v>
       </c>
       <c r="C204">
-        <v>0.6928844559719354</v>
+        <v>0.6928844559718742</v>
       </c>
       <c r="D204">
-        <v>0.9957125597948754</v>
+        <v>0.9957125597948048</v>
       </c>
       <c r="E204">
-        <v>-0.185594340762457</v>
+        <v>-0.1855943407625366</v>
       </c>
       <c r="F204">
-        <v>-0.3668920238924861</v>
+        <v>-0.3668920238925744</v>
       </c>
       <c r="G204">
-        <v>-0.004296657632427846</v>
+        <v>-0.00429665763249876</v>
       </c>
       <c r="H204">
-        <v>0.0925005176422027</v>
+        <v>0.09250051764220714</v>
       </c>
       <c r="I204">
-        <v>-2.00641407738221</v>
+        <v>-2.006414077382975</v>
       </c>
       <c r="J204">
-        <v>0.04481208760901035</v>
+        <v>0.04481208760892898</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -16703,31 +16703,31 @@
         </is>
       </c>
       <c r="B205">
-        <v>0.8010330104809716</v>
+        <v>0.8010330104810037</v>
       </c>
       <c r="C205">
-        <v>0.6425624066669833</v>
+        <v>0.6425624066670123</v>
       </c>
       <c r="D205">
-        <v>0.9985860940861955</v>
+        <v>0.9985860940862306</v>
       </c>
       <c r="E205">
-        <v>-0.2218531211762208</v>
+        <v>-0.2218531211761808</v>
       </c>
       <c r="F205">
-        <v>-0.4422913359304765</v>
+        <v>-0.4422913359304314</v>
       </c>
       <c r="G205">
-        <v>-0.001414906421965211</v>
+        <v>-0.001414906421930078</v>
       </c>
       <c r="H205">
-        <v>0.1124705435880681</v>
+        <v>0.1124705435880655</v>
       </c>
       <c r="I205">
-        <v>-1.972544224457337</v>
+        <v>-1.972544224457025</v>
       </c>
       <c r="J205">
-        <v>0.0485475129878369</v>
+        <v>0.04854751298787229</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -16783,31 +16783,31 @@
         </is>
       </c>
       <c r="B206">
-        <v>1.061523154970286</v>
+        <v>1.0615231549706</v>
       </c>
       <c r="C206">
-        <v>0.828230869806863</v>
+        <v>0.8282308698071357</v>
       </c>
       <c r="D206">
-        <v>1.360528144526706</v>
+        <v>1.360528144527062</v>
       </c>
       <c r="E206">
-        <v>0.05970481536677451</v>
+        <v>0.05970481536707008</v>
       </c>
       <c r="F206">
-        <v>-0.1884633351930966</v>
+        <v>-0.1884633351927674</v>
       </c>
       <c r="G206">
-        <v>0.3078729659266459</v>
+        <v>0.3078729659269075</v>
       </c>
       <c r="H206">
-        <v>0.1266187299957499</v>
+        <v>0.1266187299957327</v>
       </c>
       <c r="I206">
-        <v>0.4715322556842785</v>
+        <v>0.4715322556866761</v>
       </c>
       <c r="J206">
-        <v>0.6372606910156029</v>
+        <v>0.6372606910138912</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -16863,31 +16863,31 @@
         </is>
       </c>
       <c r="B207">
-        <v>1.000389690728252</v>
+        <v>1.000389690728214</v>
       </c>
       <c r="C207">
-        <v>0.8646840482792109</v>
+        <v>0.8646840482791784</v>
       </c>
       <c r="D207">
-        <v>1.157393310663007</v>
+        <v>1.157393310662964</v>
       </c>
       <c r="E207">
-        <v>0.0003896148185402922</v>
+        <v>0.0003896148185027812</v>
       </c>
       <c r="F207">
-        <v>-0.1453911008796674</v>
+        <v>-0.1453911008797049</v>
       </c>
       <c r="G207">
-        <v>0.1461703305167481</v>
+        <v>0.1461703305167105</v>
       </c>
       <c r="H207">
         <v>0.07437928290933274</v>
       </c>
       <c r="I207">
-        <v>0.005238216924130644</v>
+        <v>0.005238216923625352</v>
       </c>
       <c r="J207">
-        <v>0.9958205267034784</v>
+        <v>0.9958205267038815</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -16943,31 +16943,31 @@
         </is>
       </c>
       <c r="B208">
-        <v>0.948448937286239</v>
+        <v>0.9484489372864664</v>
       </c>
       <c r="C208">
-        <v>0.7365322503061198</v>
+        <v>0.736532250306315</v>
       </c>
       <c r="D208">
-        <v>1.221338761833606</v>
+        <v>1.221338761833868</v>
       </c>
       <c r="E208">
-        <v>-0.05292732628423919</v>
+        <v>-0.05292732628399946</v>
       </c>
       <c r="F208">
-        <v>-0.305802255435131</v>
+        <v>-0.305802255434866</v>
       </c>
       <c r="G208">
-        <v>0.1999476028666526</v>
+        <v>0.1999476028668669</v>
       </c>
       <c r="H208">
-        <v>0.1290201917716535</v>
+        <v>0.1290201917716405</v>
       </c>
       <c r="I208">
-        <v>-0.4102251404021526</v>
+        <v>-0.410225140400336</v>
       </c>
       <c r="J208">
-        <v>0.6816408004263552</v>
+        <v>0.6816408004276876</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -17023,31 +17023,31 @@
         </is>
       </c>
       <c r="B209">
-        <v>1.149854059005023</v>
+        <v>1.149854059004763</v>
       </c>
       <c r="C209">
-        <v>0.8561774229993456</v>
+        <v>0.8561774229991704</v>
       </c>
       <c r="D209">
-        <v>1.544264449742839</v>
+        <v>1.544264449742456</v>
       </c>
       <c r="E209">
-        <v>0.1396350291089872</v>
+        <v>0.139635029108761</v>
       </c>
       <c r="F209">
-        <v>-0.1552776544587759</v>
+        <v>-0.1552776544589805</v>
       </c>
       <c r="G209">
-        <v>0.4345477126767503</v>
+        <v>0.4345477126765024</v>
       </c>
       <c r="H209">
-        <v>0.1504684197740351</v>
+        <v>0.150468419774024</v>
       </c>
       <c r="I209">
-        <v>0.928002230093751</v>
+        <v>0.9280022300923156</v>
       </c>
       <c r="J209">
-        <v>0.3534064128171959</v>
+        <v>0.3534064128179405</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -17103,31 +17103,31 @@
         </is>
       </c>
       <c r="B210">
-        <v>0.9961297333174776</v>
+        <v>0.9961297333175196</v>
       </c>
       <c r="C210">
-        <v>0.8528218722022944</v>
+        <v>0.8528218722023343</v>
       </c>
       <c r="D210">
-        <v>1.163518992584861</v>
+        <v>1.163518992584905</v>
       </c>
       <c r="E210">
-        <v>-0.003877775545081291</v>
+        <v>-0.00387777554503905</v>
       </c>
       <c r="F210">
-        <v>-0.1592045783826871</v>
+        <v>-0.1592045783826404</v>
       </c>
       <c r="G210">
-        <v>0.1514490272925247</v>
+        <v>0.1514490272925625</v>
       </c>
       <c r="H210">
-        <v>0.07924982502882906</v>
+        <v>0.07924982502882678</v>
       </c>
       <c r="I210">
-        <v>-0.04893102973628789</v>
+        <v>-0.04893102973575655</v>
       </c>
       <c r="J210">
-        <v>0.9609742603183103</v>
+        <v>0.9609742603187337</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -17183,31 +17183,31 @@
         </is>
       </c>
       <c r="B211">
-        <v>1.019699273849724</v>
+        <v>1.019699273849524</v>
       </c>
       <c r="C211">
-        <v>0.7584998584962419</v>
+        <v>0.7584998584961118</v>
       </c>
       <c r="D211">
-        <v>1.370846147751531</v>
+        <v>1.370846147751228</v>
       </c>
       <c r="E211">
-        <v>0.01950775426630697</v>
+        <v>0.01950775426611034</v>
       </c>
       <c r="F211">
-        <v>-0.2764126667509282</v>
+        <v>-0.2764126667510998</v>
       </c>
       <c r="G211">
-        <v>0.3154281752835419</v>
+        <v>0.3154281752833205</v>
       </c>
       <c r="H211">
-        <v>0.1509825809818026</v>
+        <v>0.1509825809817899</v>
       </c>
       <c r="I211">
-        <v>0.1292053304391324</v>
+        <v>0.129205330437842</v>
       </c>
       <c r="J211">
-        <v>0.897195178486714</v>
+        <v>0.897195178487735</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -17263,31 +17263,31 @@
         </is>
       </c>
       <c r="B212">
-        <v>1.125158187385421</v>
+        <v>1.125158187385271</v>
       </c>
       <c r="C212">
-        <v>0.8746533281777511</v>
+        <v>0.8746533281776425</v>
       </c>
       <c r="D212">
-        <v>1.44740882570925</v>
+        <v>1.447408825709043</v>
       </c>
       <c r="E212">
-        <v>0.1179236367808451</v>
+        <v>0.1179236367807116</v>
       </c>
       <c r="F212">
-        <v>-0.1339276674993249</v>
+        <v>-0.133927667499449</v>
       </c>
       <c r="G212">
-        <v>0.3697749410610149</v>
+        <v>0.3697749410608723</v>
       </c>
       <c r="H212">
-        <v>0.1284979245877684</v>
+        <v>0.1284979245877637</v>
       </c>
       <c r="I212">
-        <v>0.9177084934184999</v>
+        <v>0.9177084934174957</v>
       </c>
       <c r="J212">
-        <v>0.3587714998783186</v>
+        <v>0.3587714998788444</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -17343,31 +17343,31 @@
         </is>
       </c>
       <c r="B213">
-        <v>0.9907298751977912</v>
+        <v>0.9907298751978094</v>
       </c>
       <c r="C213">
-        <v>0.8575234151719658</v>
+        <v>0.8575234151719873</v>
       </c>
       <c r="D213">
-        <v>1.144628436079024</v>
+        <v>1.144628436079038</v>
       </c>
       <c r="E213">
-        <v>-0.009313359812532392</v>
+        <v>-0.009313359812514015</v>
       </c>
       <c r="F213">
-        <v>-0.1537067939918607</v>
+        <v>-0.1537067939918357</v>
       </c>
       <c r="G213">
-        <v>0.1350800743667958</v>
+        <v>0.1350800743668076</v>
       </c>
       <c r="H213">
-        <v>0.07367147320985758</v>
+        <v>0.07367147320985422</v>
       </c>
       <c r="I213">
-        <v>-0.1264174504289156</v>
+        <v>-0.1264174504286721</v>
       </c>
       <c r="J213">
-        <v>0.8994014895242781</v>
+        <v>0.8994014895244709</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -17423,31 +17423,31 @@
         </is>
       </c>
       <c r="B214">
-        <v>1.003317683587903</v>
+        <v>1.003317683587787</v>
       </c>
       <c r="C214">
-        <v>0.7765140399546014</v>
+        <v>0.7765140399545249</v>
       </c>
       <c r="D214">
-        <v>1.296365966878136</v>
+        <v>1.296365966877965</v>
       </c>
       <c r="E214">
-        <v>0.00331219221810738</v>
+        <v>0.003312192217992077</v>
       </c>
       <c r="F214">
-        <v>-0.2529405554820311</v>
+        <v>-0.2529405554821297</v>
       </c>
       <c r="G214">
-        <v>0.259564939918246</v>
+        <v>0.259564939918114</v>
       </c>
       <c r="H214">
-        <v>0.1307436002505289</v>
+        <v>0.1307436002505204</v>
       </c>
       <c r="I214">
-        <v>0.02533349404300251</v>
+        <v>0.02533349404212178</v>
       </c>
       <c r="J214">
-        <v>0.9797889581153703</v>
+        <v>0.9797889581160728</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -17503,31 +17503,31 @@
         </is>
       </c>
       <c r="B215">
-        <v>0.8658176023855514</v>
+        <v>0.8658176023855561</v>
       </c>
       <c r="C215">
-        <v>0.7324823100633582</v>
+        <v>0.732482310063358</v>
       </c>
       <c r="D215">
-        <v>1.02342419782919</v>
+        <v>1.023424197829202</v>
       </c>
       <c r="E215">
-        <v>-0.1440810134052816</v>
+        <v>-0.1440810134052763</v>
       </c>
       <c r="F215">
-        <v>-0.3113160884666853</v>
+        <v>-0.3113160884666856</v>
       </c>
       <c r="G215">
-        <v>0.02315406165612195</v>
+        <v>0.02315406165613302</v>
       </c>
       <c r="H215">
-        <v>0.08532558576613278</v>
+        <v>0.08532558576613564</v>
       </c>
       <c r="I215">
-        <v>-1.688602687125881</v>
+        <v>-1.688602687125762</v>
       </c>
       <c r="J215">
-        <v>0.09129559538852605</v>
+        <v>0.09129559538854892</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -17583,31 +17583,31 @@
         </is>
       </c>
       <c r="B216">
-        <v>1.023514674229761</v>
+        <v>1.023514674229751</v>
       </c>
       <c r="C216">
-        <v>0.8909370741053306</v>
+        <v>0.8909370741053205</v>
       </c>
       <c r="D216">
-        <v>1.175820738423782</v>
+        <v>1.175820738423773</v>
       </c>
       <c r="E216">
-        <v>0.02324246331956602</v>
+        <v>0.02324246331955691</v>
       </c>
       <c r="F216">
-        <v>-0.1154814779050539</v>
+        <v>-0.1154814779050653</v>
       </c>
       <c r="G216">
-        <v>0.161966404544186</v>
+        <v>0.161966404544179</v>
       </c>
       <c r="H216">
-        <v>0.07077882161042587</v>
+        <v>0.07077882161042699</v>
       </c>
       <c r="I216">
-        <v>0.3283816089436331</v>
+        <v>0.3283816089434976</v>
       </c>
       <c r="J216">
-        <v>0.7426231466602076</v>
+        <v>0.7426231466603099</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -17663,31 +17663,31 @@
         </is>
       </c>
       <c r="B217">
-        <v>0.7426217252177695</v>
+        <v>0.7426217252177866</v>
       </c>
       <c r="C217">
-        <v>0.6229260717939242</v>
+        <v>0.6229260717939353</v>
       </c>
       <c r="D217">
-        <v>0.8853169769844832</v>
+        <v>0.8853169769845085</v>
       </c>
       <c r="E217">
-        <v>-0.2975684820546928</v>
+        <v>-0.2975684820546697</v>
       </c>
       <c r="F217">
-        <v>-0.4733274320931796</v>
+        <v>-0.4733274320931617</v>
       </c>
       <c r="G217">
-        <v>-0.1218095320162062</v>
+        <v>-0.1218095320161776</v>
       </c>
       <c r="H217">
-        <v>0.08967458148458385</v>
+        <v>0.08967458148458662</v>
       </c>
       <c r="I217">
-        <v>-3.318314701093402</v>
+        <v>-3.318314701093043</v>
       </c>
       <c r="J217">
-        <v>0.0009056238800003628</v>
+        <v>0.0009056238800015281</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -17743,31 +17743,31 @@
         </is>
       </c>
       <c r="B218">
-        <v>0.9083309882371873</v>
+        <v>0.9083309882371394</v>
       </c>
       <c r="C218">
-        <v>0.7100250213829886</v>
+        <v>0.7100250213829586</v>
       </c>
       <c r="D218">
-        <v>1.162022688418615</v>
+        <v>1.162022688418542</v>
       </c>
       <c r="E218">
-        <v>-0.09614644231346005</v>
+        <v>-0.09614644231351273</v>
       </c>
       <c r="F218">
-        <v>-0.3424550681832479</v>
+        <v>-0.3424550681832901</v>
       </c>
       <c r="G218">
-        <v>0.1501621835563278</v>
+        <v>0.1501621835562646</v>
       </c>
       <c r="H218">
-        <v>0.1256699754753858</v>
+        <v>0.1256699754753804</v>
       </c>
       <c r="I218">
-        <v>-0.7650709085424439</v>
+        <v>-0.7650709085428961</v>
       </c>
       <c r="J218">
-        <v>0.4442293218425202</v>
+        <v>0.4442293218422509</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -17823,31 +17823,31 @@
         </is>
       </c>
       <c r="B219">
-        <v>1.013812991039286</v>
+        <v>1.013812991039288</v>
       </c>
       <c r="C219">
-        <v>0.8725774728462018</v>
+        <v>0.8725774728462062</v>
       </c>
       <c r="D219">
         <v>1.177908910996128</v>
       </c>
       <c r="E219">
-        <v>0.01371846117729136</v>
+        <v>0.01371846117729377</v>
       </c>
       <c r="F219">
-        <v>-0.136303834754449</v>
+        <v>-0.1363038347544439</v>
       </c>
       <c r="G219">
-        <v>0.1637407571090316</v>
+        <v>0.1637407571090314</v>
       </c>
       <c r="H219">
-        <v>0.07654339422310669</v>
+        <v>0.07654339422310531</v>
       </c>
       <c r="I219">
-        <v>0.1792246256718785</v>
+        <v>0.179224625671913</v>
       </c>
       <c r="J219">
-        <v>0.8577613282877214</v>
+        <v>0.8577613282876942</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -17903,31 +17903,31 @@
         </is>
       </c>
       <c r="B220">
-        <v>0.7986704607743498</v>
+        <v>0.7986704607743186</v>
       </c>
       <c r="C220">
-        <v>0.6211841067365634</v>
+        <v>0.621184106736544</v>
       </c>
       <c r="D220">
-        <v>1.026868681918848</v>
+        <v>1.0268686819188</v>
       </c>
       <c r="E220">
-        <v>-0.2248068578739997</v>
+        <v>-0.2248068578740388</v>
       </c>
       <c r="F220">
-        <v>-0.4761277728118434</v>
+        <v>-0.4761277728118746</v>
       </c>
       <c r="G220">
-        <v>0.02651405706384377</v>
+        <v>0.02651405706379707</v>
       </c>
       <c r="H220">
-        <v>0.1282273128079041</v>
+        <v>0.1282273128079001</v>
       </c>
       <c r="I220">
-        <v>-1.75319011957133</v>
+        <v>-1.753190119571689</v>
       </c>
       <c r="J220">
-        <v>0.07956937843208628</v>
+        <v>0.07956937843202497</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -17983,31 +17983,31 @@
         </is>
       </c>
       <c r="B221">
-        <v>0.8832850392495351</v>
+        <v>0.8832850392494698</v>
       </c>
       <c r="C221">
-        <v>0.7324434914673836</v>
+        <v>0.7324434914673266</v>
       </c>
       <c r="D221">
-        <v>1.065191335100826</v>
+        <v>1.065191335100751</v>
       </c>
       <c r="E221">
-        <v>-0.1241073227122732</v>
+        <v>-0.1241073227123471</v>
       </c>
       <c r="F221">
-        <v>-0.3113690858211494</v>
+        <v>-0.3113690858212273</v>
       </c>
       <c r="G221">
-        <v>0.06315444039660287</v>
+        <v>0.06315444039653303</v>
       </c>
       <c r="H221">
-        <v>0.09554347150558536</v>
+        <v>0.0955434715055874</v>
       </c>
       <c r="I221">
-        <v>-1.298961831264609</v>
+        <v>-1.298961831265355</v>
       </c>
       <c r="J221">
-        <v>0.1939570283544031</v>
+        <v>0.1939570283541472</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -18063,31 +18063,31 @@
         </is>
       </c>
       <c r="B222">
-        <v>1.000435344154069</v>
+        <v>1.000435344154099</v>
       </c>
       <c r="C222">
-        <v>0.8707821430835726</v>
+        <v>0.8707821430835967</v>
       </c>
       <c r="D222">
-        <v>1.149392974789807</v>
+        <v>1.149392974789845</v>
       </c>
       <c r="E222">
-        <v>0.0004352494192965653</v>
+        <v>0.0004352494193269721</v>
       </c>
       <c r="F222">
-        <v>-0.1383634561668984</v>
+        <v>-0.1383634561668707</v>
       </c>
       <c r="G222">
-        <v>0.1392339550054916</v>
+        <v>0.1392339550055249</v>
       </c>
       <c r="H222">
-        <v>0.07081696739379988</v>
+        <v>0.07081696739380126</v>
       </c>
       <c r="I222">
-        <v>0.006146117735828629</v>
+        <v>0.006146117736258234</v>
       </c>
       <c r="J222">
-        <v>0.9950961384234268</v>
+        <v>0.9950961384230841</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -18143,31 +18143,31 @@
         </is>
       </c>
       <c r="B223">
-        <v>0.7652801590513234</v>
+        <v>0.7652801590512683</v>
       </c>
       <c r="C223">
-        <v>0.6304438768718926</v>
+        <v>0.6304438768718456</v>
       </c>
       <c r="D223">
-        <v>0.9289545720445228</v>
+        <v>0.9289545720444584</v>
       </c>
       <c r="E223">
-        <v>-0.2675132912160152</v>
+        <v>-0.2675132912160872</v>
       </c>
       <c r="F223">
-        <v>-0.4613311412236637</v>
+        <v>-0.4613311412237384</v>
       </c>
       <c r="G223">
-        <v>-0.07369544120836675</v>
+        <v>-0.07369544120843607</v>
       </c>
       <c r="H223">
-        <v>0.09888847526610642</v>
+        <v>0.09888847526610782</v>
       </c>
       <c r="I223">
-        <v>-2.705201900384687</v>
+        <v>-2.705201900385377</v>
       </c>
       <c r="J223">
-        <v>0.006826288576053876</v>
+        <v>0.006826288576039702</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -18223,31 +18223,31 @@
         </is>
       </c>
       <c r="B224">
-        <v>1.340001960911868</v>
+        <v>1.34000196091228</v>
       </c>
       <c r="C224">
-        <v>0.9725565663020882</v>
+        <v>0.9725565663023847</v>
       </c>
       <c r="D224">
-        <v>1.846273335107907</v>
+        <v>1.846273335108481</v>
       </c>
       <c r="E224">
-        <v>0.2926710773288147</v>
+        <v>0.2926710773291227</v>
       </c>
       <c r="F224">
-        <v>-0.02782703931777416</v>
+        <v>-0.02782703931746925</v>
       </c>
       <c r="G224">
-        <v>0.6131691939754036</v>
+        <v>0.6131691939757147</v>
       </c>
       <c r="H224">
-        <v>0.1635224520320971</v>
+        <v>0.1635224520320987</v>
       </c>
       <c r="I224">
-        <v>1.789791393730859</v>
+        <v>1.789791393732725</v>
       </c>
       <c r="J224">
-        <v>0.07348745324849724</v>
+        <v>0.07348745324819735</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -18303,31 +18303,31 @@
         </is>
       </c>
       <c r="B225">
-        <v>0.8504203986472997</v>
+        <v>0.8504203986472152</v>
       </c>
       <c r="C225">
-        <v>0.7031700664791795</v>
+        <v>0.7031700664790929</v>
       </c>
       <c r="D225">
-        <v>1.028506315771686</v>
+        <v>1.028506315771608</v>
       </c>
       <c r="E225">
-        <v>-0.1620244651215541</v>
+        <v>-0.1620244651216535</v>
       </c>
       <c r="F225">
-        <v>-0.3521565010951536</v>
+        <v>-0.3521565010952767</v>
       </c>
       <c r="G225">
-        <v>0.02810757085204531</v>
+        <v>0.02810757085196997</v>
       </c>
       <c r="H225">
-        <v>0.09700792334621285</v>
+        <v>0.09700792334622506</v>
       </c>
       <c r="I225">
-        <v>-1.670218880403232</v>
+        <v>-1.670218880404045</v>
       </c>
       <c r="J225">
-        <v>0.09487606582619813</v>
+        <v>0.09487606582603685</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -18383,31 +18383,31 @@
         </is>
       </c>
       <c r="B226">
-        <v>0.9932768404677821</v>
+        <v>0.993276840468006</v>
       </c>
       <c r="C226">
-        <v>0.7358094769218189</v>
+        <v>0.7358094769220059</v>
       </c>
       <c r="D226">
-        <v>1.340834703484646</v>
+        <v>1.34083470348491</v>
       </c>
       <c r="E226">
-        <v>-0.006745861780370734</v>
+        <v>-0.006745861780145286</v>
       </c>
       <c r="F226">
-        <v>-0.3067840566420024</v>
+        <v>-0.3067840566417481</v>
       </c>
       <c r="G226">
-        <v>0.2932923330812608</v>
+        <v>0.2932923330814576</v>
       </c>
       <c r="H226">
-        <v>0.1530835246097861</v>
+        <v>0.1530835246097714</v>
       </c>
       <c r="I226">
-        <v>-0.04406654339561417</v>
+        <v>-0.0440665433941457</v>
       </c>
       <c r="J226">
-        <v>0.964851361368682</v>
+        <v>0.9648513613698525</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -18463,31 +18463,31 @@
         </is>
       </c>
       <c r="B227">
-        <v>1.369793630518813</v>
+        <v>1.36979363051894</v>
       </c>
       <c r="C227">
-        <v>0.9775889119397663</v>
+        <v>0.9775889119398434</v>
       </c>
       <c r="D227">
-        <v>1.919349296307813</v>
+        <v>1.919349296308018</v>
       </c>
       <c r="E227">
-        <v>0.3146600938356933</v>
+        <v>0.3146600938357863</v>
       </c>
       <c r="F227">
-        <v>-0.02266603275293556</v>
+        <v>-0.02266603275285663</v>
       </c>
       <c r="G227">
-        <v>0.6519862204243223</v>
+        <v>0.6519862204244293</v>
       </c>
       <c r="H227">
-        <v>0.1721083291577878</v>
+        <v>0.172108329157795</v>
       </c>
       <c r="I227">
-        <v>1.828267669411949</v>
+        <v>1.828267669412413</v>
       </c>
       <c r="J227">
-        <v>0.06750938950963156</v>
+        <v>0.06750938950956187</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -18543,31 +18543,31 @@
         </is>
       </c>
       <c r="B228">
-        <v>0.8639320233290809</v>
+        <v>0.863932023329154</v>
       </c>
       <c r="C228">
-        <v>0.7105474539414091</v>
+        <v>0.7105474539414729</v>
       </c>
       <c r="D228">
-        <v>1.050427437032271</v>
+        <v>1.050427437032354</v>
       </c>
       <c r="E228">
-        <v>-0.1462611899757082</v>
+        <v>-0.1462611899756236</v>
       </c>
       <c r="F228">
-        <v>-0.3417195441729662</v>
+        <v>-0.3417195441728763</v>
       </c>
       <c r="G228">
-        <v>0.04919716422155009</v>
+        <v>0.04919716422162915</v>
       </c>
       <c r="H228">
-        <v>0.09972548257978654</v>
+        <v>0.09972548257978375</v>
       </c>
       <c r="I228">
-        <v>-1.466638076769296</v>
+        <v>-1.46663807676849</v>
       </c>
       <c r="J228">
-        <v>0.1424745361595251</v>
+        <v>0.1424745361597453</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -18623,31 +18623,31 @@
         </is>
       </c>
       <c r="B229">
-        <v>1.017258029520061</v>
+        <v>1.017258029520188</v>
       </c>
       <c r="C229">
-        <v>0.7349840453931983</v>
+        <v>0.7349840453932686</v>
       </c>
       <c r="D229">
-        <v>1.407940628247838</v>
+        <v>1.407940628248055</v>
       </c>
       <c r="E229">
-        <v>0.01711080122811749</v>
+        <v>0.01711080122824234</v>
       </c>
       <c r="F229">
-        <v>-0.3079064869529291</v>
+        <v>-0.3079064869528335</v>
       </c>
       <c r="G229">
-        <v>0.3421280894091643</v>
+        <v>0.3421280894093183</v>
       </c>
       <c r="H229">
-        <v>0.1658281941631284</v>
+        <v>0.1658281941631433</v>
       </c>
       <c r="I229">
-        <v>0.1031839085896657</v>
+        <v>0.1031839085904091</v>
       </c>
       <c r="J229">
-        <v>0.9178170108233794</v>
+        <v>0.9178170108227894</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -18703,31 +18703,31 @@
         </is>
       </c>
       <c r="B230">
-        <v>1.384049952314249</v>
+        <v>1.384049952314071</v>
       </c>
       <c r="C230">
-        <v>1.02354571919225</v>
+        <v>1.023545719192127</v>
       </c>
       <c r="D230">
-        <v>1.871527802405155</v>
+        <v>1.871527802404899</v>
       </c>
       <c r="E230">
-        <v>0.3250139492567594</v>
+        <v>0.3250139492566308</v>
       </c>
       <c r="F230">
-        <v>0.02327279458149784</v>
+        <v>0.02327279458137744</v>
       </c>
       <c r="G230">
-        <v>0.6267551039320209</v>
+        <v>0.6267551039318842</v>
       </c>
       <c r="H230">
-        <v>0.153952397623302</v>
+        <v>0.1539523976232978</v>
       </c>
       <c r="I230">
-        <v>2.111132754502589</v>
+        <v>2.111132754501811</v>
       </c>
       <c r="J230">
-        <v>0.03476090278140699</v>
+        <v>0.03476090278147391</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -18783,31 +18783,31 @@
         </is>
       </c>
       <c r="B231">
-        <v>0.8488168610315502</v>
+        <v>0.8488168610316439</v>
       </c>
       <c r="C231">
-        <v>0.7039638265247181</v>
+        <v>0.7039638265247997</v>
       </c>
       <c r="D231">
-        <v>1.023475974793082</v>
+        <v>1.023475974793189</v>
       </c>
       <c r="E231">
-        <v>-0.1639118273278821</v>
+        <v>-0.1639118273277717</v>
       </c>
       <c r="F231">
-        <v>-0.3510283069216238</v>
+        <v>-0.3510283069215079</v>
       </c>
       <c r="G231">
-        <v>0.02320465226585958</v>
+        <v>0.02320465226596459</v>
       </c>
       <c r="H231">
-        <v>0.09546934590109445</v>
+        <v>0.09546934590109168</v>
       </c>
       <c r="I231">
-        <v>-1.716905314274317</v>
+        <v>-1.71690531427321</v>
       </c>
       <c r="J231">
-        <v>0.08599647375705971</v>
+        <v>0.08599647375726177</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -18863,31 +18863,31 @@
         </is>
       </c>
       <c r="B232">
-        <v>1.028786183465735</v>
+        <v>1.028786183465667</v>
       </c>
       <c r="C232">
-        <v>0.7724103631881429</v>
+        <v>0.7724103631880994</v>
       </c>
       <c r="D232">
-        <v>1.370257393908358</v>
+        <v>1.370257393908255</v>
       </c>
       <c r="E232">
-        <v>0.02837964465378211</v>
+        <v>0.02837964465371606</v>
       </c>
       <c r="F232">
-        <v>-0.2582393116506896</v>
+        <v>-0.258239311650746</v>
       </c>
       <c r="G232">
-        <v>0.3149986009582538</v>
+        <v>0.3149986009581781</v>
       </c>
       <c r="H232">
-        <v>0.1462368485162409</v>
+        <v>0.146236848516236</v>
       </c>
       <c r="I232">
-        <v>0.1940663036828935</v>
+        <v>0.1940663036824481</v>
       </c>
       <c r="J232">
-        <v>0.8461239657665246</v>
+        <v>0.8461239657668734</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -18943,31 +18943,31 @@
         </is>
       </c>
       <c r="B233">
-        <v>1.129656473674332</v>
+        <v>1.129656473674353</v>
       </c>
       <c r="C233">
-        <v>0.9192117714802541</v>
+        <v>0.919211771480283</v>
       </c>
       <c r="D233">
-        <v>1.388280468231296</v>
+        <v>1.388280468231304</v>
       </c>
       <c r="E233">
-        <v>0.1219135809072434</v>
+        <v>0.1219135809072621</v>
       </c>
       <c r="F233">
-        <v>-0.08423874630651119</v>
+        <v>-0.0842387463064798</v>
       </c>
       <c r="G233">
-        <v>0.3280659081209982</v>
+        <v>0.328065908121004</v>
       </c>
       <c r="H233">
-        <v>0.1051816915207923</v>
+        <v>0.1051816915207857</v>
       </c>
       <c r="I233">
-        <v>1.159076062996607</v>
+        <v>1.159076062996856</v>
       </c>
       <c r="J233">
-        <v>0.2464251819836815</v>
+        <v>0.2464251819835799</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -19023,31 +19023,31 @@
         </is>
       </c>
       <c r="B234">
-        <v>0.8482390798211896</v>
+        <v>0.8482390798211727</v>
       </c>
       <c r="C234">
-        <v>0.7097208244992504</v>
+        <v>0.7097208244992416</v>
       </c>
       <c r="D234">
-        <v>1.01379234157819</v>
+        <v>1.013792341578162</v>
       </c>
       <c r="E234">
-        <v>-0.1645927491746828</v>
+        <v>-0.1645927491747027</v>
       </c>
       <c r="F234">
-        <v>-0.3428835912027383</v>
+        <v>-0.3428835912027509</v>
       </c>
       <c r="G234">
-        <v>0.0136980928533726</v>
+        <v>0.01369809285334544</v>
       </c>
       <c r="H234">
-        <v>0.09096638684914161</v>
+        <v>0.09096638684913785</v>
       </c>
       <c r="I234">
-        <v>-1.8093798695956</v>
+        <v>-1.809379869595894</v>
       </c>
       <c r="J234">
-        <v>0.07039200836150949</v>
+        <v>0.07039200836146421</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -19103,31 +19103,31 @@
         </is>
       </c>
       <c r="B235">
-        <v>0.7959589832688015</v>
+        <v>0.7959589832688024</v>
       </c>
       <c r="C235">
-        <v>0.660303955389838</v>
+        <v>0.6603039553898403</v>
       </c>
       <c r="D235">
-        <v>0.9594834286162366</v>
+        <v>0.9594834286162354</v>
       </c>
       <c r="E235">
-        <v>-0.2282076230221777</v>
+        <v>-0.2282076230221766</v>
       </c>
       <c r="F235">
-        <v>-0.4150550115075071</v>
+        <v>-0.4150550115075036</v>
       </c>
       <c r="G235">
-        <v>-0.04136023453684835</v>
+        <v>-0.04136023453684962</v>
       </c>
       <c r="H235">
-        <v>0.09533205199644371</v>
+        <v>0.09533205199644249</v>
       </c>
       <c r="I235">
-        <v>-2.393818429825583</v>
+        <v>-2.393818429825603</v>
       </c>
       <c r="J235">
-        <v>0.01667400074673961</v>
+        <v>0.01667400074673869</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -19183,31 +19183,31 @@
         </is>
       </c>
       <c r="B236">
-        <v>1.152169518333816</v>
+        <v>1.152169518334078</v>
       </c>
       <c r="C236">
-        <v>0.8700589234639504</v>
+        <v>0.870058923464157</v>
       </c>
       <c r="D236">
-        <v>1.525752524544482</v>
+        <v>1.525752524544815</v>
       </c>
       <c r="E236">
-        <v>0.1416467027794415</v>
+        <v>0.1416467027796695</v>
       </c>
       <c r="F236">
-        <v>-0.13919434150747</v>
+        <v>-0.1391943415072325</v>
       </c>
       <c r="G236">
-        <v>0.4224877470663529</v>
+        <v>0.4224877470665713</v>
       </c>
       <c r="H236">
-        <v>0.1432888800519549</v>
+        <v>0.1432888800519501</v>
       </c>
       <c r="I236">
-        <v>0.9885393948789462</v>
+        <v>0.9885393948805705</v>
       </c>
       <c r="J236">
-        <v>0.3228885507732108</v>
+        <v>0.3228885507724158</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -19263,31 +19263,31 @@
         </is>
       </c>
       <c r="B237">
-        <v>0.8606292615850961</v>
+        <v>0.8606292615850497</v>
       </c>
       <c r="C237">
-        <v>0.7125769321472664</v>
+        <v>0.7125769321472428</v>
       </c>
       <c r="D237">
-        <v>1.039442469270718</v>
+        <v>1.039442469270641</v>
       </c>
       <c r="E237">
-        <v>-0.1500914577786135</v>
+        <v>-0.1500914577786674</v>
       </c>
       <c r="F237">
-        <v>-0.3388673977246743</v>
+        <v>-0.3388673977247074</v>
       </c>
       <c r="G237">
-        <v>0.03868448216744731</v>
+        <v>0.03868448216737254</v>
       </c>
       <c r="H237">
-        <v>0.09631602490408062</v>
+        <v>0.09631602490406994</v>
       </c>
       <c r="I237">
-        <v>-1.558322801715362</v>
+        <v>-1.558322801716095</v>
       </c>
       <c r="J237">
-        <v>0.1191567463872959</v>
+        <v>0.1191567463871226</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -19343,31 +19343,31 @@
         </is>
       </c>
       <c r="B238">
-        <v>0.8415435446605739</v>
+        <v>0.8415435446607077</v>
       </c>
       <c r="C238">
-        <v>0.6426736783082648</v>
+        <v>0.642673678308364</v>
       </c>
       <c r="D238">
-        <v>1.101951988175546</v>
+        <v>1.101951988175726</v>
       </c>
       <c r="E238">
-        <v>-0.1725175202128671</v>
+        <v>-0.1725175202127081</v>
       </c>
       <c r="F238">
-        <v>-0.4421181823085694</v>
+        <v>-0.4421181823084152</v>
       </c>
       <c r="G238">
-        <v>0.09708314188283525</v>
+        <v>0.09708314188299887</v>
       </c>
       <c r="H238">
-        <v>0.1375538857970239</v>
+        <v>0.1375538857970262</v>
       </c>
       <c r="I238">
-        <v>-1.254181364730299</v>
+        <v>-1.254181364729122</v>
       </c>
       <c r="J238">
-        <v>0.2097760916869975</v>
+        <v>0.2097760916874252</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -19423,31 +19423,31 @@
         </is>
       </c>
       <c r="B239">
-        <v>1.144552581451421</v>
+        <v>1.144552581451572</v>
       </c>
       <c r="C239">
-        <v>0.9175414400033376</v>
+        <v>0.9175414400034597</v>
       </c>
       <c r="D239">
-        <v>1.427729097121049</v>
+        <v>1.427729097121234</v>
       </c>
       <c r="E239">
-        <v>0.1350138020824728</v>
+        <v>0.1350138020826042</v>
       </c>
       <c r="F239">
-        <v>-0.08605753385720279</v>
+        <v>-0.08605753385706968</v>
       </c>
       <c r="G239">
-        <v>0.3560851380221483</v>
+        <v>0.3560851380222779</v>
       </c>
       <c r="H239">
-        <v>0.1127935705367334</v>
+        <v>0.1127935705367325</v>
       </c>
       <c r="I239">
-        <v>1.196999097023025</v>
+        <v>1.196999097024199</v>
       </c>
       <c r="J239">
-        <v>0.2313069067036723</v>
+        <v>0.2313069067032146</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -19503,31 +19503,31 @@
         </is>
       </c>
       <c r="B240">
-        <v>0.8332202608758191</v>
+        <v>0.8332202608757497</v>
       </c>
       <c r="C240">
-        <v>0.6971947647272524</v>
+        <v>0.6971947647271884</v>
       </c>
       <c r="D240">
-        <v>0.9957848771362562</v>
+        <v>0.9957848771361818</v>
       </c>
       <c r="E240">
-        <v>-0.1824572529492785</v>
+        <v>-0.1824572529493618</v>
       </c>
       <c r="F240">
-        <v>-0.3606904743615201</v>
+        <v>-0.3606904743616118</v>
       </c>
       <c r="G240">
-        <v>-0.004224031537037005</v>
+        <v>-0.004224031537111705</v>
       </c>
       <c r="H240">
-        <v>0.09093698803555701</v>
+        <v>0.09093698803556141</v>
       </c>
       <c r="I240">
-        <v>-2.006414077382203</v>
+        <v>-2.006414077383021</v>
       </c>
       <c r="J240">
-        <v>0.04481208760901129</v>
+        <v>0.04481208760892384</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -19583,31 +19583,31 @@
         </is>
       </c>
       <c r="B241">
-        <v>0.8140246002458702</v>
+        <v>0.8140246002459016</v>
       </c>
       <c r="C241">
-        <v>0.6635061977166652</v>
+        <v>0.6635061977166938</v>
       </c>
       <c r="D241">
-        <v>0.9986885609897679</v>
+        <v>0.998688560989802</v>
       </c>
       <c r="E241">
-        <v>-0.2057646920039821</v>
+        <v>-0.2057646920039435</v>
       </c>
       <c r="F241">
-        <v>-0.4102170843090171</v>
+        <v>-0.410217084308974</v>
       </c>
       <c r="G241">
-        <v>-0.00131229969894703</v>
+        <v>-0.001312299698912902</v>
       </c>
       <c r="H241">
-        <v>0.1043143618544675</v>
+        <v>0.1043143618544652</v>
       </c>
       <c r="I241">
-        <v>-1.972544224457332</v>
+        <v>-1.972544224457005</v>
       </c>
       <c r="J241">
-        <v>0.04854751298783735</v>
+        <v>0.04854751298787473</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
